--- a/demo_data/sectors/insaat_taahhut/sales_ledger.xlsx
+++ b/demo_data/sectors/insaat_taahhut/sales_ledger.xlsx
@@ -470,12 +470,12 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
+          <t>Maliyet</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
           <t>Net Satış Tutarı</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>Maliyet</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
@@ -492,37 +492,37 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Gaziantep İhracat ve Toptan</t>
+          <t>Ege Dağıtım ve Ticaret Ltd.</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Ürün Alpha Standart</t>
+          <t>Özel Sipariş Modeli X</t>
         </is>
       </c>
       <c r="C2" s="2" t="n">
         <v>45658</v>
       </c>
       <c r="D2" t="n">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="E2" t="n">
-        <v>1850</v>
+        <v>21500</v>
       </c>
       <c r="F2" t="n">
-        <v>165065.4</v>
+        <v>368669.12</v>
       </c>
       <c r="G2" t="n">
-        <v>19807.85</v>
+        <v>-0.02</v>
       </c>
       <c r="H2" t="n">
-        <v>145257.56</v>
+        <v>243493.1</v>
       </c>
       <c r="I2" t="n">
-        <v>111530.68</v>
+        <v>368669.14</v>
       </c>
       <c r="J2" t="n">
-        <v>145257.56</v>
+        <v>368669.14</v>
       </c>
       <c r="K2" t="n">
         <v>0</v>
@@ -531,37 +531,37 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Bursa İmalat Tedarik Ltd.</t>
+          <t>Ege Dağıtım ve Ticaret Ltd.</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Yedek Parça Servis Paketi</t>
+          <t>Ürün Alpha Standart</t>
         </is>
       </c>
       <c r="C3" s="2" t="n">
         <v>45660</v>
       </c>
       <c r="D3" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="E3" t="n">
-        <v>2400</v>
+        <v>1850</v>
       </c>
       <c r="F3" t="n">
-        <v>95172.85000000001</v>
+        <v>15861.35</v>
       </c>
       <c r="G3" t="n">
-        <v>2855.19</v>
+        <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>92317.66</v>
+        <v>10717.13</v>
       </c>
       <c r="I3" t="n">
-        <v>59483.03</v>
+        <v>15861.35</v>
       </c>
       <c r="J3" t="n">
-        <v>92317.66</v>
+        <v>15861.35</v>
       </c>
       <c r="K3" t="n">
         <v>0</v>
@@ -570,37 +570,37 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Toroslar Lojistik ve Ticaret</t>
+          <t>Marmara Perakende Çözümleri</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Yedek Parça Servis Paketi</t>
+          <t>Ürün Delta Kompakt</t>
         </is>
       </c>
       <c r="C4" s="2" t="n">
         <v>45662</v>
       </c>
       <c r="D4" t="n">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="E4" t="n">
-        <v>2400</v>
+        <v>1200</v>
       </c>
       <c r="F4" t="n">
-        <v>285518.54</v>
+        <v>66874.87</v>
       </c>
       <c r="G4" t="n">
-        <v>8565.559999999999</v>
+        <v>1437.41</v>
       </c>
       <c r="H4" t="n">
-        <v>276952.98</v>
+        <v>45697.83</v>
       </c>
       <c r="I4" t="n">
-        <v>178449.09</v>
+        <v>65437.46</v>
       </c>
       <c r="J4" t="n">
-        <v>276952.98</v>
+        <v>65437.46</v>
       </c>
       <c r="K4" t="n">
         <v>0</v>
@@ -609,7 +609,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Karadeniz Toptan Dağıtım A.Ş.</t>
+          <t>İzmir Ticari Faaliyetler A.Ş.</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -627,19 +627,19 @@
         <v>4200</v>
       </c>
       <c r="F5" t="n">
-        <v>395562.14</v>
+        <v>342090.66</v>
       </c>
       <c r="G5" t="n">
-        <v>11866.86</v>
+        <v>18382.24</v>
       </c>
       <c r="H5" t="n">
-        <v>383695.27</v>
+        <v>228060.44</v>
       </c>
       <c r="I5" t="n">
-        <v>263708.09</v>
+        <v>323708.42</v>
       </c>
       <c r="J5" t="n">
-        <v>383695.27</v>
+        <v>323708.42</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
@@ -648,37 +648,37 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Ege Dağıtım ve Ticaret Ltd.</t>
+          <t>Karadeniz Toptan Dağıtım A.Ş.</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Ürün Alpha Standart</t>
+          <t>Ürün Beta Premium</t>
         </is>
       </c>
       <c r="C6" s="2" t="n">
         <v>45666</v>
       </c>
       <c r="D6" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E6" t="n">
-        <v>1850</v>
+        <v>4200</v>
       </c>
       <c r="F6" t="n">
-        <v>55021.8</v>
+        <v>18004.77</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>55021.8</v>
+        <v>12003.18</v>
       </c>
       <c r="I6" t="n">
-        <v>37176.89</v>
+        <v>18004.77</v>
       </c>
       <c r="J6" t="n">
-        <v>55021.8</v>
+        <v>18004.77</v>
       </c>
       <c r="K6" t="n">
         <v>0</v>
@@ -687,37 +687,37 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Kocaeli Ağır Sanayi Pazarlama</t>
+          <t>Toroslar Lojistik ve Ticaret</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Ürün Alpha Standart</t>
+          <t>Özel Sipariş Modeli X</t>
         </is>
       </c>
       <c r="C7" s="2" t="n">
         <v>45668</v>
       </c>
       <c r="D7" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="E7" t="n">
-        <v>1850</v>
+        <v>21500</v>
       </c>
       <c r="F7" t="n">
-        <v>119213.9</v>
+        <v>460836.42</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>119213.9</v>
+        <v>304366.38</v>
       </c>
       <c r="I7" t="n">
-        <v>80549.92999999999</v>
+        <v>460836.42</v>
       </c>
       <c r="J7" t="n">
-        <v>119213.9</v>
+        <v>460836.42</v>
       </c>
       <c r="K7" t="n">
         <v>0</v>
@@ -731,32 +731,32 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Özel Sipariş Modeli X</t>
+          <t>Ürün Zeta Hızlı Tüketim</t>
         </is>
       </c>
       <c r="C8" s="2" t="n">
         <v>45670</v>
       </c>
       <c r="D8" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="E8" t="n">
-        <v>21500</v>
+        <v>650</v>
       </c>
       <c r="F8" t="n">
-        <v>1065737.59</v>
+        <v>11145.81</v>
       </c>
       <c r="G8" t="n">
-        <v>31972.13</v>
+        <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>1033765.46</v>
+        <v>7544.86</v>
       </c>
       <c r="I8" t="n">
-        <v>703882.5</v>
+        <v>11145.81</v>
       </c>
       <c r="J8" t="n">
-        <v>1033765.46</v>
+        <v>11145.81</v>
       </c>
       <c r="K8" t="n">
         <v>0</v>
@@ -765,37 +765,37 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>İç Anadolu Tüketim Malları</t>
+          <t>Güneydoğu Pazarlama Ltd.</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Ürün Beta Premium</t>
+          <t>Ürün Alpha Standart</t>
         </is>
       </c>
       <c r="C9" s="2" t="n">
         <v>45672</v>
       </c>
       <c r="D9" t="n">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="E9" t="n">
-        <v>4200</v>
+        <v>1850</v>
       </c>
       <c r="F9" t="n">
-        <v>374743.08</v>
+        <v>47584.04</v>
       </c>
       <c r="G9" t="n">
-        <v>18737.15</v>
+        <v>2556.93</v>
       </c>
       <c r="H9" t="n">
-        <v>356005.93</v>
+        <v>32151.38</v>
       </c>
       <c r="I9" t="n">
-        <v>249828.72</v>
+        <v>45027.11</v>
       </c>
       <c r="J9" t="n">
-        <v>356005.93</v>
+        <v>45027.11</v>
       </c>
       <c r="K9" t="n">
         <v>0</v>
@@ -804,37 +804,37 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Anadolu Sanayi Grubu A.Ş.</t>
+          <t>Akdeniz Endüstriyel Ürünler</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Ürün Zeta Hızlı Tüketim</t>
+          <t>Yedek Parça Servis Paketi</t>
         </is>
       </c>
       <c r="C10" s="2" t="n">
         <v>45674</v>
       </c>
       <c r="D10" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="E10" t="n">
-        <v>650</v>
+        <v>2400</v>
       </c>
       <c r="F10" t="n">
-        <v>22553.98</v>
+        <v>164615.06</v>
       </c>
       <c r="G10" t="n">
-        <v>676.62</v>
+        <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>21877.36</v>
+        <v>102884.41</v>
       </c>
       <c r="I10" t="n">
-        <v>15267.31</v>
+        <v>164615.06</v>
       </c>
       <c r="J10" t="n">
-        <v>21877.36</v>
+        <v>164615.06</v>
       </c>
       <c r="K10" t="n">
         <v>0</v>
@@ -843,37 +843,37 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Ankara Proje Yönetim ve Satış</t>
+          <t>Akdeniz Endüstriyel Ürünler</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Ürün Epsilon Profesyonel</t>
+          <t>Yedek Parça Servis Paketi</t>
         </is>
       </c>
       <c r="C11" s="2" t="n">
         <v>45676</v>
       </c>
       <c r="D11" t="n">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="E11" t="n">
-        <v>15400</v>
+        <v>2400</v>
       </c>
       <c r="F11" t="n">
-        <v>1832077.28</v>
+        <v>61730.65</v>
       </c>
       <c r="G11" t="n">
-        <v>146566.18</v>
+        <v>1326.84</v>
       </c>
       <c r="H11" t="n">
-        <v>1685511.09</v>
+        <v>38581.65</v>
       </c>
       <c r="I11" t="n">
-        <v>1165867.36</v>
+        <v>60403.81</v>
       </c>
       <c r="J11" t="n">
-        <v>1685511.09</v>
+        <v>60403.81</v>
       </c>
       <c r="K11" t="n">
         <v>0</v>
@@ -887,32 +887,32 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Özel Sipariş Modeli X</t>
+          <t>Ürün Gamma Endüstriyel</t>
         </is>
       </c>
       <c r="C12" s="2" t="n">
         <v>45678</v>
       </c>
       <c r="D12" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="E12" t="n">
-        <v>21500</v>
+        <v>8900</v>
       </c>
       <c r="F12" t="n">
-        <v>1278885.11</v>
+        <v>343376.72</v>
       </c>
       <c r="G12" t="n">
-        <v>102310.81</v>
+        <v>7380.54</v>
       </c>
       <c r="H12" t="n">
-        <v>1176574.3</v>
+        <v>227631.76</v>
       </c>
       <c r="I12" t="n">
-        <v>844659</v>
+        <v>335996.18</v>
       </c>
       <c r="J12" t="n">
-        <v>1176574.3</v>
+        <v>335996.18</v>
       </c>
       <c r="K12" t="n">
         <v>0</v>
@@ -926,32 +926,32 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Ürün Delta Kompakt</t>
+          <t>Ürün Gamma Endüstriyel</t>
         </is>
       </c>
       <c r="C13" s="2" t="n">
         <v>45680</v>
       </c>
       <c r="D13" t="n">
-        <v>24</v>
+        <v>2</v>
       </c>
       <c r="E13" t="n">
-        <v>1200</v>
+        <v>8900</v>
       </c>
       <c r="F13" t="n">
-        <v>142759.27</v>
+        <v>76305.94</v>
       </c>
       <c r="G13" t="n">
-        <v>11420.74</v>
+        <v>4100.3</v>
       </c>
       <c r="H13" t="n">
-        <v>131338.53</v>
+        <v>50584.84</v>
       </c>
       <c r="I13" t="n">
-        <v>97552.17</v>
+        <v>72205.64</v>
       </c>
       <c r="J13" t="n">
-        <v>131338.53</v>
+        <v>72205.64</v>
       </c>
       <c r="K13" t="n">
         <v>0</v>
@@ -960,7 +960,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Kocaeli Ağır Sanayi Pazarlama</t>
+          <t>Ankara Proje Yönetim ve Satış</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -972,25 +972,25 @@
         <v>45682</v>
       </c>
       <c r="D14" t="n">
-        <v>5</v>
+        <v>21</v>
       </c>
       <c r="E14" t="n">
         <v>1200</v>
       </c>
       <c r="F14" t="n">
-        <v>29741.51</v>
+        <v>108028.63</v>
       </c>
       <c r="G14" t="n">
-        <v>0</v>
+        <v>2321.97</v>
       </c>
       <c r="H14" t="n">
-        <v>29741.51</v>
+        <v>73819.56</v>
       </c>
       <c r="I14" t="n">
-        <v>20323.37</v>
+        <v>105706.66</v>
       </c>
       <c r="J14" t="n">
-        <v>29741.51</v>
+        <v>105706.66</v>
       </c>
       <c r="K14" t="n">
         <v>0</v>
@@ -999,7 +999,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Gaziantep İhracat ve Toptan</t>
+          <t>Güneydoğu Pazarlama Ltd.</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1011,25 +1011,25 @@
         <v>45684</v>
       </c>
       <c r="D15" t="n">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="E15" t="n">
         <v>2400</v>
       </c>
       <c r="F15" t="n">
-        <v>11896.61</v>
+        <v>185191.94</v>
       </c>
       <c r="G15" t="n">
-        <v>0</v>
+        <v>5970.77</v>
       </c>
       <c r="H15" t="n">
-        <v>11896.61</v>
+        <v>115744.96</v>
       </c>
       <c r="I15" t="n">
-        <v>7435.38</v>
+        <v>179221.17</v>
       </c>
       <c r="J15" t="n">
-        <v>11896.61</v>
+        <v>179221.17</v>
       </c>
       <c r="K15" t="n">
         <v>0</v>
@@ -1038,37 +1038,37 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>İstanbul Kurumsal Tedarik A.Ş.</t>
+          <t>Anadolu Sanayi Grubu A.Ş.</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Ürün Zeta Hızlı Tüketim</t>
+          <t>Ürün Beta Premium</t>
         </is>
       </c>
       <c r="C16" s="2" t="n">
         <v>45686</v>
       </c>
       <c r="D16" t="n">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="E16" t="n">
-        <v>650</v>
+        <v>4200</v>
       </c>
       <c r="F16" t="n">
-        <v>67661.94</v>
+        <v>162042.95</v>
       </c>
       <c r="G16" t="n">
-        <v>8119.43</v>
+        <v>5224.43</v>
       </c>
       <c r="H16" t="n">
-        <v>59542.51</v>
+        <v>108028.63</v>
       </c>
       <c r="I16" t="n">
-        <v>45801.93</v>
+        <v>156818.52</v>
       </c>
       <c r="J16" t="n">
-        <v>59542.51</v>
+        <v>156818.52</v>
       </c>
       <c r="K16" t="n">
         <v>0</v>
@@ -1077,37 +1077,37 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Gaziantep İhracat ve Toptan</t>
+          <t>Marmara Perakende Çözümleri</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Ürün Alpha Standart</t>
+          <t>Yedek Parça Servis Paketi</t>
         </is>
       </c>
       <c r="C17" s="2" t="n">
         <v>45688</v>
       </c>
       <c r="D17" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="E17" t="n">
-        <v>1850</v>
+        <v>2400</v>
       </c>
       <c r="F17" t="n">
-        <v>100873.3</v>
+        <v>72019.09</v>
       </c>
       <c r="G17" t="n">
-        <v>0</v>
+        <v>3869.95</v>
       </c>
       <c r="H17" t="n">
-        <v>100873.3</v>
+        <v>45011.93</v>
       </c>
       <c r="I17" t="n">
-        <v>68157.64</v>
+        <v>68149.14</v>
       </c>
       <c r="J17" t="n">
-        <v>100873.3</v>
+        <v>68149.14</v>
       </c>
       <c r="K17" t="n">
         <v>0</v>
@@ -1116,37 +1116,37 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Kocaeli Ağır Sanayi Pazarlama</t>
+          <t>Toroslar Lojistik ve Ticaret</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Yedek Parça Servis Paketi</t>
+          <t>Ürün Alpha Standart</t>
         </is>
       </c>
       <c r="C18" s="2" t="n">
         <v>45690</v>
       </c>
       <c r="D18" t="n">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="E18" t="n">
-        <v>2400</v>
+        <v>1850</v>
       </c>
       <c r="F18" t="n">
-        <v>285518.54</v>
+        <v>103098.75</v>
       </c>
       <c r="G18" t="n">
-        <v>34262.22</v>
+        <v>2216</v>
       </c>
       <c r="H18" t="n">
-        <v>251256.31</v>
+        <v>69661.32000000001</v>
       </c>
       <c r="I18" t="n">
-        <v>178449.09</v>
+        <v>100882.75</v>
       </c>
       <c r="J18" t="n">
-        <v>251256.31</v>
+        <v>100882.75</v>
       </c>
       <c r="K18" t="n">
         <v>0</v>
@@ -1155,37 +1155,37 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Karadeniz Toptan Dağıtım A.Ş.</t>
+          <t>Güneydoğu Pazarlama Ltd.</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Ürün Beta Premium</t>
+          <t>Özel Sipariş Modeli X</t>
         </is>
       </c>
       <c r="C19" s="2" t="n">
         <v>45692</v>
       </c>
       <c r="D19" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="E19" t="n">
-        <v>4200</v>
+        <v>21500</v>
       </c>
       <c r="F19" t="n">
-        <v>145733.42</v>
+        <v>1106007.41</v>
       </c>
       <c r="G19" t="n">
-        <v>11658.67</v>
+        <v>59431.31</v>
       </c>
       <c r="H19" t="n">
-        <v>134074.75</v>
+        <v>730479.3100000001</v>
       </c>
       <c r="I19" t="n">
-        <v>97155.61</v>
+        <v>1046576.1</v>
       </c>
       <c r="J19" t="n">
-        <v>134074.75</v>
+        <v>1046576.1</v>
       </c>
       <c r="K19" t="n">
         <v>0</v>
@@ -1194,37 +1194,37 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Toroslar Lojistik ve Ticaret</t>
+          <t>İstanbul Kurumsal Tedarik A.Ş.</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Yedek Parça Servis Paketi</t>
+          <t>Ürün Zeta Hızlı Tüketim</t>
         </is>
       </c>
       <c r="C20" s="2" t="n">
         <v>45694</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E20" t="n">
-        <v>2400</v>
+        <v>650</v>
       </c>
       <c r="F20" t="n">
-        <v>190345.69</v>
+        <v>36223.89</v>
       </c>
       <c r="G20" t="n">
-        <v>0</v>
+        <v>778.6</v>
       </c>
       <c r="H20" t="n">
-        <v>190345.69</v>
+        <v>24520.78</v>
       </c>
       <c r="I20" t="n">
-        <v>118966.06</v>
+        <v>35445.29</v>
       </c>
       <c r="J20" t="n">
-        <v>190345.69</v>
+        <v>35445.29</v>
       </c>
       <c r="K20" t="n">
         <v>0</v>
@@ -1238,32 +1238,32 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Ürün Epsilon Profesyonel</t>
+          <t>Ürün Alpha Standart</t>
         </is>
       </c>
       <c r="C21" s="2" t="n">
         <v>45696</v>
       </c>
       <c r="D21" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="E21" t="n">
-        <v>15400</v>
+        <v>1850</v>
       </c>
       <c r="F21" t="n">
-        <v>229009.66</v>
+        <v>87237.41</v>
       </c>
       <c r="G21" t="n">
-        <v>0</v>
+        <v>4687.7</v>
       </c>
       <c r="H21" t="n">
-        <v>229009.66</v>
+        <v>58944.19</v>
       </c>
       <c r="I21" t="n">
-        <v>145733.42</v>
+        <v>82549.71000000001</v>
       </c>
       <c r="J21" t="n">
-        <v>229009.66</v>
+        <v>82549.71000000001</v>
       </c>
       <c r="K21" t="n">
         <v>0</v>
@@ -1272,37 +1272,37 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Gaziantep İhracat ve Toptan</t>
+          <t>Toroslar Lojistik ve Ticaret</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Ürün Delta Kompakt</t>
+          <t>Ürün Alpha Standart</t>
         </is>
       </c>
       <c r="C22" s="2" t="n">
         <v>45698</v>
       </c>
       <c r="D22" t="n">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="E22" t="n">
-        <v>1200</v>
+        <v>1850</v>
       </c>
       <c r="F22" t="n">
-        <v>101121.15</v>
+        <v>198266.83</v>
       </c>
       <c r="G22" t="n">
-        <v>5056.06</v>
+        <v>4261.55</v>
       </c>
       <c r="H22" t="n">
-        <v>96065.09</v>
+        <v>133964.08</v>
       </c>
       <c r="I22" t="n">
-        <v>69099.45</v>
+        <v>194005.28</v>
       </c>
       <c r="J22" t="n">
-        <v>96065.09</v>
+        <v>194005.28</v>
       </c>
       <c r="K22" t="n">
         <v>0</v>
@@ -1311,37 +1311,37 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Bursa İmalat Tedarik Ltd.</t>
+          <t>Anadolu Sanayi Grubu A.Ş.</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Ürün Zeta Hızlı Tüketim</t>
+          <t>Özel Sipariş Modeli X</t>
         </is>
       </c>
       <c r="C23" s="2" t="n">
         <v>45700</v>
       </c>
       <c r="D23" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E23" t="n">
-        <v>650</v>
+        <v>21500</v>
       </c>
       <c r="F23" t="n">
-        <v>48329.96</v>
+        <v>1566843.83</v>
       </c>
       <c r="G23" t="n">
-        <v>5799.6</v>
+        <v>33677.74</v>
       </c>
       <c r="H23" t="n">
-        <v>42530.37</v>
+        <v>1034845.69</v>
       </c>
       <c r="I23" t="n">
-        <v>32715.67</v>
+        <v>1533166.09</v>
       </c>
       <c r="J23" t="n">
-        <v>42530.37</v>
+        <v>1533166.09</v>
       </c>
       <c r="K23" t="n">
         <v>0</v>
@@ -1350,37 +1350,37 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Ege Dağıtım ve Ticaret Ltd.</t>
+          <t>Kocaeli Ağır Sanayi Pazarlama</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Ürün Beta Premium</t>
+          <t>Ürün Delta Kompakt</t>
         </is>
       </c>
       <c r="C24" s="2" t="n">
         <v>45702</v>
       </c>
       <c r="D24" t="n">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="E24" t="n">
-        <v>4200</v>
+        <v>1200</v>
       </c>
       <c r="F24" t="n">
-        <v>353924.02</v>
+        <v>30865.32</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>353924.02</v>
+        <v>21091.3</v>
       </c>
       <c r="I24" t="n">
-        <v>235949.35</v>
+        <v>30865.32</v>
       </c>
       <c r="J24" t="n">
-        <v>353924.02</v>
+        <v>30865.32</v>
       </c>
       <c r="K24" t="n">
         <v>0</v>
@@ -1389,37 +1389,37 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>İzmir Ticari Faaliyetler A.Ş.</t>
+          <t>Toroslar Lojistik ve Ticaret</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Yedek Parça Servis Paketi</t>
+          <t>Ürün Delta Kompakt</t>
         </is>
       </c>
       <c r="C25" s="2" t="n">
         <v>45704</v>
       </c>
       <c r="D25" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="E25" t="n">
-        <v>2400</v>
+        <v>1200</v>
       </c>
       <c r="F25" t="n">
-        <v>35689.82</v>
+        <v>46297.98</v>
       </c>
       <c r="G25" t="n">
-        <v>2855.19</v>
+        <v>2487.82</v>
       </c>
       <c r="H25" t="n">
-        <v>32834.63</v>
+        <v>31636.96</v>
       </c>
       <c r="I25" t="n">
-        <v>22306.14</v>
+        <v>43810.16</v>
       </c>
       <c r="J25" t="n">
-        <v>32834.63</v>
+        <v>43810.16</v>
       </c>
       <c r="K25" t="n">
         <v>0</v>
@@ -1428,7 +1428,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Ankara Proje Yönetim ve Satış</t>
+          <t>Adana Bölge Bayi A.Ş.</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1440,25 +1440,25 @@
         <v>45706</v>
       </c>
       <c r="D26" t="n">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="E26" t="n">
         <v>1850</v>
       </c>
       <c r="F26" t="n">
-        <v>128384.2</v>
+        <v>198266.83</v>
       </c>
       <c r="G26" t="n">
-        <v>15406.1</v>
+        <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>112978.1</v>
+        <v>133964.08</v>
       </c>
       <c r="I26" t="n">
-        <v>86746.08</v>
+        <v>198266.83</v>
       </c>
       <c r="J26" t="n">
-        <v>112978.1</v>
+        <v>198266.83</v>
       </c>
       <c r="K26" t="n">
         <v>0</v>
@@ -1467,37 +1467,37 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Marmara Perakende Çözümleri</t>
+          <t>Ankara Proje Yönetim ve Satış</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Ürün Delta Kompakt</t>
+          <t>Yedek Parça Servis Paketi</t>
         </is>
       </c>
       <c r="C27" s="2" t="n">
         <v>45708</v>
       </c>
       <c r="D27" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E27" t="n">
-        <v>1200</v>
+        <v>2400</v>
       </c>
       <c r="F27" t="n">
-        <v>59483.03</v>
+        <v>123461.29</v>
       </c>
       <c r="G27" t="n">
-        <v>1784.49</v>
+        <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>57698.54</v>
+        <v>77163.31</v>
       </c>
       <c r="I27" t="n">
-        <v>40646.74</v>
+        <v>123461.29</v>
       </c>
       <c r="J27" t="n">
-        <v>57698.54</v>
+        <v>123461.29</v>
       </c>
       <c r="K27" t="n">
         <v>0</v>
@@ -1506,37 +1506,37 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Adana Bölge Bayi A.Ş.</t>
+          <t>Marmara Perakende Çözümleri</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Ürün Zeta Hızlı Tüketim</t>
+          <t>Ürün Delta Kompakt</t>
         </is>
       </c>
       <c r="C28" s="2" t="n">
         <v>45710</v>
       </c>
       <c r="D28" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="E28" t="n">
-        <v>650</v>
+        <v>1200</v>
       </c>
       <c r="F28" t="n">
-        <v>41885.97</v>
+        <v>97740.19</v>
       </c>
       <c r="G28" t="n">
-        <v>5026.32</v>
+        <v>2100.83</v>
       </c>
       <c r="H28" t="n">
-        <v>36859.65</v>
+        <v>66789.13</v>
       </c>
       <c r="I28" t="n">
-        <v>28353.58</v>
+        <v>95639.36</v>
       </c>
       <c r="J28" t="n">
-        <v>36859.65</v>
+        <v>95639.36</v>
       </c>
       <c r="K28" t="n">
         <v>0</v>
@@ -1545,7 +1545,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Adana Bölge Bayi A.Ş.</t>
+          <t>Kocaeli Ağır Sanayi Pazarlama</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1557,25 +1557,25 @@
         <v>45712</v>
       </c>
       <c r="D29" t="n">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="E29" t="n">
         <v>650</v>
       </c>
       <c r="F29" t="n">
-        <v>35441.97</v>
+        <v>52942.6</v>
       </c>
       <c r="G29" t="n">
-        <v>1772.1</v>
+        <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>33669.87</v>
+        <v>35838.07</v>
       </c>
       <c r="I29" t="n">
-        <v>23991.49</v>
+        <v>52942.6</v>
       </c>
       <c r="J29" t="n">
-        <v>33669.87</v>
+        <v>52942.6</v>
       </c>
       <c r="K29" t="n">
         <v>0</v>
@@ -1584,37 +1584,37 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Karadeniz Toptan Dağıtım A.Ş.</t>
+          <t>Bursa İmalat Tedarik Ltd.</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Ürün Delta Kompakt</t>
+          <t>Ürün Zeta Hızlı Tüketim</t>
         </is>
       </c>
       <c r="C30" s="2" t="n">
         <v>45714</v>
       </c>
       <c r="D30" t="n">
-        <v>3</v>
+        <v>19</v>
       </c>
       <c r="E30" t="n">
-        <v>1200</v>
+        <v>650</v>
       </c>
       <c r="F30" t="n">
-        <v>17844.91</v>
+        <v>52942.6</v>
       </c>
       <c r="G30" t="n">
-        <v>0</v>
+        <v>2844.87</v>
       </c>
       <c r="H30" t="n">
-        <v>17844.91</v>
+        <v>35838.07</v>
       </c>
       <c r="I30" t="n">
-        <v>12194.02</v>
+        <v>50097.73</v>
       </c>
       <c r="J30" t="n">
-        <v>17844.91</v>
+        <v>50097.73</v>
       </c>
       <c r="K30" t="n">
         <v>0</v>
@@ -1628,32 +1628,32 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Ürün Beta Premium</t>
+          <t>Ürün Delta Kompakt</t>
         </is>
       </c>
       <c r="C31" s="2" t="n">
         <v>45716</v>
       </c>
       <c r="D31" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="E31" t="n">
-        <v>4200</v>
+        <v>1200</v>
       </c>
       <c r="F31" t="n">
-        <v>104095.3</v>
+        <v>82307.53</v>
       </c>
       <c r="G31" t="n">
-        <v>0</v>
+        <v>4422.8</v>
       </c>
       <c r="H31" t="n">
-        <v>104095.3</v>
+        <v>56243.48</v>
       </c>
       <c r="I31" t="n">
-        <v>69396.87</v>
+        <v>77884.73</v>
       </c>
       <c r="J31" t="n">
-        <v>104095.3</v>
+        <v>77884.73</v>
       </c>
       <c r="K31" t="n">
         <v>0</v>
@@ -1662,37 +1662,37 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Marmara Perakende Çözümleri</t>
+          <t>Karadeniz Toptan Dağıtım A.Ş.</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Özel Sipariş Modeli X</t>
+          <t>Ürün Gamma Endüstriyel</t>
         </is>
       </c>
       <c r="C32" s="2" t="n">
         <v>45718</v>
       </c>
       <c r="D32" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E32" t="n">
-        <v>21500</v>
+        <v>8900</v>
       </c>
       <c r="F32" t="n">
-        <v>1598606.39</v>
+        <v>610447.5</v>
       </c>
       <c r="G32" t="n">
-        <v>47958.19</v>
+        <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>1550648.2</v>
+        <v>404678.68</v>
       </c>
       <c r="I32" t="n">
-        <v>1055823.75</v>
+        <v>610447.5</v>
       </c>
       <c r="J32" t="n">
-        <v>1550648.2</v>
+        <v>610447.5</v>
       </c>
       <c r="K32" t="n">
         <v>0</v>
@@ -1701,37 +1701,37 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Akdeniz Endüstriyel Ürünler</t>
+          <t>Ege Dağıtım ve Ticaret Ltd.</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Ürün Beta Premium</t>
+          <t>Ürün Alpha Standart</t>
         </is>
       </c>
       <c r="C33" s="2" t="n">
         <v>45720</v>
       </c>
       <c r="D33" t="n">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="E33" t="n">
-        <v>4200</v>
+        <v>1850</v>
       </c>
       <c r="F33" t="n">
-        <v>374743.08</v>
+        <v>63445.39</v>
       </c>
       <c r="G33" t="n">
-        <v>11242.29</v>
+        <v>3409.24</v>
       </c>
       <c r="H33" t="n">
-        <v>363500.79</v>
+        <v>42868.5</v>
       </c>
       <c r="I33" t="n">
-        <v>249828.72</v>
+        <v>60036.15</v>
       </c>
       <c r="J33" t="n">
-        <v>363500.79</v>
+        <v>60036.15</v>
       </c>
       <c r="K33" t="n">
         <v>0</v>
@@ -1740,37 +1740,37 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Kocaeli Ağır Sanayi Pazarlama</t>
+          <t>Toroslar Lojistik ve Ticaret</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Ürün Delta Kompakt</t>
+          <t>Ürün Alpha Standart</t>
         </is>
       </c>
       <c r="C34" s="2" t="n">
         <v>45722</v>
       </c>
       <c r="D34" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E34" t="n">
-        <v>1200</v>
+        <v>1850</v>
       </c>
       <c r="F34" t="n">
-        <v>89224.53999999999</v>
+        <v>134821.45</v>
       </c>
       <c r="G34" t="n">
-        <v>2676.74</v>
+        <v>4346.78</v>
       </c>
       <c r="H34" t="n">
-        <v>86547.81</v>
+        <v>91095.57000000001</v>
       </c>
       <c r="I34" t="n">
-        <v>60970.1</v>
+        <v>130474.67</v>
       </c>
       <c r="J34" t="n">
-        <v>86547.81</v>
+        <v>130474.67</v>
       </c>
       <c r="K34" t="n">
         <v>0</v>
@@ -1779,37 +1779,37 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Güneydoğu Pazarlama Ltd.</t>
+          <t>Anadolu Sanayi Grubu A.Ş.</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Ürün Epsilon Profesyonel</t>
+          <t>Ürün Zeta Hızlı Tüketim</t>
         </is>
       </c>
       <c r="C35" s="2" t="n">
         <v>45724</v>
       </c>
       <c r="D35" t="n">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="E35" t="n">
-        <v>15400</v>
+        <v>650</v>
       </c>
       <c r="F35" t="n">
-        <v>305346.21</v>
+        <v>55729.06</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>305346.21</v>
+        <v>37724.28</v>
       </c>
       <c r="I35" t="n">
-        <v>194311.23</v>
+        <v>55729.06</v>
       </c>
       <c r="J35" t="n">
-        <v>305346.21</v>
+        <v>55729.06</v>
       </c>
       <c r="K35" t="n">
         <v>0</v>
@@ -1818,37 +1818,37 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Marmara Perakende Çözümleri</t>
+          <t>Kocaeli Ağır Sanayi Pazarlama</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Ürün Epsilon Profesyonel</t>
+          <t>Ürün Gamma Endüstriyel</t>
         </is>
       </c>
       <c r="C36" s="2" t="n">
         <v>45726</v>
       </c>
       <c r="D36" t="n">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="E36" t="n">
-        <v>15400</v>
+        <v>8900</v>
       </c>
       <c r="F36" t="n">
-        <v>1755740.72</v>
+        <v>419682.66</v>
       </c>
       <c r="G36" t="n">
-        <v>210688.89</v>
+        <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>1545051.84</v>
+        <v>278216.59</v>
       </c>
       <c r="I36" t="n">
-        <v>1117289.55</v>
+        <v>419682.66</v>
       </c>
       <c r="J36" t="n">
-        <v>1545051.84</v>
+        <v>419682.66</v>
       </c>
       <c r="K36" t="n">
         <v>0</v>
@@ -1857,37 +1857,37 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Ankara Proje Yönetim ve Satış</t>
+          <t>Gaziantep İhracat ve Toptan</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Ürün Alpha Standart</t>
+          <t>Ürün Zeta Hızlı Tüketim</t>
         </is>
       </c>
       <c r="C37" s="2" t="n">
         <v>45728</v>
       </c>
       <c r="D37" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="E37" t="n">
-        <v>1850</v>
+        <v>650</v>
       </c>
       <c r="F37" t="n">
-        <v>64192.1</v>
+        <v>5572.91</v>
       </c>
       <c r="G37" t="n">
-        <v>1925.76</v>
+        <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>62266.34</v>
+        <v>3772.43</v>
       </c>
       <c r="I37" t="n">
-        <v>43373.04</v>
+        <v>5572.91</v>
       </c>
       <c r="J37" t="n">
-        <v>62266.34</v>
+        <v>5572.91</v>
       </c>
       <c r="K37" t="n">
         <v>0</v>
@@ -1901,32 +1901,32 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Ürün Beta Premium</t>
+          <t>Ürün Gamma Endüstriyel</t>
         </is>
       </c>
       <c r="C38" s="2" t="n">
         <v>45730</v>
       </c>
       <c r="D38" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="E38" t="n">
-        <v>4200</v>
+        <v>8900</v>
       </c>
       <c r="F38" t="n">
-        <v>478838.38</v>
+        <v>953824.22</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>478838.38</v>
+        <v>632310.4399999999</v>
       </c>
       <c r="I38" t="n">
-        <v>319225.59</v>
+        <v>953824.22</v>
       </c>
       <c r="J38" t="n">
-        <v>478838.38</v>
+        <v>953824.22</v>
       </c>
       <c r="K38" t="n">
         <v>0</v>
@@ -1935,37 +1935,37 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>İç Anadolu Tüketim Malları</t>
+          <t>Adana Bölge Bayi A.Ş.</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Yedek Parça Servis Paketi</t>
+          <t>Ürün Zeta Hızlı Tüketim</t>
         </is>
       </c>
       <c r="C39" s="2" t="n">
         <v>45732</v>
       </c>
       <c r="D39" t="n">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="E39" t="n">
-        <v>2400</v>
+        <v>650</v>
       </c>
       <c r="F39" t="n">
-        <v>202242.3</v>
+        <v>8359.360000000001</v>
       </c>
       <c r="G39" t="n">
-        <v>0</v>
+        <v>179.68</v>
       </c>
       <c r="H39" t="n">
-        <v>202242.3</v>
+        <v>5658.64</v>
       </c>
       <c r="I39" t="n">
-        <v>126401.44</v>
+        <v>8179.68</v>
       </c>
       <c r="J39" t="n">
-        <v>202242.3</v>
+        <v>8179.68</v>
       </c>
       <c r="K39" t="n">
         <v>0</v>
@@ -1974,37 +1974,37 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>İzmir Ticari Faaliyetler A.Ş.</t>
+          <t>Bursa İmalat Tedarik Ltd.</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Ürün Epsilon Profesyonel</t>
+          <t>Yedek Parça Servis Paketi</t>
         </is>
       </c>
       <c r="C40" s="2" t="n">
         <v>45734</v>
       </c>
       <c r="D40" t="n">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="E40" t="n">
-        <v>15400</v>
+        <v>2400</v>
       </c>
       <c r="F40" t="n">
-        <v>687028.98</v>
+        <v>195480.38</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>687028.98</v>
+        <v>122175.24</v>
       </c>
       <c r="I40" t="n">
-        <v>437200.26</v>
+        <v>195480.38</v>
       </c>
       <c r="J40" t="n">
-        <v>687028.98</v>
+        <v>195480.38</v>
       </c>
       <c r="K40" t="n">
         <v>0</v>
@@ -2013,37 +2013,37 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Anadolu Sanayi Grubu A.Ş.</t>
+          <t>İç Anadolu Tüketim Malları</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Yedek Parça Servis Paketi</t>
+          <t>Ürün Epsilon Profesyonel</t>
         </is>
       </c>
       <c r="C41" s="2" t="n">
         <v>45736</v>
       </c>
       <c r="D41" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="E41" t="n">
-        <v>2400</v>
+        <v>15400</v>
       </c>
       <c r="F41" t="n">
-        <v>178449.09</v>
+        <v>726192.46</v>
       </c>
       <c r="G41" t="n">
-        <v>14275.93</v>
+        <v>0</v>
       </c>
       <c r="H41" t="n">
-        <v>164173.16</v>
+        <v>462122.48</v>
       </c>
       <c r="I41" t="n">
-        <v>111530.68</v>
+        <v>726192.46</v>
       </c>
       <c r="J41" t="n">
-        <v>164173.16</v>
+        <v>726192.46</v>
       </c>
       <c r="K41" t="n">
         <v>0</v>
@@ -2052,37 +2052,37 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Bursa İmalat Tedarik Ltd.</t>
+          <t>Marmara Perakende Çözümleri</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Ürün Delta Kompakt</t>
+          <t>Yedek Parça Servis Paketi</t>
         </is>
       </c>
       <c r="C42" s="2" t="n">
         <v>45738</v>
       </c>
       <c r="D42" t="n">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="E42" t="n">
-        <v>1200</v>
+        <v>2400</v>
       </c>
       <c r="F42" t="n">
-        <v>23793.21</v>
+        <v>216057.26</v>
       </c>
       <c r="G42" t="n">
-        <v>1189.66</v>
+        <v>6965.9</v>
       </c>
       <c r="H42" t="n">
-        <v>22603.55</v>
+        <v>135035.79</v>
       </c>
       <c r="I42" t="n">
-        <v>16258.69</v>
+        <v>209091.36</v>
       </c>
       <c r="J42" t="n">
-        <v>22603.55</v>
+        <v>209091.36</v>
       </c>
       <c r="K42" t="n">
         <v>0</v>
@@ -2091,37 +2091,37 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Ege Dağıtım ve Ticaret Ltd.</t>
+          <t>İzmir Ticari Faaliyetler A.Ş.</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Ürün Gamma Endüstriyel</t>
+          <t>Ürün Zeta Hızlı Tüketim</t>
         </is>
       </c>
       <c r="C43" s="2" t="n">
         <v>45740</v>
       </c>
       <c r="D43" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E43" t="n">
-        <v>8900</v>
+        <v>650</v>
       </c>
       <c r="F43" t="n">
-        <v>176466.32</v>
+        <v>16718.72</v>
       </c>
       <c r="G43" t="n">
-        <v>0</v>
+        <v>898.38</v>
       </c>
       <c r="H43" t="n">
-        <v>176466.32</v>
+        <v>11317.29</v>
       </c>
       <c r="I43" t="n">
-        <v>116983.29</v>
+        <v>15820.34</v>
       </c>
       <c r="J43" t="n">
-        <v>176466.32</v>
+        <v>15820.34</v>
       </c>
       <c r="K43" t="n">
         <v>0</v>
@@ -2130,37 +2130,37 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Anadolu Sanayi Grubu A.Ş.</t>
+          <t>Bursa İmalat Tedarik Ltd.</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Ürün Delta Kompakt</t>
+          <t>Ürün Zeta Hızlı Tüketim</t>
         </is>
       </c>
       <c r="C44" s="2" t="n">
         <v>45742</v>
       </c>
       <c r="D44" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E44" t="n">
-        <v>1200</v>
+        <v>650</v>
       </c>
       <c r="F44" t="n">
-        <v>29741.51</v>
+        <v>22291.62</v>
       </c>
       <c r="G44" t="n">
-        <v>0</v>
+        <v>1197.84</v>
       </c>
       <c r="H44" t="n">
-        <v>29741.51</v>
+        <v>15089.71</v>
       </c>
       <c r="I44" t="n">
-        <v>20323.37</v>
+        <v>21093.78</v>
       </c>
       <c r="J44" t="n">
-        <v>29741.51</v>
+        <v>21093.78</v>
       </c>
       <c r="K44" t="n">
         <v>0</v>
@@ -2174,32 +2174,32 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Yedek Parça Servis Paketi</t>
+          <t>Ürün Gamma Endüstriyel</t>
         </is>
       </c>
       <c r="C45" s="2" t="n">
         <v>45744</v>
       </c>
       <c r="D45" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E45" t="n">
-        <v>2400</v>
+        <v>8900</v>
       </c>
       <c r="F45" t="n">
-        <v>142759.27</v>
+        <v>495988.59</v>
       </c>
       <c r="G45" t="n">
-        <v>17131.11</v>
+        <v>10660.78</v>
       </c>
       <c r="H45" t="n">
-        <v>125628.16</v>
+        <v>328801.43</v>
       </c>
       <c r="I45" t="n">
-        <v>89224.53999999999</v>
+        <v>485327.81</v>
       </c>
       <c r="J45" t="n">
-        <v>125628.16</v>
+        <v>485327.81</v>
       </c>
       <c r="K45" t="n">
         <v>0</v>
@@ -2208,37 +2208,37 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>İzmir Ticari Faaliyetler A.Ş.</t>
+          <t>Bursa İmalat Tedarik Ltd.</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Ürün Beta Premium</t>
+          <t>Ürün Epsilon Profesyonel</t>
         </is>
       </c>
       <c r="C46" s="2" t="n">
         <v>45746</v>
       </c>
       <c r="D46" t="n">
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="E46" t="n">
-        <v>4200</v>
+        <v>15400</v>
       </c>
       <c r="F46" t="n">
-        <v>395562.14</v>
+        <v>330087.48</v>
       </c>
       <c r="G46" t="n">
-        <v>31644.97</v>
+        <v>0</v>
       </c>
       <c r="H46" t="n">
-        <v>363917.17</v>
+        <v>210055.67</v>
       </c>
       <c r="I46" t="n">
-        <v>263708.09</v>
+        <v>330087.48</v>
       </c>
       <c r="J46" t="n">
-        <v>363917.17</v>
+        <v>330087.48</v>
       </c>
       <c r="K46" t="n">
         <v>0</v>
@@ -2247,37 +2247,37 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Karadeniz Toptan Dağıtım A.Ş.</t>
+          <t>Bursa İmalat Tedarik Ltd.</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Ürün Beta Premium</t>
+          <t>Ürün Alpha Standart</t>
         </is>
       </c>
       <c r="C47" s="2" t="n">
         <v>45749</v>
       </c>
       <c r="D47" t="n">
-        <v>1</v>
+        <v>23</v>
       </c>
       <c r="E47" t="n">
-        <v>4200</v>
+        <v>1850</v>
       </c>
       <c r="F47" t="n">
-        <v>20819.06</v>
+        <v>182405.49</v>
       </c>
       <c r="G47" t="n">
-        <v>0</v>
+        <v>9801.559999999999</v>
       </c>
       <c r="H47" t="n">
-        <v>20819.06</v>
+        <v>123246.95</v>
       </c>
       <c r="I47" t="n">
-        <v>13879.37</v>
+        <v>172603.93</v>
       </c>
       <c r="J47" t="n">
-        <v>20819.06</v>
+        <v>172603.93</v>
       </c>
       <c r="K47" t="n">
         <v>0</v>
@@ -2286,37 +2286,37 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Toroslar Lojistik ve Ticaret</t>
+          <t>Akdeniz Endüstriyel Ürünler</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Özel Sipariş Modeli X</t>
+          <t>Ürün Alpha Standart</t>
         </is>
       </c>
       <c r="C48" s="2" t="n">
         <v>45751</v>
       </c>
       <c r="D48" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E48" t="n">
-        <v>21500</v>
+        <v>1850</v>
       </c>
       <c r="F48" t="n">
-        <v>532868.8</v>
+        <v>47584.04</v>
       </c>
       <c r="G48" t="n">
-        <v>0</v>
+        <v>2556.93</v>
       </c>
       <c r="H48" t="n">
-        <v>532868.8</v>
+        <v>32151.38</v>
       </c>
       <c r="I48" t="n">
-        <v>351941.25</v>
+        <v>45027.11</v>
       </c>
       <c r="J48" t="n">
-        <v>532868.8</v>
+        <v>45027.11</v>
       </c>
       <c r="K48" t="n">
         <v>0</v>
@@ -2325,37 +2325,37 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Gaziantep İhracat ve Toptan</t>
+          <t>İç Anadolu Tüketim Malları</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Ürün Zeta Hızlı Tüketim</t>
+          <t>Ürün Delta Kompakt</t>
         </is>
       </c>
       <c r="C49" s="2" t="n">
         <v>45753</v>
       </c>
       <c r="D49" t="n">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="E49" t="n">
-        <v>650</v>
+        <v>1200</v>
       </c>
       <c r="F49" t="n">
-        <v>12887.99</v>
+        <v>108028.63</v>
       </c>
       <c r="G49" t="n">
-        <v>0</v>
+        <v>5804.92</v>
       </c>
       <c r="H49" t="n">
-        <v>12887.99</v>
+        <v>73819.56</v>
       </c>
       <c r="I49" t="n">
-        <v>8724.18</v>
+        <v>102223.71</v>
       </c>
       <c r="J49" t="n">
-        <v>12887.99</v>
+        <v>102223.71</v>
       </c>
       <c r="K49" t="n">
         <v>0</v>
@@ -2364,37 +2364,37 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Güneydoğu Pazarlama Ltd.</t>
+          <t>Ege Dağıtım ve Ticaret Ltd.</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Ürün Alpha Standart</t>
+          <t>Özel Sipariş Modeli X</t>
         </is>
       </c>
       <c r="C50" s="2" t="n">
         <v>45755</v>
       </c>
       <c r="D50" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E50" t="n">
-        <v>1850</v>
+        <v>21500</v>
       </c>
       <c r="F50" t="n">
-        <v>55021.8</v>
+        <v>460836.42</v>
       </c>
       <c r="G50" t="n">
-        <v>4401.74</v>
+        <v>9905.219999999999</v>
       </c>
       <c r="H50" t="n">
-        <v>50620.06</v>
+        <v>304366.38</v>
       </c>
       <c r="I50" t="n">
-        <v>37176.89</v>
+        <v>450931.2</v>
       </c>
       <c r="J50" t="n">
-        <v>50620.06</v>
+        <v>450931.2</v>
       </c>
       <c r="K50" t="n">
         <v>0</v>
@@ -2403,37 +2403,37 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Akdeniz Endüstriyel Ürünler</t>
+          <t>Bursa İmalat Tedarik Ltd.</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Yedek Parça Servis Paketi</t>
+          <t>Ürün Beta Premium</t>
         </is>
       </c>
       <c r="C51" s="2" t="n">
         <v>45757</v>
       </c>
       <c r="D51" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="E51" t="n">
-        <v>2400</v>
+        <v>4200</v>
       </c>
       <c r="F51" t="n">
-        <v>190345.69</v>
+        <v>144038.17</v>
       </c>
       <c r="G51" t="n">
-        <v>0</v>
+        <v>3095.96</v>
       </c>
       <c r="H51" t="n">
-        <v>190345.69</v>
+        <v>96025.45</v>
       </c>
       <c r="I51" t="n">
-        <v>118966.06</v>
+        <v>140942.21</v>
       </c>
       <c r="J51" t="n">
-        <v>190345.69</v>
+        <v>140942.21</v>
       </c>
       <c r="K51" t="n">
         <v>0</v>
@@ -2442,37 +2442,37 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Akdeniz Endüstriyel Ürünler</t>
+          <t>İç Anadolu Tüketim Malları</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Yedek Parça Servis Paketi</t>
+          <t>Ürün Gamma Endüstriyel</t>
         </is>
       </c>
       <c r="C52" s="2" t="n">
         <v>45759</v>
       </c>
       <c r="D52" t="n">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="E52" t="n">
-        <v>2400</v>
+        <v>8900</v>
       </c>
       <c r="F52" t="n">
-        <v>71379.63</v>
+        <v>801212.34</v>
       </c>
       <c r="G52" t="n">
-        <v>2141.39</v>
+        <v>0</v>
       </c>
       <c r="H52" t="n">
-        <v>69238.25</v>
+        <v>531140.77</v>
       </c>
       <c r="I52" t="n">
-        <v>44612.27</v>
+        <v>801212.34</v>
       </c>
       <c r="J52" t="n">
-        <v>69238.25</v>
+        <v>801212.34</v>
       </c>
       <c r="K52" t="n">
         <v>0</v>
@@ -2481,37 +2481,37 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Toroslar Lojistik ve Ticaret</t>
+          <t>Adana Bölge Bayi A.Ş.</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Ürün Gamma Endüstriyel</t>
+          <t>Ürün Zeta Hızlı Tüketim</t>
         </is>
       </c>
       <c r="C53" s="2" t="n">
         <v>45761</v>
       </c>
       <c r="D53" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="E53" t="n">
-        <v>8900</v>
+        <v>650</v>
       </c>
       <c r="F53" t="n">
-        <v>397049.21</v>
+        <v>41796.79</v>
       </c>
       <c r="G53" t="n">
-        <v>11911.48</v>
+        <v>0</v>
       </c>
       <c r="H53" t="n">
-        <v>385137.74</v>
+        <v>28293.21</v>
       </c>
       <c r="I53" t="n">
-        <v>263212.4</v>
+        <v>41796.79</v>
       </c>
       <c r="J53" t="n">
-        <v>385137.74</v>
+        <v>41796.79</v>
       </c>
       <c r="K53" t="n">
         <v>0</v>
@@ -2520,37 +2520,37 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Güneydoğu Pazarlama Ltd.</t>
+          <t>Karadeniz Toptan Dağıtım A.Ş.</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Ürün Gamma Endüstriyel</t>
+          <t>Ürün Delta Kompakt</t>
         </is>
       </c>
       <c r="C54" s="2" t="n">
         <v>45763</v>
       </c>
       <c r="D54" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="E54" t="n">
-        <v>8900</v>
+        <v>1200</v>
       </c>
       <c r="F54" t="n">
-        <v>88233.16</v>
+        <v>41153.76</v>
       </c>
       <c r="G54" t="n">
-        <v>7058.65</v>
+        <v>0</v>
       </c>
       <c r="H54" t="n">
-        <v>81174.50999999999</v>
+        <v>28121.74</v>
       </c>
       <c r="I54" t="n">
-        <v>58491.64</v>
+        <v>41153.76</v>
       </c>
       <c r="J54" t="n">
-        <v>81174.50999999999</v>
+        <v>41153.76</v>
       </c>
       <c r="K54" t="n">
         <v>0</v>
@@ -2559,37 +2559,37 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Ankara Proje Yönetim ve Satış</t>
+          <t>İç Anadolu Tüketim Malları</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Ürün Delta Kompakt</t>
+          <t>Ürün Epsilon Profesyonel</t>
         </is>
       </c>
       <c r="C55" s="2" t="n">
         <v>45765</v>
       </c>
       <c r="D55" t="n">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="E55" t="n">
-        <v>1200</v>
+        <v>15400</v>
       </c>
       <c r="F55" t="n">
-        <v>124914.36</v>
+        <v>264069.99</v>
       </c>
       <c r="G55" t="n">
-        <v>3747.43</v>
+        <v>0</v>
       </c>
       <c r="H55" t="n">
-        <v>121166.93</v>
+        <v>168044.54</v>
       </c>
       <c r="I55" t="n">
-        <v>85358.14999999999</v>
+        <v>264069.99</v>
       </c>
       <c r="J55" t="n">
-        <v>121166.93</v>
+        <v>264069.99</v>
       </c>
       <c r="K55" t="n">
         <v>0</v>
@@ -2598,7 +2598,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Güneydoğu Pazarlama Ltd.</t>
+          <t>Anadolu Sanayi Grubu A.Ş.</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -2610,25 +2610,25 @@
         <v>45767</v>
       </c>
       <c r="D56" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="E56" t="n">
         <v>2400</v>
       </c>
       <c r="F56" t="n">
-        <v>214138.9</v>
+        <v>154326.62</v>
       </c>
       <c r="G56" t="n">
-        <v>10706.95</v>
+        <v>4975.64</v>
       </c>
       <c r="H56" t="n">
-        <v>203431.96</v>
+        <v>96454.13</v>
       </c>
       <c r="I56" t="n">
-        <v>133836.81</v>
+        <v>149350.98</v>
       </c>
       <c r="J56" t="n">
-        <v>203431.96</v>
+        <v>149350.98</v>
       </c>
       <c r="K56" t="n">
         <v>0</v>
@@ -2637,37 +2637,37 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Anadolu Sanayi Grubu A.Ş.</t>
+          <t>Marmara Perakende Çözümleri</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Ürün Beta Premium</t>
+          <t>Yedek Parça Servis Paketi</t>
         </is>
       </c>
       <c r="C57" s="2" t="n">
         <v>45769</v>
       </c>
       <c r="D57" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="E57" t="n">
-        <v>4200</v>
+        <v>2400</v>
       </c>
       <c r="F57" t="n">
-        <v>187371.54</v>
+        <v>164615.06</v>
       </c>
       <c r="G57" t="n">
-        <v>9368.58</v>
+        <v>5307.35</v>
       </c>
       <c r="H57" t="n">
-        <v>178002.96</v>
+        <v>102884.41</v>
       </c>
       <c r="I57" t="n">
-        <v>124914.36</v>
+        <v>159307.71</v>
       </c>
       <c r="J57" t="n">
-        <v>178002.96</v>
+        <v>159307.71</v>
       </c>
       <c r="K57" t="n">
         <v>0</v>
@@ -2676,7 +2676,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Marmara Perakende Çözümleri</t>
+          <t>İç Anadolu Tüketim Malları</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -2688,25 +2688,25 @@
         <v>45771</v>
       </c>
       <c r="D58" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E58" t="n">
         <v>2400</v>
       </c>
       <c r="F58" t="n">
-        <v>83276.24000000001</v>
+        <v>41153.76</v>
       </c>
       <c r="G58" t="n">
-        <v>9993.15</v>
+        <v>1326.84</v>
       </c>
       <c r="H58" t="n">
-        <v>73283.09</v>
+        <v>25721.1</v>
       </c>
       <c r="I58" t="n">
-        <v>52047.65</v>
+        <v>39826.92</v>
       </c>
       <c r="J58" t="n">
-        <v>73283.09</v>
+        <v>39826.92</v>
       </c>
       <c r="K58" t="n">
         <v>0</v>
@@ -2715,7 +2715,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Gaziantep İhracat ve Toptan</t>
+          <t>Kocaeli Ağır Sanayi Pazarlama</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2727,25 +2727,25 @@
         <v>45773</v>
       </c>
       <c r="D59" t="n">
-        <v>21</v>
+        <v>6</v>
       </c>
       <c r="E59" t="n">
         <v>1200</v>
       </c>
       <c r="F59" t="n">
-        <v>124914.36</v>
+        <v>30865.32</v>
       </c>
       <c r="G59" t="n">
-        <v>9993.15</v>
+        <v>995.13</v>
       </c>
       <c r="H59" t="n">
-        <v>114921.21</v>
+        <v>21091.3</v>
       </c>
       <c r="I59" t="n">
-        <v>85358.14999999999</v>
+        <v>29870.19</v>
       </c>
       <c r="J59" t="n">
-        <v>114921.21</v>
+        <v>29870.19</v>
       </c>
       <c r="K59" t="n">
         <v>0</v>
@@ -2754,7 +2754,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Kocaeli Ağır Sanayi Pazarlama</t>
+          <t>Ege Dağıtım ve Ticaret Ltd.</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -2766,25 +2766,25 @@
         <v>45775</v>
       </c>
       <c r="D60" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="E60" t="n">
         <v>1850</v>
       </c>
       <c r="F60" t="n">
-        <v>119213.9</v>
+        <v>79306.73</v>
       </c>
       <c r="G60" t="n">
-        <v>14305.67</v>
+        <v>0</v>
       </c>
       <c r="H60" t="n">
-        <v>104908.23</v>
+        <v>53585.63</v>
       </c>
       <c r="I60" t="n">
-        <v>80549.92999999999</v>
+        <v>79306.73</v>
       </c>
       <c r="J60" t="n">
-        <v>104908.23</v>
+        <v>79306.73</v>
       </c>
       <c r="K60" t="n">
         <v>0</v>
@@ -2798,32 +2798,32 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Özel Sipariş Modeli X</t>
+          <t>Ürün Epsilon Profesyonel</t>
         </is>
       </c>
       <c r="C61" s="2" t="n">
         <v>45777</v>
       </c>
       <c r="D61" t="n">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="E61" t="n">
-        <v>21500</v>
+        <v>15400</v>
       </c>
       <c r="F61" t="n">
-        <v>1918327.67</v>
+        <v>264069.99</v>
       </c>
       <c r="G61" t="n">
-        <v>95916.38</v>
+        <v>0</v>
       </c>
       <c r="H61" t="n">
-        <v>1822411.28</v>
+        <v>168044.54</v>
       </c>
       <c r="I61" t="n">
-        <v>1266988.51</v>
+        <v>264069.99</v>
       </c>
       <c r="J61" t="n">
-        <v>1822411.28</v>
+        <v>264069.99</v>
       </c>
       <c r="K61" t="n">
         <v>0</v>
@@ -2837,7 +2837,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Ürün Zeta Hızlı Tüketim</t>
+          <t>Ürün Gamma Endüstriyel</t>
         </is>
       </c>
       <c r="C62" s="2" t="n">
@@ -2847,22 +2847,22 @@
         <v>13</v>
       </c>
       <c r="E62" t="n">
-        <v>650</v>
+        <v>8900</v>
       </c>
       <c r="F62" t="n">
-        <v>41885.97</v>
+        <v>495988.59</v>
       </c>
       <c r="G62" t="n">
-        <v>1256.58</v>
+        <v>0</v>
       </c>
       <c r="H62" t="n">
-        <v>40629.39</v>
+        <v>328801.43</v>
       </c>
       <c r="I62" t="n">
-        <v>28353.58</v>
+        <v>495988.59</v>
       </c>
       <c r="J62" t="n">
-        <v>40629.39</v>
+        <v>495988.59</v>
       </c>
       <c r="K62" t="n">
         <v>0</v>
@@ -2871,37 +2871,37 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Marmara Perakende Çözümleri</t>
+          <t>Bursa İmalat Tedarik Ltd.</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Ürün Alpha Standart</t>
+          <t>Ürün Beta Premium</t>
         </is>
       </c>
       <c r="C63" s="2" t="n">
         <v>45781</v>
       </c>
       <c r="D63" t="n">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="E63" t="n">
-        <v>1850</v>
+        <v>4200</v>
       </c>
       <c r="F63" t="n">
-        <v>100873.3</v>
+        <v>324085.89</v>
       </c>
       <c r="G63" t="n">
-        <v>8069.86</v>
+        <v>0</v>
       </c>
       <c r="H63" t="n">
-        <v>92803.44</v>
+        <v>216057.26</v>
       </c>
       <c r="I63" t="n">
-        <v>68157.64</v>
+        <v>324085.89</v>
       </c>
       <c r="J63" t="n">
-        <v>92803.44</v>
+        <v>324085.89</v>
       </c>
       <c r="K63" t="n">
         <v>0</v>
@@ -2910,37 +2910,37 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Toroslar Lojistik ve Ticaret</t>
+          <t>İç Anadolu Tüketim Malları</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Ürün Alpha Standart</t>
+          <t>Özel Sipariş Modeli X</t>
         </is>
       </c>
       <c r="C64" s="2" t="n">
         <v>45783</v>
       </c>
       <c r="D64" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="E64" t="n">
-        <v>1850</v>
+        <v>21500</v>
       </c>
       <c r="F64" t="n">
-        <v>229257.51</v>
+        <v>2119847.54</v>
       </c>
       <c r="G64" t="n">
-        <v>6877.73</v>
+        <v>0</v>
       </c>
       <c r="H64" t="n">
-        <v>222379.78</v>
+        <v>1400085.35</v>
       </c>
       <c r="I64" t="n">
-        <v>154903.72</v>
+        <v>2119847.54</v>
       </c>
       <c r="J64" t="n">
-        <v>222379.78</v>
+        <v>2119847.54</v>
       </c>
       <c r="K64" t="n">
         <v>0</v>
@@ -2949,37 +2949,37 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Anadolu Sanayi Grubu A.Ş.</t>
+          <t>Akdeniz Endüstriyel Ürünler</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Özel Sipariş Modeli X</t>
+          <t>Ürün Gamma Endüstriyel</t>
         </is>
       </c>
       <c r="C65" s="2" t="n">
         <v>45785</v>
       </c>
       <c r="D65" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="E65" t="n">
-        <v>21500</v>
+        <v>8900</v>
       </c>
       <c r="F65" t="n">
-        <v>1811753.91</v>
+        <v>763059.38</v>
       </c>
       <c r="G65" t="n">
-        <v>54352.62</v>
+        <v>24601.8</v>
       </c>
       <c r="H65" t="n">
-        <v>1757401.29</v>
+        <v>505848.35</v>
       </c>
       <c r="I65" t="n">
-        <v>1196600.26</v>
+        <v>738457.58</v>
       </c>
       <c r="J65" t="n">
-        <v>1757401.29</v>
+        <v>738457.58</v>
       </c>
       <c r="K65" t="n">
         <v>0</v>
@@ -2988,37 +2988,37 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Kocaeli Ağır Sanayi Pazarlama</t>
+          <t>Marmara Perakende Çözümleri</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Ürün Delta Kompakt</t>
+          <t>Ürün Alpha Standart</t>
         </is>
       </c>
       <c r="C66" s="2" t="n">
         <v>45787</v>
       </c>
       <c r="D66" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E66" t="n">
-        <v>1200</v>
+        <v>1850</v>
       </c>
       <c r="F66" t="n">
-        <v>35689.82</v>
+        <v>31722.69</v>
       </c>
       <c r="G66" t="n">
-        <v>0</v>
+        <v>681.85</v>
       </c>
       <c r="H66" t="n">
-        <v>35689.82</v>
+        <v>21434.25</v>
       </c>
       <c r="I66" t="n">
-        <v>24388.04</v>
+        <v>31040.84</v>
       </c>
       <c r="J66" t="n">
-        <v>35689.82</v>
+        <v>31040.84</v>
       </c>
       <c r="K66" t="n">
         <v>0</v>
@@ -3039,25 +3039,25 @@
         <v>45789</v>
       </c>
       <c r="D67" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="E67" t="n">
         <v>1200</v>
       </c>
       <c r="F67" t="n">
-        <v>53534.73</v>
+        <v>72019.09</v>
       </c>
       <c r="G67" t="n">
-        <v>4282.78</v>
+        <v>3869.95</v>
       </c>
       <c r="H67" t="n">
-        <v>49251.95</v>
+        <v>49213.04</v>
       </c>
       <c r="I67" t="n">
-        <v>36582.06</v>
+        <v>68149.14</v>
       </c>
       <c r="J67" t="n">
-        <v>49251.95</v>
+        <v>68149.14</v>
       </c>
       <c r="K67" t="n">
         <v>0</v>
@@ -3066,37 +3066,37 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Adana Bölge Bayi A.Ş.</t>
+          <t>Bursa İmalat Tedarik Ltd.</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Ürün Alpha Standart</t>
+          <t>Ürün Epsilon Profesyonel</t>
         </is>
       </c>
       <c r="C68" s="2" t="n">
         <v>45791</v>
       </c>
       <c r="D68" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="E68" t="n">
-        <v>1850</v>
+        <v>15400</v>
       </c>
       <c r="F68" t="n">
-        <v>229257.51</v>
+        <v>1452384.92</v>
       </c>
       <c r="G68" t="n">
-        <v>0</v>
+        <v>31217.56</v>
       </c>
       <c r="H68" t="n">
-        <v>229257.51</v>
+        <v>924244.95</v>
       </c>
       <c r="I68" t="n">
-        <v>154903.72</v>
+        <v>1421167.36</v>
       </c>
       <c r="J68" t="n">
-        <v>229257.51</v>
+        <v>1421167.36</v>
       </c>
       <c r="K68" t="n">
         <v>0</v>
@@ -3105,37 +3105,37 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Ankara Proje Yönetim ve Satış</t>
+          <t>Karadeniz Toptan Dağıtım A.Ş.</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Yedek Parça Servis Paketi</t>
+          <t>Ürün Delta Kompakt</t>
         </is>
       </c>
       <c r="C69" s="2" t="n">
         <v>45793</v>
       </c>
       <c r="D69" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="E69" t="n">
-        <v>2400</v>
+        <v>1200</v>
       </c>
       <c r="F69" t="n">
-        <v>142759.27</v>
+        <v>20576.88</v>
       </c>
       <c r="G69" t="n">
         <v>0</v>
       </c>
       <c r="H69" t="n">
-        <v>142759.27</v>
+        <v>14060.87</v>
       </c>
       <c r="I69" t="n">
-        <v>89224.53999999999</v>
+        <v>20576.88</v>
       </c>
       <c r="J69" t="n">
-        <v>142759.27</v>
+        <v>20576.88</v>
       </c>
       <c r="K69" t="n">
         <v>0</v>
@@ -3144,37 +3144,37 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Marmara Perakende Çözümleri</t>
+          <t>Akdeniz Endüstriyel Ürünler</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Ürün Delta Kompakt</t>
+          <t>Özel Sipariş Modeli X</t>
         </is>
       </c>
       <c r="C70" s="2" t="n">
         <v>45795</v>
       </c>
       <c r="D70" t="n">
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="E70" t="n">
-        <v>1200</v>
+        <v>21500</v>
       </c>
       <c r="F70" t="n">
-        <v>113017.75</v>
+        <v>460836.42</v>
       </c>
       <c r="G70" t="n">
-        <v>3390.53</v>
+        <v>0</v>
       </c>
       <c r="H70" t="n">
-        <v>109627.22</v>
+        <v>304366.38</v>
       </c>
       <c r="I70" t="n">
-        <v>77228.8</v>
+        <v>460836.42</v>
       </c>
       <c r="J70" t="n">
-        <v>109627.22</v>
+        <v>460836.42</v>
       </c>
       <c r="K70" t="n">
         <v>0</v>
@@ -3183,37 +3183,37 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Kocaeli Ağır Sanayi Pazarlama</t>
+          <t>İç Anadolu Tüketim Malları</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Ürün Zeta Hızlı Tüketim</t>
+          <t>Ürün Alpha Standart</t>
         </is>
       </c>
       <c r="C71" s="2" t="n">
         <v>45797</v>
       </c>
       <c r="D71" t="n">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="E71" t="n">
-        <v>650</v>
+        <v>1850</v>
       </c>
       <c r="F71" t="n">
-        <v>61217.95</v>
+        <v>111029.43</v>
       </c>
       <c r="G71" t="n">
         <v>0</v>
       </c>
       <c r="H71" t="n">
-        <v>61217.95</v>
+        <v>75019.88</v>
       </c>
       <c r="I71" t="n">
-        <v>41439.84</v>
+        <v>111029.43</v>
       </c>
       <c r="J71" t="n">
-        <v>61217.95</v>
+        <v>111029.43</v>
       </c>
       <c r="K71" t="n">
         <v>0</v>
@@ -3222,37 +3222,37 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Bursa İmalat Tedarik Ltd.</t>
+          <t>Karadeniz Toptan Dağıtım A.Ş.</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Ürün Zeta Hızlı Tüketim</t>
+          <t>Özel Sipariş Modeli X</t>
         </is>
       </c>
       <c r="C72" s="2" t="n">
         <v>45799</v>
       </c>
       <c r="D72" t="n">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="E72" t="n">
-        <v>650</v>
+        <v>21500</v>
       </c>
       <c r="F72" t="n">
-        <v>61217.95</v>
+        <v>645170.99</v>
       </c>
       <c r="G72" t="n">
-        <v>4897.44</v>
+        <v>0</v>
       </c>
       <c r="H72" t="n">
-        <v>56320.51</v>
+        <v>426112.93</v>
       </c>
       <c r="I72" t="n">
-        <v>41439.84</v>
+        <v>645170.99</v>
       </c>
       <c r="J72" t="n">
-        <v>56320.51</v>
+        <v>645170.99</v>
       </c>
       <c r="K72" t="n">
         <v>0</v>
@@ -3261,7 +3261,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Marmara Perakende Çözümleri</t>
+          <t>Anadolu Sanayi Grubu A.Ş.</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -3273,25 +3273,25 @@
         <v>45801</v>
       </c>
       <c r="D73" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="E73" t="n">
         <v>1200</v>
       </c>
       <c r="F73" t="n">
-        <v>95172.85000000001</v>
+        <v>30865.32</v>
       </c>
       <c r="G73" t="n">
-        <v>7613.83</v>
+        <v>663.42</v>
       </c>
       <c r="H73" t="n">
-        <v>87559.02</v>
+        <v>21091.3</v>
       </c>
       <c r="I73" t="n">
-        <v>65034.78</v>
+        <v>30201.9</v>
       </c>
       <c r="J73" t="n">
-        <v>87559.02</v>
+        <v>30201.9</v>
       </c>
       <c r="K73" t="n">
         <v>0</v>
@@ -3300,37 +3300,37 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Karadeniz Toptan Dağıtım A.Ş.</t>
+          <t>Ege Dağıtım ve Ticaret Ltd.</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Ürün Gamma Endüstriyel</t>
+          <t>Özel Sipariş Modeli X</t>
         </is>
       </c>
       <c r="C74" s="2" t="n">
         <v>45803</v>
       </c>
       <c r="D74" t="n">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="E74" t="n">
-        <v>8900</v>
+        <v>21500</v>
       </c>
       <c r="F74" t="n">
-        <v>705865.27</v>
+        <v>368669.14</v>
       </c>
       <c r="G74" t="n">
-        <v>0</v>
+        <v>7924.17</v>
       </c>
       <c r="H74" t="n">
-        <v>705865.27</v>
+        <v>243493.1</v>
       </c>
       <c r="I74" t="n">
-        <v>467933.16</v>
+        <v>360744.97</v>
       </c>
       <c r="J74" t="n">
-        <v>705865.27</v>
+        <v>360744.97</v>
       </c>
       <c r="K74" t="n">
         <v>0</v>
@@ -3339,37 +3339,37 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Ege Dağıtım ve Ticaret Ltd.</t>
+          <t>Kocaeli Ağır Sanayi Pazarlama</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Ürün Alpha Standart</t>
+          <t>Yedek Parça Servis Paketi</t>
         </is>
       </c>
       <c r="C75" s="2" t="n">
         <v>45805</v>
       </c>
       <c r="D75" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="E75" t="n">
-        <v>1850</v>
+        <v>2400</v>
       </c>
       <c r="F75" t="n">
-        <v>73362.39999999999</v>
+        <v>164615.06</v>
       </c>
       <c r="G75" t="n">
-        <v>5868.99</v>
+        <v>5307.35</v>
       </c>
       <c r="H75" t="n">
-        <v>67493.41</v>
+        <v>102884.41</v>
       </c>
       <c r="I75" t="n">
-        <v>49569.19</v>
+        <v>159307.71</v>
       </c>
       <c r="J75" t="n">
-        <v>67493.41</v>
+        <v>159307.71</v>
       </c>
       <c r="K75" t="n">
         <v>0</v>
@@ -3378,37 +3378,37 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Toroslar Lojistik ve Ticaret</t>
+          <t>Gaziantep İhracat ve Toptan</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Ürün Alpha Standart</t>
+          <t>Ürün Epsilon Profesyonel</t>
         </is>
       </c>
       <c r="C76" s="2" t="n">
         <v>45807</v>
       </c>
       <c r="D76" t="n">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="E76" t="n">
-        <v>1850</v>
+        <v>15400</v>
       </c>
       <c r="F76" t="n">
-        <v>155895.1</v>
+        <v>198052.49</v>
       </c>
       <c r="G76" t="n">
-        <v>7794.76</v>
+        <v>10642.35</v>
       </c>
       <c r="H76" t="n">
-        <v>148100.35</v>
+        <v>126033.4</v>
       </c>
       <c r="I76" t="n">
-        <v>105334.53</v>
+        <v>187410.14</v>
       </c>
       <c r="J76" t="n">
-        <v>148100.35</v>
+        <v>187410.14</v>
       </c>
       <c r="K76" t="n">
         <v>0</v>
@@ -3417,37 +3417,37 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Anadolu Sanayi Grubu A.Ş.</t>
+          <t>Akdeniz Endüstriyel Ürünler</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Ürün Zeta Hızlı Tüketim</t>
+          <t>Ürün Gamma Endüstriyel</t>
         </is>
       </c>
       <c r="C77" s="2" t="n">
         <v>45809</v>
       </c>
       <c r="D77" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="E77" t="n">
-        <v>650</v>
+        <v>8900</v>
       </c>
       <c r="F77" t="n">
-        <v>64439.95</v>
+        <v>457835.63</v>
       </c>
       <c r="G77" t="n">
-        <v>0</v>
+        <v>14761.08</v>
       </c>
       <c r="H77" t="n">
-        <v>64439.95</v>
+        <v>303509.01</v>
       </c>
       <c r="I77" t="n">
-        <v>43620.89</v>
+        <v>443074.55</v>
       </c>
       <c r="J77" t="n">
-        <v>64439.95</v>
+        <v>443074.55</v>
       </c>
       <c r="K77" t="n">
         <v>0</v>
@@ -3456,7 +3456,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Kocaeli Ağır Sanayi Pazarlama</t>
+          <t>İç Anadolu Tüketim Malları</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -3468,25 +3468,25 @@
         <v>45811</v>
       </c>
       <c r="D78" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="E78" t="n">
         <v>8900</v>
       </c>
       <c r="F78" t="n">
-        <v>485282.37</v>
+        <v>572294.53</v>
       </c>
       <c r="G78" t="n">
-        <v>58233.88</v>
+        <v>0</v>
       </c>
       <c r="H78" t="n">
-        <v>427048.49</v>
+        <v>379386.26</v>
       </c>
       <c r="I78" t="n">
-        <v>321704.05</v>
+        <v>572294.53</v>
       </c>
       <c r="J78" t="n">
-        <v>427048.49</v>
+        <v>572294.53</v>
       </c>
       <c r="K78" t="n">
         <v>0</v>
@@ -3495,37 +3495,37 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Marmara Perakende Çözümleri</t>
+          <t>Karadeniz Toptan Dağıtım A.Ş.</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Ürün Zeta Hızlı Tüketim</t>
+          <t>Özel Sipariş Modeli X</t>
         </is>
       </c>
       <c r="C79" s="2" t="n">
         <v>45813</v>
       </c>
       <c r="D79" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="E79" t="n">
-        <v>650</v>
+        <v>21500</v>
       </c>
       <c r="F79" t="n">
-        <v>6443.99</v>
+        <v>1382509.26</v>
       </c>
       <c r="G79" t="n">
-        <v>0</v>
+        <v>29715.65</v>
       </c>
       <c r="H79" t="n">
-        <v>6443.99</v>
+        <v>913099.14</v>
       </c>
       <c r="I79" t="n">
-        <v>4362.09</v>
+        <v>1352793.61</v>
       </c>
       <c r="J79" t="n">
-        <v>6443.99</v>
+        <v>1352793.61</v>
       </c>
       <c r="K79" t="n">
         <v>0</v>
@@ -3534,37 +3534,37 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Marmara Perakende Çözümleri</t>
+          <t>Toroslar Lojistik ve Ticaret</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Ürün Gamma Endüstriyel</t>
+          <t>Ürün Epsilon Profesyonel</t>
         </is>
       </c>
       <c r="C80" s="2" t="n">
         <v>45815</v>
       </c>
       <c r="D80" t="n">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="E80" t="n">
-        <v>8900</v>
+        <v>15400</v>
       </c>
       <c r="F80" t="n">
-        <v>1102914.49</v>
+        <v>1254332.43</v>
       </c>
       <c r="G80" t="n">
         <v>0</v>
       </c>
       <c r="H80" t="n">
-        <v>1102914.49</v>
+        <v>798211.55</v>
       </c>
       <c r="I80" t="n">
-        <v>731145.5600000001</v>
+        <v>1254332.43</v>
       </c>
       <c r="J80" t="n">
-        <v>1102914.49</v>
+        <v>1254332.43</v>
       </c>
       <c r="K80" t="n">
         <v>0</v>
@@ -3573,12 +3573,12 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Adana Bölge Bayi A.Ş.</t>
+          <t>Marmara Perakende Çözümleri</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Ürün Zeta Hızlı Tüketim</t>
+          <t>Ürün Beta Premium</t>
         </is>
       </c>
       <c r="C81" s="2" t="n">
@@ -3588,22 +3588,22 @@
         <v>3</v>
       </c>
       <c r="E81" t="n">
-        <v>650</v>
+        <v>4200</v>
       </c>
       <c r="F81" t="n">
-        <v>9665.99</v>
+        <v>54014.32</v>
       </c>
       <c r="G81" t="n">
-        <v>289.98</v>
+        <v>1160.98</v>
       </c>
       <c r="H81" t="n">
-        <v>9376.01</v>
+        <v>36009.54</v>
       </c>
       <c r="I81" t="n">
-        <v>6543.13</v>
+        <v>52853.34</v>
       </c>
       <c r="J81" t="n">
-        <v>9376.01</v>
+        <v>52853.34</v>
       </c>
       <c r="K81" t="n">
         <v>0</v>
@@ -3612,7 +3612,7 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Bursa İmalat Tedarik Ltd.</t>
+          <t>Kocaeli Ağır Sanayi Pazarlama</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -3624,25 +3624,25 @@
         <v>45819</v>
       </c>
       <c r="D82" t="n">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="E82" t="n">
         <v>2400</v>
       </c>
       <c r="F82" t="n">
-        <v>226035.51</v>
+        <v>257211.03</v>
       </c>
       <c r="G82" t="n">
-        <v>0</v>
+        <v>13821.23</v>
       </c>
       <c r="H82" t="n">
-        <v>226035.51</v>
+        <v>160756.89</v>
       </c>
       <c r="I82" t="n">
-        <v>141272.19</v>
+        <v>243389.8</v>
       </c>
       <c r="J82" t="n">
-        <v>226035.51</v>
+        <v>243389.8</v>
       </c>
       <c r="K82" t="n">
         <v>0</v>
@@ -3651,37 +3651,37 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>İç Anadolu Tüketim Malları</t>
+          <t>Toroslar Lojistik ve Ticaret</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Ürün Epsilon Profesyonel</t>
+          <t>Ürün Alpha Standart</t>
         </is>
       </c>
       <c r="C83" s="2" t="n">
         <v>45821</v>
       </c>
       <c r="D83" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E83" t="n">
-        <v>15400</v>
+        <v>1850</v>
       </c>
       <c r="F83" t="n">
-        <v>839702.08</v>
+        <v>103098.75</v>
       </c>
       <c r="G83" t="n">
-        <v>0</v>
+        <v>5540.01</v>
       </c>
       <c r="H83" t="n">
-        <v>839702.08</v>
+        <v>69661.32000000001</v>
       </c>
       <c r="I83" t="n">
-        <v>534355.87</v>
+        <v>97558.74000000001</v>
       </c>
       <c r="J83" t="n">
-        <v>839702.08</v>
+        <v>97558.74000000001</v>
       </c>
       <c r="K83" t="n">
         <v>0</v>
@@ -3690,37 +3690,37 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Marmara Perakende Çözümleri</t>
+          <t>Akdeniz Endüstriyel Ürünler</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Yedek Parça Servis Paketi</t>
+          <t>Özel Sipariş Modeli X</t>
         </is>
       </c>
       <c r="C84" s="2" t="n">
         <v>45823</v>
       </c>
       <c r="D84" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="E84" t="n">
-        <v>2400</v>
+        <v>21500</v>
       </c>
       <c r="F84" t="n">
-        <v>249828.72</v>
+        <v>1751178.4</v>
       </c>
       <c r="G84" t="n">
-        <v>12491.44</v>
+        <v>0</v>
       </c>
       <c r="H84" t="n">
-        <v>237337.28</v>
+        <v>1156592.24</v>
       </c>
       <c r="I84" t="n">
-        <v>156142.95</v>
+        <v>1751178.4</v>
       </c>
       <c r="J84" t="n">
-        <v>237337.28</v>
+        <v>1751178.4</v>
       </c>
       <c r="K84" t="n">
         <v>0</v>
@@ -3729,37 +3729,37 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>İzmir Ticari Faaliyetler A.Ş.</t>
+          <t>Güneydoğu Pazarlama Ltd.</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Ürün Zeta Hızlı Tüketim</t>
+          <t>Ürün Epsilon Profesyonel</t>
         </is>
       </c>
       <c r="C85" s="2" t="n">
         <v>45825</v>
       </c>
       <c r="D85" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E85" t="n">
-        <v>650</v>
+        <v>15400</v>
       </c>
       <c r="F85" t="n">
-        <v>19331.98</v>
+        <v>198052.49</v>
       </c>
       <c r="G85" t="n">
-        <v>2319.84</v>
+        <v>6385.41</v>
       </c>
       <c r="H85" t="n">
-        <v>17012.15</v>
+        <v>126033.4</v>
       </c>
       <c r="I85" t="n">
-        <v>13086.27</v>
+        <v>191667.08</v>
       </c>
       <c r="J85" t="n">
-        <v>17012.15</v>
+        <v>191667.08</v>
       </c>
       <c r="K85" t="n">
         <v>0</v>
@@ -3768,37 +3768,37 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>İstanbul Kurumsal Tedarik A.Ş.</t>
+          <t>Gaziantep İhracat ve Toptan</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Ürün Zeta Hızlı Tüketim</t>
+          <t>Ürün Alpha Standart</t>
         </is>
       </c>
       <c r="C86" s="2" t="n">
         <v>45827</v>
       </c>
       <c r="D86" t="n">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="E86" t="n">
-        <v>650</v>
+        <v>1850</v>
       </c>
       <c r="F86" t="n">
-        <v>25775.98</v>
+        <v>134821.45</v>
       </c>
       <c r="G86" t="n">
-        <v>3093.12</v>
+        <v>7244.63</v>
       </c>
       <c r="H86" t="n">
-        <v>22682.86</v>
+        <v>91095.57000000001</v>
       </c>
       <c r="I86" t="n">
-        <v>17448.36</v>
+        <v>127576.82</v>
       </c>
       <c r="J86" t="n">
-        <v>22682.86</v>
+        <v>127576.82</v>
       </c>
       <c r="K86" t="n">
         <v>0</v>
@@ -3807,7 +3807,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Ankara Proje Yönetim ve Satış</t>
+          <t>Gaziantep İhracat ve Toptan</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -3819,25 +3819,25 @@
         <v>45829</v>
       </c>
       <c r="D87" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="E87" t="n">
         <v>8900</v>
       </c>
       <c r="F87" t="n">
-        <v>573515.53</v>
+        <v>152611.88</v>
       </c>
       <c r="G87" t="n">
-        <v>17205.47</v>
+        <v>4920.36</v>
       </c>
       <c r="H87" t="n">
-        <v>556310.0699999999</v>
+        <v>101169.67</v>
       </c>
       <c r="I87" t="n">
-        <v>380195.69</v>
+        <v>147691.52</v>
       </c>
       <c r="J87" t="n">
-        <v>556310.0699999999</v>
+        <v>147691.52</v>
       </c>
       <c r="K87" t="n">
         <v>0</v>
@@ -3846,37 +3846,37 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Bursa İmalat Tedarik Ltd.</t>
+          <t>Marmara Perakende Çözümleri</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Ürün Epsilon Profesyonel</t>
+          <t>Ürün Gamma Endüstriyel</t>
         </is>
       </c>
       <c r="C88" s="2" t="n">
         <v>45831</v>
       </c>
       <c r="D88" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E88" t="n">
-        <v>15400</v>
+        <v>8900</v>
       </c>
       <c r="F88" t="n">
-        <v>381682.77</v>
+        <v>267070.78</v>
       </c>
       <c r="G88" t="n">
         <v>0</v>
       </c>
       <c r="H88" t="n">
-        <v>381682.77</v>
+        <v>177046.92</v>
       </c>
       <c r="I88" t="n">
-        <v>242889.03</v>
+        <v>267070.78</v>
       </c>
       <c r="J88" t="n">
-        <v>381682.77</v>
+        <v>267070.78</v>
       </c>
       <c r="K88" t="n">
         <v>0</v>
@@ -3885,7 +3885,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Bursa İmalat Tedarik Ltd.</t>
+          <t>Marmara Perakende Çözümleri</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -3897,25 +3897,25 @@
         <v>45833</v>
       </c>
       <c r="D89" t="n">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="E89" t="n">
         <v>1850</v>
       </c>
       <c r="F89" t="n">
-        <v>210916.9</v>
+        <v>111029.43</v>
       </c>
       <c r="G89" t="n">
-        <v>16873.35</v>
+        <v>0</v>
       </c>
       <c r="H89" t="n">
-        <v>194043.55</v>
+        <v>75019.88</v>
       </c>
       <c r="I89" t="n">
-        <v>142511.42</v>
+        <v>111029.43</v>
       </c>
       <c r="J89" t="n">
-        <v>194043.55</v>
+        <v>111029.43</v>
       </c>
       <c r="K89" t="n">
         <v>0</v>
@@ -3924,37 +3924,37 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Akdeniz Endüstriyel Ürünler</t>
+          <t>İzmir Ticari Faaliyetler A.Ş.</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Ürün Alpha Standart</t>
+          <t>Yedek Parça Servis Paketi</t>
         </is>
       </c>
       <c r="C90" s="2" t="n">
         <v>45835</v>
       </c>
       <c r="D90" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E90" t="n">
-        <v>1850</v>
+        <v>2400</v>
       </c>
       <c r="F90" t="n">
-        <v>55021.8</v>
+        <v>72019.09</v>
       </c>
       <c r="G90" t="n">
-        <v>4401.74</v>
+        <v>0</v>
       </c>
       <c r="H90" t="n">
-        <v>50620.06</v>
+        <v>45011.93</v>
       </c>
       <c r="I90" t="n">
-        <v>37176.89</v>
+        <v>72019.09</v>
       </c>
       <c r="J90" t="n">
-        <v>50620.06</v>
+        <v>72019.09</v>
       </c>
       <c r="K90" t="n">
         <v>0</v>
@@ -3963,37 +3963,37 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>İç Anadolu Tüketim Malları</t>
+          <t>Adana Bölge Bayi A.Ş.</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Ürün Delta Kompakt</t>
+          <t>Ürün Epsilon Profesyonel</t>
         </is>
       </c>
       <c r="C91" s="2" t="n">
         <v>45837</v>
       </c>
       <c r="D91" t="n">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="E91" t="n">
-        <v>1200</v>
+        <v>15400</v>
       </c>
       <c r="F91" t="n">
-        <v>124914.36</v>
+        <v>726192.46</v>
       </c>
       <c r="G91" t="n">
-        <v>9993.15</v>
+        <v>0</v>
       </c>
       <c r="H91" t="n">
-        <v>114921.21</v>
+        <v>462122.48</v>
       </c>
       <c r="I91" t="n">
-        <v>85358.14999999999</v>
+        <v>726192.46</v>
       </c>
       <c r="J91" t="n">
-        <v>114921.21</v>
+        <v>726192.46</v>
       </c>
       <c r="K91" t="n">
         <v>0</v>
@@ -4007,32 +4007,32 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Özel Sipariş Modeli X</t>
+          <t>Yedek Parça Servis Paketi</t>
         </is>
       </c>
       <c r="C92" s="2" t="n">
         <v>45840</v>
       </c>
       <c r="D92" t="n">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="E92" t="n">
-        <v>21500</v>
+        <v>2400</v>
       </c>
       <c r="F92" t="n">
-        <v>532868.8</v>
+        <v>185191.94</v>
       </c>
       <c r="G92" t="n">
-        <v>15986.06</v>
+        <v>5970.77</v>
       </c>
       <c r="H92" t="n">
-        <v>516882.73</v>
+        <v>115744.96</v>
       </c>
       <c r="I92" t="n">
-        <v>351941.25</v>
+        <v>179221.17</v>
       </c>
       <c r="J92" t="n">
-        <v>516882.73</v>
+        <v>179221.17</v>
       </c>
       <c r="K92" t="n">
         <v>0</v>
@@ -4041,37 +4041,37 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Bursa İmalat Tedarik Ltd.</t>
+          <t>İstanbul Kurumsal Tedarik A.Ş.</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Ürün Beta Premium</t>
+          <t>Ürün Zeta Hızlı Tüketim</t>
         </is>
       </c>
       <c r="C93" s="2" t="n">
         <v>45842</v>
       </c>
       <c r="D93" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E93" t="n">
-        <v>4200</v>
+        <v>650</v>
       </c>
       <c r="F93" t="n">
-        <v>166552.48</v>
+        <v>25078.07</v>
       </c>
       <c r="G93" t="n">
-        <v>4996.57</v>
+        <v>1347.57</v>
       </c>
       <c r="H93" t="n">
-        <v>161555.91</v>
+        <v>16975.93</v>
       </c>
       <c r="I93" t="n">
-        <v>111034.99</v>
+        <v>23730.5</v>
       </c>
       <c r="J93" t="n">
-        <v>161555.91</v>
+        <v>23730.5</v>
       </c>
       <c r="K93" t="n">
         <v>0</v>
@@ -4080,37 +4080,37 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>İç Anadolu Tüketim Malları</t>
+          <t>Güneydoğu Pazarlama Ltd.</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Ürün Gamma Endüstriyel</t>
+          <t>Ürün Alpha Standart</t>
         </is>
       </c>
       <c r="C94" s="2" t="n">
         <v>45844</v>
       </c>
       <c r="D94" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="E94" t="n">
-        <v>8900</v>
+        <v>1850</v>
       </c>
       <c r="F94" t="n">
-        <v>926448.17</v>
+        <v>182405.49</v>
       </c>
       <c r="G94" t="n">
-        <v>0</v>
+        <v>9801.559999999999</v>
       </c>
       <c r="H94" t="n">
-        <v>926448.17</v>
+        <v>123246.95</v>
       </c>
       <c r="I94" t="n">
-        <v>614162.27</v>
+        <v>172603.93</v>
       </c>
       <c r="J94" t="n">
-        <v>926448.17</v>
+        <v>172603.93</v>
       </c>
       <c r="K94" t="n">
         <v>0</v>
@@ -4119,37 +4119,37 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Adana Bölge Bayi A.Ş.</t>
+          <t>Ankara Proje Yönetim ve Satış</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Ürün Zeta Hızlı Tüketim</t>
+          <t>Yedek Parça Servis Paketi</t>
         </is>
       </c>
       <c r="C95" s="2" t="n">
         <v>45846</v>
       </c>
       <c r="D95" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="E95" t="n">
-        <v>650</v>
+        <v>2400</v>
       </c>
       <c r="F95" t="n">
-        <v>48329.96</v>
+        <v>41153.76</v>
       </c>
       <c r="G95" t="n">
-        <v>0</v>
+        <v>1326.84</v>
       </c>
       <c r="H95" t="n">
-        <v>48329.96</v>
+        <v>25721.1</v>
       </c>
       <c r="I95" t="n">
-        <v>32715.67</v>
+        <v>39826.92</v>
       </c>
       <c r="J95" t="n">
-        <v>48329.96</v>
+        <v>39826.92</v>
       </c>
       <c r="K95" t="n">
         <v>0</v>
@@ -4158,37 +4158,37 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Karadeniz Toptan Dağıtım A.Ş.</t>
+          <t>Marmara Perakende Çözümleri</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Ürün Delta Kompakt</t>
+          <t>Ürün Gamma Endüstriyel</t>
         </is>
       </c>
       <c r="C96" s="2" t="n">
         <v>45848</v>
       </c>
       <c r="D96" t="n">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="E96" t="n">
-        <v>1200</v>
+        <v>8900</v>
       </c>
       <c r="F96" t="n">
-        <v>47586.42</v>
+        <v>724906.41</v>
       </c>
       <c r="G96" t="n">
-        <v>5710.37</v>
+        <v>38952.85</v>
       </c>
       <c r="H96" t="n">
-        <v>41876.05</v>
+        <v>480555.93</v>
       </c>
       <c r="I96" t="n">
-        <v>32517.39</v>
+        <v>685953.5600000001</v>
       </c>
       <c r="J96" t="n">
-        <v>41876.05</v>
+        <v>685953.5600000001</v>
       </c>
       <c r="K96" t="n">
         <v>0</v>
@@ -4197,37 +4197,37 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Ege Dağıtım ve Ticaret Ltd.</t>
+          <t>Ankara Proje Yönetim ve Satış</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Ürün Zeta Hızlı Tüketim</t>
+          <t>Ürün Beta Premium</t>
         </is>
       </c>
       <c r="C97" s="2" t="n">
         <v>45850</v>
       </c>
       <c r="D97" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="E97" t="n">
-        <v>650</v>
+        <v>4200</v>
       </c>
       <c r="F97" t="n">
-        <v>28997.98</v>
+        <v>72019.09</v>
       </c>
       <c r="G97" t="n">
-        <v>0</v>
+        <v>3869.95</v>
       </c>
       <c r="H97" t="n">
-        <v>28997.98</v>
+        <v>48012.72</v>
       </c>
       <c r="I97" t="n">
-        <v>19629.4</v>
+        <v>68149.14</v>
       </c>
       <c r="J97" t="n">
-        <v>28997.98</v>
+        <v>68149.14</v>
       </c>
       <c r="K97" t="n">
         <v>0</v>
@@ -4236,37 +4236,37 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Bursa İmalat Tedarik Ltd.</t>
+          <t>Kocaeli Ağır Sanayi Pazarlama</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Ürün Alpha Standart</t>
+          <t>Ürün Beta Premium</t>
         </is>
       </c>
       <c r="C98" s="2" t="n">
         <v>45852</v>
       </c>
       <c r="D98" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="E98" t="n">
-        <v>1850</v>
+        <v>4200</v>
       </c>
       <c r="F98" t="n">
-        <v>18340.6</v>
+        <v>180047.72</v>
       </c>
       <c r="G98" t="n">
-        <v>917.03</v>
+        <v>9674.860000000001</v>
       </c>
       <c r="H98" t="n">
-        <v>17423.57</v>
+        <v>120031.81</v>
       </c>
       <c r="I98" t="n">
-        <v>12392.3</v>
+        <v>170372.86</v>
       </c>
       <c r="J98" t="n">
-        <v>17423.57</v>
+        <v>170372.86</v>
       </c>
       <c r="K98" t="n">
         <v>0</v>
@@ -4275,37 +4275,37 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Güneydoğu Pazarlama Ltd.</t>
+          <t>Gaziantep İhracat ve Toptan</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Yedek Parça Servis Paketi</t>
+          <t>Ürün Zeta Hızlı Tüketim</t>
         </is>
       </c>
       <c r="C99" s="2" t="n">
         <v>45854</v>
       </c>
       <c r="D99" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="E99" t="n">
-        <v>2400</v>
+        <v>650</v>
       </c>
       <c r="F99" t="n">
-        <v>71379.63</v>
+        <v>39010.34</v>
       </c>
       <c r="G99" t="n">
-        <v>3568.98</v>
+        <v>838.49</v>
       </c>
       <c r="H99" t="n">
-        <v>67810.64999999999</v>
+        <v>26407</v>
       </c>
       <c r="I99" t="n">
-        <v>44612.27</v>
+        <v>38171.85</v>
       </c>
       <c r="J99" t="n">
-        <v>67810.64999999999</v>
+        <v>38171.85</v>
       </c>
       <c r="K99" t="n">
         <v>0</v>
@@ -4314,37 +4314,37 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Güneydoğu Pazarlama Ltd.</t>
+          <t>Akdeniz Endüstriyel Ürünler</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Yedek Parça Servis Paketi</t>
+          <t>Özel Sipariş Modeli X</t>
         </is>
       </c>
       <c r="C100" s="2" t="n">
         <v>45856</v>
       </c>
       <c r="D100" t="n">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="E100" t="n">
-        <v>2400</v>
+        <v>21500</v>
       </c>
       <c r="F100" t="n">
-        <v>142759.27</v>
+        <v>1751178.4</v>
       </c>
       <c r="G100" t="n">
-        <v>11420.74</v>
+        <v>94099.57000000001</v>
       </c>
       <c r="H100" t="n">
-        <v>131338.53</v>
+        <v>1156592.24</v>
       </c>
       <c r="I100" t="n">
-        <v>89224.53999999999</v>
+        <v>1657078.83</v>
       </c>
       <c r="J100" t="n">
-        <v>131338.53</v>
+        <v>1657078.83</v>
       </c>
       <c r="K100" t="n">
         <v>0</v>
@@ -4353,37 +4353,37 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Akdeniz Endüstriyel Ürünler</t>
+          <t>Güneydoğu Pazarlama Ltd.</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Ürün Beta Premium</t>
+          <t>Ürün Alpha Standart</t>
         </is>
       </c>
       <c r="C101" s="2" t="n">
         <v>45858</v>
       </c>
       <c r="D101" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="E101" t="n">
-        <v>4200</v>
+        <v>1850</v>
       </c>
       <c r="F101" t="n">
-        <v>333104.96</v>
+        <v>47584.04</v>
       </c>
       <c r="G101" t="n">
-        <v>26648.4</v>
+        <v>1022.77</v>
       </c>
       <c r="H101" t="n">
-        <v>306456.56</v>
+        <v>32151.38</v>
       </c>
       <c r="I101" t="n">
-        <v>222069.97</v>
+        <v>46561.27</v>
       </c>
       <c r="J101" t="n">
-        <v>306456.56</v>
+        <v>46561.27</v>
       </c>
       <c r="K101" t="n">
         <v>0</v>
@@ -4392,37 +4392,37 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>İzmir Ticari Faaliyetler A.Ş.</t>
+          <t>Akdeniz Endüstriyel Ürünler</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Ürün Delta Kompakt</t>
+          <t>Ürün Gamma Endüstriyel</t>
         </is>
       </c>
       <c r="C102" s="2" t="n">
         <v>45860</v>
       </c>
       <c r="D102" t="n">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="E102" t="n">
-        <v>1200</v>
+        <v>8900</v>
       </c>
       <c r="F102" t="n">
-        <v>35689.82</v>
+        <v>763059.38</v>
       </c>
       <c r="G102" t="n">
-        <v>1784.49</v>
+        <v>41003</v>
       </c>
       <c r="H102" t="n">
-        <v>33905.33</v>
+        <v>505848.35</v>
       </c>
       <c r="I102" t="n">
-        <v>24388.04</v>
+        <v>722056.38</v>
       </c>
       <c r="J102" t="n">
-        <v>33905.33</v>
+        <v>722056.38</v>
       </c>
       <c r="K102" t="n">
         <v>0</v>
@@ -4431,37 +4431,37 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Ege Dağıtım ve Ticaret Ltd.</t>
+          <t>İzmir Ticari Faaliyetler A.Ş.</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Ürün Alpha Standart</t>
+          <t>Yedek Parça Servis Paketi</t>
         </is>
       </c>
       <c r="C103" s="2" t="n">
         <v>45862</v>
       </c>
       <c r="D103" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="E103" t="n">
-        <v>1850</v>
+        <v>2400</v>
       </c>
       <c r="F103" t="n">
-        <v>91703</v>
+        <v>20576.88</v>
       </c>
       <c r="G103" t="n">
-        <v>0</v>
+        <v>663.42</v>
       </c>
       <c r="H103" t="n">
-        <v>91703</v>
+        <v>12860.55</v>
       </c>
       <c r="I103" t="n">
-        <v>61961.49</v>
+        <v>19913.46</v>
       </c>
       <c r="J103" t="n">
-        <v>91703</v>
+        <v>19913.46</v>
       </c>
       <c r="K103" t="n">
         <v>0</v>
@@ -4470,37 +4470,37 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>İç Anadolu Tüketim Malları</t>
+          <t>Gaziantep İhracat ve Toptan</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Ürün Epsilon Profesyonel</t>
+          <t>Ürün Zeta Hızlı Tüketim</t>
         </is>
       </c>
       <c r="C104" s="2" t="n">
         <v>45864</v>
       </c>
       <c r="D104" t="n">
-        <v>4</v>
+        <v>23</v>
       </c>
       <c r="E104" t="n">
-        <v>15400</v>
+        <v>650</v>
       </c>
       <c r="F104" t="n">
-        <v>305346.21</v>
+        <v>64088.41</v>
       </c>
       <c r="G104" t="n">
         <v>0</v>
       </c>
       <c r="H104" t="n">
-        <v>305346.21</v>
+        <v>43382.93</v>
       </c>
       <c r="I104" t="n">
-        <v>194311.23</v>
+        <v>64088.41</v>
       </c>
       <c r="J104" t="n">
-        <v>305346.21</v>
+        <v>64088.41</v>
       </c>
       <c r="K104" t="n">
         <v>0</v>
@@ -4509,37 +4509,37 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>İç Anadolu Tüketim Malları</t>
+          <t>Anadolu Sanayi Grubu A.Ş.</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Ürün Gamma Endüstriyel</t>
+          <t>Özel Sipariş Modeli X</t>
         </is>
       </c>
       <c r="C105" s="2" t="n">
         <v>45866</v>
       </c>
       <c r="D105" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E105" t="n">
-        <v>8900</v>
+        <v>21500</v>
       </c>
       <c r="F105" t="n">
-        <v>573515.53</v>
+        <v>829505.5600000001</v>
       </c>
       <c r="G105" t="n">
-        <v>0</v>
+        <v>17829.39</v>
       </c>
       <c r="H105" t="n">
-        <v>573515.53</v>
+        <v>547859.48</v>
       </c>
       <c r="I105" t="n">
-        <v>380195.69</v>
+        <v>811676.17</v>
       </c>
       <c r="J105" t="n">
-        <v>573515.53</v>
+        <v>811676.17</v>
       </c>
       <c r="K105" t="n">
         <v>0</v>
@@ -4548,37 +4548,37 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Bursa İmalat Tedarik Ltd.</t>
+          <t>Anadolu Sanayi Grubu A.Ş.</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Ürün Beta Premium</t>
+          <t>Ürün Zeta Hızlı Tüketim</t>
         </is>
       </c>
       <c r="C106" s="2" t="n">
         <v>45868</v>
       </c>
       <c r="D106" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="E106" t="n">
-        <v>4200</v>
+        <v>650</v>
       </c>
       <c r="F106" t="n">
-        <v>374743.08</v>
+        <v>27864.53</v>
       </c>
       <c r="G106" t="n">
-        <v>0</v>
+        <v>598.92</v>
       </c>
       <c r="H106" t="n">
-        <v>374743.08</v>
+        <v>18862.14</v>
       </c>
       <c r="I106" t="n">
-        <v>249828.72</v>
+        <v>27265.61</v>
       </c>
       <c r="J106" t="n">
-        <v>374743.08</v>
+        <v>27265.61</v>
       </c>
       <c r="K106" t="n">
         <v>0</v>
@@ -4587,7 +4587,7 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>İç Anadolu Tüketim Malları</t>
+          <t>Karadeniz Toptan Dağıtım A.Ş.</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -4605,19 +4605,19 @@
         <v>21500</v>
       </c>
       <c r="F107" t="n">
-        <v>2451196.46</v>
+        <v>2119847.54</v>
       </c>
       <c r="G107" t="n">
         <v>0</v>
       </c>
       <c r="H107" t="n">
-        <v>2451196.46</v>
+        <v>1400085.35</v>
       </c>
       <c r="I107" t="n">
-        <v>1618929.76</v>
+        <v>2119847.54</v>
       </c>
       <c r="J107" t="n">
-        <v>2451196.46</v>
+        <v>2119847.54</v>
       </c>
       <c r="K107" t="n">
         <v>0</v>
@@ -4626,37 +4626,37 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Akdeniz Endüstriyel Ürünler</t>
+          <t>Adana Bölge Bayi A.Ş.</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Ürün Gamma Endüstriyel</t>
+          <t>Ürün Delta Kompakt</t>
         </is>
       </c>
       <c r="C108" s="2" t="n">
         <v>45872</v>
       </c>
       <c r="D108" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="E108" t="n">
-        <v>8900</v>
+        <v>1200</v>
       </c>
       <c r="F108" t="n">
-        <v>882331.59</v>
+        <v>25721.1</v>
       </c>
       <c r="G108" t="n">
-        <v>44116.58</v>
+        <v>552.85</v>
       </c>
       <c r="H108" t="n">
-        <v>838215.01</v>
+        <v>17576.09</v>
       </c>
       <c r="I108" t="n">
-        <v>584916.45</v>
+        <v>25168.25</v>
       </c>
       <c r="J108" t="n">
-        <v>838215.01</v>
+        <v>25168.25</v>
       </c>
       <c r="K108" t="n">
         <v>0</v>
@@ -4665,37 +4665,37 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Marmara Perakende Çözümleri</t>
+          <t>Bursa İmalat Tedarik Ltd.</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Ürün Alpha Standart</t>
+          <t>Özel Sipariş Modeli X</t>
         </is>
       </c>
       <c r="C109" s="2" t="n">
         <v>45874</v>
       </c>
       <c r="D109" t="n">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="E109" t="n">
-        <v>1850</v>
+        <v>21500</v>
       </c>
       <c r="F109" t="n">
-        <v>36681.2</v>
+        <v>2304182.1</v>
       </c>
       <c r="G109" t="n">
-        <v>1100.44</v>
+        <v>49526.09</v>
       </c>
       <c r="H109" t="n">
-        <v>35580.76</v>
+        <v>1521831.9</v>
       </c>
       <c r="I109" t="n">
-        <v>24784.6</v>
+        <v>2254656.01</v>
       </c>
       <c r="J109" t="n">
-        <v>35580.76</v>
+        <v>2254656.01</v>
       </c>
       <c r="K109" t="n">
         <v>0</v>
@@ -4704,37 +4704,37 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Toroslar Lojistik ve Ticaret</t>
+          <t>Karadeniz Toptan Dağıtım A.Ş.</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Ürün Delta Kompakt</t>
+          <t>Yedek Parça Servis Paketi</t>
         </is>
       </c>
       <c r="C110" s="2" t="n">
         <v>45876</v>
       </c>
       <c r="D110" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="E110" t="n">
-        <v>1200</v>
+        <v>2400</v>
       </c>
       <c r="F110" t="n">
-        <v>83276.24000000001</v>
+        <v>205768.82</v>
       </c>
       <c r="G110" t="n">
-        <v>9993.15</v>
+        <v>0</v>
       </c>
       <c r="H110" t="n">
-        <v>73283.09</v>
+        <v>128605.51</v>
       </c>
       <c r="I110" t="n">
-        <v>56905.43</v>
+        <v>205768.82</v>
       </c>
       <c r="J110" t="n">
-        <v>73283.09</v>
+        <v>205768.82</v>
       </c>
       <c r="K110" t="n">
         <v>0</v>
@@ -4743,37 +4743,37 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>İstanbul Kurumsal Tedarik A.Ş.</t>
+          <t>Toroslar Lojistik ve Ticaret</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Ürün Epsilon Profesyonel</t>
+          <t>Özel Sipariş Modeli X</t>
         </is>
       </c>
       <c r="C111" s="2" t="n">
         <v>45878</v>
       </c>
       <c r="D111" t="n">
-        <v>22</v>
+        <v>7</v>
       </c>
       <c r="E111" t="n">
-        <v>15400</v>
+        <v>21500</v>
       </c>
       <c r="F111" t="n">
-        <v>1679404.17</v>
+        <v>645170.99</v>
       </c>
       <c r="G111" t="n">
-        <v>50382.13</v>
+        <v>20800.96</v>
       </c>
       <c r="H111" t="n">
-        <v>1629022.04</v>
+        <v>426112.93</v>
       </c>
       <c r="I111" t="n">
-        <v>1068711.74</v>
+        <v>624370.03</v>
       </c>
       <c r="J111" t="n">
-        <v>1629022.04</v>
+        <v>624370.03</v>
       </c>
       <c r="K111" t="n">
         <v>0</v>
@@ -4782,37 +4782,37 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Karadeniz Toptan Dağıtım A.Ş.</t>
+          <t>Bursa İmalat Tedarik Ltd.</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Ürün Delta Kompakt</t>
+          <t>Özel Sipariş Modeli X</t>
         </is>
       </c>
       <c r="C112" s="2" t="n">
         <v>45880</v>
       </c>
       <c r="D112" t="n">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="E112" t="n">
-        <v>1200</v>
+        <v>21500</v>
       </c>
       <c r="F112" t="n">
-        <v>23793.21</v>
+        <v>2304182.1</v>
       </c>
       <c r="G112" t="n">
-        <v>0</v>
+        <v>123815.23</v>
       </c>
       <c r="H112" t="n">
-        <v>23793.21</v>
+        <v>1521831.9</v>
       </c>
       <c r="I112" t="n">
-        <v>16258.69</v>
+        <v>2180366.87</v>
       </c>
       <c r="J112" t="n">
-        <v>23793.21</v>
+        <v>2180366.87</v>
       </c>
       <c r="K112" t="n">
         <v>0</v>
@@ -4821,37 +4821,37 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Akdeniz Endüstriyel Ürünler</t>
+          <t>Adana Bölge Bayi A.Ş.</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Özel Sipariş Modeli X</t>
+          <t>Ürün Zeta Hızlı Tüketim</t>
         </is>
       </c>
       <c r="C113" s="2" t="n">
         <v>45882</v>
       </c>
       <c r="D113" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E113" t="n">
-        <v>21500</v>
+        <v>650</v>
       </c>
       <c r="F113" t="n">
-        <v>532868.8</v>
+        <v>5572.91</v>
       </c>
       <c r="G113" t="n">
-        <v>0</v>
+        <v>299.46</v>
       </c>
       <c r="H113" t="n">
-        <v>532868.8</v>
+        <v>3772.43</v>
       </c>
       <c r="I113" t="n">
-        <v>351941.25</v>
+        <v>5273.45</v>
       </c>
       <c r="J113" t="n">
-        <v>532868.8</v>
+        <v>5273.45</v>
       </c>
       <c r="K113" t="n">
         <v>0</v>
@@ -4860,37 +4860,37 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>İç Anadolu Tüketim Malları</t>
+          <t>Kocaeli Ağır Sanayi Pazarlama</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Ürün Alpha Standart</t>
+          <t>Ürün Gamma Endüstriyel</t>
         </is>
       </c>
       <c r="C114" s="2" t="n">
         <v>45884</v>
       </c>
       <c r="D114" t="n">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="E114" t="n">
-        <v>1850</v>
+        <v>8900</v>
       </c>
       <c r="F114" t="n">
-        <v>128384.2</v>
+        <v>114458.91</v>
       </c>
       <c r="G114" t="n">
-        <v>0</v>
+        <v>2460.18</v>
       </c>
       <c r="H114" t="n">
-        <v>128384.2</v>
+        <v>75877.25</v>
       </c>
       <c r="I114" t="n">
-        <v>86746.08</v>
+        <v>111998.73</v>
       </c>
       <c r="J114" t="n">
-        <v>128384.2</v>
+        <v>111998.73</v>
       </c>
       <c r="K114" t="n">
         <v>0</v>
@@ -4899,37 +4899,37 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Karadeniz Toptan Dağıtım A.Ş.</t>
+          <t>Bursa İmalat Tedarik Ltd.</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Özel Sipariş Modeli X</t>
+          <t>Yedek Parça Servis Paketi</t>
         </is>
       </c>
       <c r="C115" s="2" t="n">
         <v>45886</v>
       </c>
       <c r="D115" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E115" t="n">
-        <v>21500</v>
+        <v>2400</v>
       </c>
       <c r="F115" t="n">
-        <v>746016.3100000001</v>
+        <v>51442.21</v>
       </c>
       <c r="G115" t="n">
-        <v>0</v>
+        <v>2764.25</v>
       </c>
       <c r="H115" t="n">
-        <v>746016.3100000001</v>
+        <v>32151.38</v>
       </c>
       <c r="I115" t="n">
-        <v>492717.75</v>
+        <v>48677.96</v>
       </c>
       <c r="J115" t="n">
-        <v>746016.3100000001</v>
+        <v>48677.96</v>
       </c>
       <c r="K115" t="n">
         <v>0</v>
@@ -4938,12 +4938,12 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Anadolu Sanayi Grubu A.Ş.</t>
+          <t>Gaziantep İhracat ve Toptan</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Ürün Delta Kompakt</t>
+          <t>Ürün Alpha Standart</t>
         </is>
       </c>
       <c r="C116" s="2" t="n">
@@ -4953,22 +4953,22 @@
         <v>6</v>
       </c>
       <c r="E116" t="n">
-        <v>1200</v>
+        <v>1850</v>
       </c>
       <c r="F116" t="n">
-        <v>35689.82</v>
+        <v>47584.04</v>
       </c>
       <c r="G116" t="n">
-        <v>4282.78</v>
+        <v>0</v>
       </c>
       <c r="H116" t="n">
-        <v>31407.04</v>
+        <v>32151.38</v>
       </c>
       <c r="I116" t="n">
-        <v>24388.04</v>
+        <v>47584.04</v>
       </c>
       <c r="J116" t="n">
-        <v>31407.04</v>
+        <v>47584.04</v>
       </c>
       <c r="K116" t="n">
         <v>0</v>
@@ -4977,37 +4977,37 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Karadeniz Toptan Dağıtım A.Ş.</t>
+          <t>Gaziantep İhracat ve Toptan</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Ürün Beta Premium</t>
+          <t>Ürün Delta Kompakt</t>
         </is>
       </c>
       <c r="C117" s="2" t="n">
         <v>45890</v>
       </c>
       <c r="D117" t="n">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="E117" t="n">
-        <v>4200</v>
+        <v>1200</v>
       </c>
       <c r="F117" t="n">
-        <v>333104.96</v>
+        <v>10288.44</v>
       </c>
       <c r="G117" t="n">
         <v>0</v>
       </c>
       <c r="H117" t="n">
-        <v>333104.96</v>
+        <v>7030.43</v>
       </c>
       <c r="I117" t="n">
-        <v>222069.97</v>
+        <v>10288.44</v>
       </c>
       <c r="J117" t="n">
-        <v>333104.96</v>
+        <v>10288.44</v>
       </c>
       <c r="K117" t="n">
         <v>0</v>
@@ -5016,37 +5016,37 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Karadeniz Toptan Dağıtım A.Ş.</t>
+          <t>Anadolu Sanayi Grubu A.Ş.</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Yedek Parça Servis Paketi</t>
+          <t>Özel Sipariş Modeli X</t>
         </is>
       </c>
       <c r="C118" s="2" t="n">
         <v>45892</v>
       </c>
       <c r="D118" t="n">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="E118" t="n">
-        <v>2400</v>
+        <v>21500</v>
       </c>
       <c r="F118" t="n">
-        <v>190345.69</v>
+        <v>184334.57</v>
       </c>
       <c r="G118" t="n">
-        <v>9517.280000000001</v>
+        <v>3962.09</v>
       </c>
       <c r="H118" t="n">
-        <v>180828.41</v>
+        <v>121746.55</v>
       </c>
       <c r="I118" t="n">
-        <v>118966.06</v>
+        <v>180372.48</v>
       </c>
       <c r="J118" t="n">
-        <v>180828.41</v>
+        <v>180372.48</v>
       </c>
       <c r="K118" t="n">
         <v>0</v>
@@ -5055,37 +5055,37 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Gaziantep İhracat ve Toptan</t>
+          <t>Bursa İmalat Tedarik Ltd.</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Ürün Epsilon Profesyonel</t>
+          <t>Ürün Delta Kompakt</t>
         </is>
       </c>
       <c r="C119" s="2" t="n">
         <v>45894</v>
       </c>
       <c r="D119" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="E119" t="n">
-        <v>15400</v>
+        <v>1200</v>
       </c>
       <c r="F119" t="n">
-        <v>229009.66</v>
+        <v>46297.98</v>
       </c>
       <c r="G119" t="n">
-        <v>27481.16</v>
+        <v>995.13</v>
       </c>
       <c r="H119" t="n">
-        <v>201528.5</v>
+        <v>31636.96</v>
       </c>
       <c r="I119" t="n">
-        <v>145733.42</v>
+        <v>45302.85</v>
       </c>
       <c r="J119" t="n">
-        <v>201528.5</v>
+        <v>45302.85</v>
       </c>
       <c r="K119" t="n">
         <v>0</v>
@@ -5094,37 +5094,37 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>İstanbul Kurumsal Tedarik A.Ş.</t>
+          <t>Adana Bölge Bayi A.Ş.</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Yedek Parça Servis Paketi</t>
+          <t>Özel Sipariş Modeli X</t>
         </is>
       </c>
       <c r="C120" s="2" t="n">
         <v>45896</v>
       </c>
       <c r="D120" t="n">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="E120" t="n">
-        <v>2400</v>
+        <v>21500</v>
       </c>
       <c r="F120" t="n">
-        <v>71379.63</v>
+        <v>1566843.83</v>
       </c>
       <c r="G120" t="n">
-        <v>2141.39</v>
+        <v>50516.61</v>
       </c>
       <c r="H120" t="n">
-        <v>69238.25</v>
+        <v>1034845.69</v>
       </c>
       <c r="I120" t="n">
-        <v>44612.27</v>
+        <v>1516327.22</v>
       </c>
       <c r="J120" t="n">
-        <v>69238.25</v>
+        <v>1516327.22</v>
       </c>
       <c r="K120" t="n">
         <v>0</v>
@@ -5133,37 +5133,37 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Gaziantep İhracat ve Toptan</t>
+          <t>İzmir Ticari Faaliyetler A.Ş.</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Yedek Parça Servis Paketi</t>
+          <t>Ürün Beta Premium</t>
         </is>
       </c>
       <c r="C121" s="2" t="n">
         <v>45898</v>
       </c>
       <c r="D121" t="n">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="E121" t="n">
-        <v>2400</v>
+        <v>4200</v>
       </c>
       <c r="F121" t="n">
-        <v>142759.27</v>
+        <v>396104.98</v>
       </c>
       <c r="G121" t="n">
         <v>0</v>
       </c>
       <c r="H121" t="n">
-        <v>142759.27</v>
+        <v>264069.99</v>
       </c>
       <c r="I121" t="n">
-        <v>89224.53999999999</v>
+        <v>396104.98</v>
       </c>
       <c r="J121" t="n">
-        <v>142759.27</v>
+        <v>396104.98</v>
       </c>
       <c r="K121" t="n">
         <v>0</v>
@@ -5172,37 +5172,37 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Güneydoğu Pazarlama Ltd.</t>
+          <t>Toroslar Lojistik ve Ticaret</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Ürün Alpha Standart</t>
+          <t>Ürün Zeta Hızlı Tüketim</t>
         </is>
       </c>
       <c r="C122" s="2" t="n">
         <v>45900</v>
       </c>
       <c r="D122" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="E122" t="n">
-        <v>1850</v>
+        <v>650</v>
       </c>
       <c r="F122" t="n">
-        <v>82532.7</v>
+        <v>44583.24</v>
       </c>
       <c r="G122" t="n">
-        <v>4126.64</v>
+        <v>2395.68</v>
       </c>
       <c r="H122" t="n">
-        <v>78406.07000000001</v>
+        <v>30179.43</v>
       </c>
       <c r="I122" t="n">
-        <v>55765.34</v>
+        <v>42187.56</v>
       </c>
       <c r="J122" t="n">
-        <v>78406.07000000001</v>
+        <v>42187.56</v>
       </c>
       <c r="K122" t="n">
         <v>0</v>
@@ -5216,32 +5216,32 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Ürün Epsilon Profesyonel</t>
+          <t>Ürün Gamma Endüstriyel</t>
         </is>
       </c>
       <c r="C123" s="2" t="n">
         <v>45902</v>
       </c>
       <c r="D123" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="E123" t="n">
-        <v>15400</v>
+        <v>8900</v>
       </c>
       <c r="F123" t="n">
-        <v>610692.4300000001</v>
+        <v>610447.5</v>
       </c>
       <c r="G123" t="n">
-        <v>18320.77</v>
+        <v>32802.4</v>
       </c>
       <c r="H123" t="n">
-        <v>592371.65</v>
+        <v>404678.68</v>
       </c>
       <c r="I123" t="n">
-        <v>388622.45</v>
+        <v>577645.1</v>
       </c>
       <c r="J123" t="n">
-        <v>592371.65</v>
+        <v>577645.1</v>
       </c>
       <c r="K123" t="n">
         <v>0</v>
@@ -5250,37 +5250,37 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Ankara Proje Yönetim ve Satış</t>
+          <t>İstanbul Kurumsal Tedarik A.Ş.</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Ürün Alpha Standart</t>
+          <t>Ürün Zeta Hızlı Tüketim</t>
         </is>
       </c>
       <c r="C124" s="2" t="n">
         <v>45904</v>
       </c>
       <c r="D124" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="E124" t="n">
-        <v>1850</v>
+        <v>650</v>
       </c>
       <c r="F124" t="n">
-        <v>45851.5</v>
+        <v>33437.43</v>
       </c>
       <c r="G124" t="n">
-        <v>5502.18</v>
+        <v>0</v>
       </c>
       <c r="H124" t="n">
-        <v>40349.32</v>
+        <v>22634.57</v>
       </c>
       <c r="I124" t="n">
-        <v>30980.74</v>
+        <v>33437.43</v>
       </c>
       <c r="J124" t="n">
-        <v>40349.32</v>
+        <v>33437.43</v>
       </c>
       <c r="K124" t="n">
         <v>0</v>
@@ -5289,37 +5289,37 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>İzmir Ticari Faaliyetler A.Ş.</t>
+          <t>Adana Bölge Bayi A.Ş.</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Ürün Beta Premium</t>
+          <t>Ürün Epsilon Profesyonel</t>
         </is>
       </c>
       <c r="C125" s="2" t="n">
         <v>45906</v>
       </c>
       <c r="D125" t="n">
-        <v>3</v>
+        <v>24</v>
       </c>
       <c r="E125" t="n">
-        <v>4200</v>
+        <v>15400</v>
       </c>
       <c r="F125" t="n">
-        <v>62457.18</v>
+        <v>1584419.92</v>
       </c>
       <c r="G125" t="n">
-        <v>7494.86</v>
+        <v>0</v>
       </c>
       <c r="H125" t="n">
-        <v>54962.32</v>
+        <v>1008267.22</v>
       </c>
       <c r="I125" t="n">
-        <v>41638.12</v>
+        <v>1584419.92</v>
       </c>
       <c r="J125" t="n">
-        <v>54962.32</v>
+        <v>1584419.92</v>
       </c>
       <c r="K125" t="n">
         <v>0</v>
@@ -5328,37 +5328,37 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>İç Anadolu Tüketim Malları</t>
+          <t>Karadeniz Toptan Dağıtım A.Ş.</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Yedek Parça Servis Paketi</t>
+          <t>Ürün Alpha Standart</t>
         </is>
       </c>
       <c r="C126" s="2" t="n">
         <v>45908</v>
       </c>
       <c r="D126" t="n">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="E126" t="n">
-        <v>2400</v>
+        <v>1850</v>
       </c>
       <c r="F126" t="n">
-        <v>297415.14</v>
+        <v>103098.75</v>
       </c>
       <c r="G126" t="n">
-        <v>23793.21</v>
+        <v>0</v>
       </c>
       <c r="H126" t="n">
-        <v>273621.93</v>
+        <v>69661.32000000001</v>
       </c>
       <c r="I126" t="n">
-        <v>185884.46</v>
+        <v>103098.75</v>
       </c>
       <c r="J126" t="n">
-        <v>273621.93</v>
+        <v>103098.75</v>
       </c>
       <c r="K126" t="n">
         <v>0</v>
@@ -5367,37 +5367,37 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Toroslar Lojistik ve Ticaret</t>
+          <t>Marmara Perakende Çözümleri</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Ürün Alpha Standart</t>
+          <t>Ürün Delta Kompakt</t>
         </is>
       </c>
       <c r="C127" s="2" t="n">
         <v>45910</v>
       </c>
       <c r="D127" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="E127" t="n">
-        <v>1850</v>
+        <v>1200</v>
       </c>
       <c r="F127" t="n">
-        <v>119213.9</v>
+        <v>41153.76</v>
       </c>
       <c r="G127" t="n">
-        <v>9537.110000000001</v>
+        <v>0</v>
       </c>
       <c r="H127" t="n">
-        <v>109676.79</v>
+        <v>28121.74</v>
       </c>
       <c r="I127" t="n">
-        <v>80549.92999999999</v>
+        <v>41153.76</v>
       </c>
       <c r="J127" t="n">
-        <v>109676.79</v>
+        <v>41153.76</v>
       </c>
       <c r="K127" t="n">
         <v>0</v>
@@ -5406,37 +5406,37 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Akdeniz Endüstriyel Ürünler</t>
+          <t>İzmir Ticari Faaliyetler A.Ş.</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Özel Sipariş Modeli X</t>
+          <t>Ürün Delta Kompakt</t>
         </is>
       </c>
       <c r="C128" s="2" t="n">
         <v>45912</v>
       </c>
       <c r="D128" t="n">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="E128" t="n">
-        <v>21500</v>
+        <v>1200</v>
       </c>
       <c r="F128" t="n">
-        <v>2024901.43</v>
+        <v>46297.98</v>
       </c>
       <c r="G128" t="n">
-        <v>0</v>
+        <v>1492.69</v>
       </c>
       <c r="H128" t="n">
-        <v>2024901.43</v>
+        <v>31636.96</v>
       </c>
       <c r="I128" t="n">
-        <v>1337376.76</v>
+        <v>44805.29</v>
       </c>
       <c r="J128" t="n">
-        <v>2024901.43</v>
+        <v>44805.29</v>
       </c>
       <c r="K128" t="n">
         <v>0</v>
@@ -5445,37 +5445,37 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Güneydoğu Pazarlama Ltd.</t>
+          <t>İstanbul Kurumsal Tedarik A.Ş.</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Ürün Epsilon Profesyonel</t>
+          <t>Ürün Alpha Standart</t>
         </is>
       </c>
       <c r="C129" s="2" t="n">
         <v>45914</v>
       </c>
       <c r="D129" t="n">
-        <v>3</v>
+        <v>25</v>
       </c>
       <c r="E129" t="n">
-        <v>15400</v>
+        <v>1850</v>
       </c>
       <c r="F129" t="n">
-        <v>229009.66</v>
+        <v>198266.83</v>
       </c>
       <c r="G129" t="n">
-        <v>11450.48</v>
+        <v>0</v>
       </c>
       <c r="H129" t="n">
-        <v>217559.18</v>
+        <v>133964.08</v>
       </c>
       <c r="I129" t="n">
-        <v>145733.42</v>
+        <v>198266.83</v>
       </c>
       <c r="J129" t="n">
-        <v>217559.18</v>
+        <v>198266.83</v>
       </c>
       <c r="K129" t="n">
         <v>0</v>
@@ -5484,37 +5484,37 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Gaziantep İhracat ve Toptan</t>
+          <t>Güneydoğu Pazarlama Ltd.</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Ürün Alpha Standart</t>
+          <t>Ürün Gamma Endüstriyel</t>
         </is>
       </c>
       <c r="C130" s="2" t="n">
         <v>45916</v>
       </c>
       <c r="D130" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="E130" t="n">
-        <v>1850</v>
+        <v>8900</v>
       </c>
       <c r="F130" t="n">
-        <v>155895.1</v>
+        <v>801212.34</v>
       </c>
       <c r="G130" t="n">
-        <v>12471.61</v>
+        <v>0</v>
       </c>
       <c r="H130" t="n">
-        <v>143423.5</v>
+        <v>531140.77</v>
       </c>
       <c r="I130" t="n">
-        <v>105334.53</v>
+        <v>801212.34</v>
       </c>
       <c r="J130" t="n">
-        <v>143423.5</v>
+        <v>801212.34</v>
       </c>
       <c r="K130" t="n">
         <v>0</v>
@@ -5523,37 +5523,37 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Gaziantep İhracat ve Toptan</t>
+          <t>Ankara Proje Yönetim ve Satış</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Ürün Gamma Endüstriyel</t>
+          <t>Ürün Alpha Standart</t>
         </is>
       </c>
       <c r="C131" s="2" t="n">
         <v>45918</v>
       </c>
       <c r="D131" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E131" t="n">
-        <v>8900</v>
+        <v>1850</v>
       </c>
       <c r="F131" t="n">
-        <v>176466.32</v>
+        <v>63445.39</v>
       </c>
       <c r="G131" t="n">
-        <v>8823.32</v>
+        <v>1363.7</v>
       </c>
       <c r="H131" t="n">
-        <v>167643</v>
+        <v>42868.5</v>
       </c>
       <c r="I131" t="n">
-        <v>116983.29</v>
+        <v>62081.69</v>
       </c>
       <c r="J131" t="n">
-        <v>167643</v>
+        <v>62081.69</v>
       </c>
       <c r="K131" t="n">
         <v>0</v>
@@ -5562,37 +5562,37 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Marmara Perakende Çözümleri</t>
+          <t>Ankara Proje Yönetim ve Satış</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Ürün Gamma Endüstriyel</t>
+          <t>Ürün Epsilon Profesyonel</t>
         </is>
       </c>
       <c r="C132" s="2" t="n">
         <v>45920</v>
       </c>
       <c r="D132" t="n">
-        <v>7</v>
+        <v>23</v>
       </c>
       <c r="E132" t="n">
-        <v>8900</v>
+        <v>15400</v>
       </c>
       <c r="F132" t="n">
-        <v>308816.06</v>
+        <v>1518402.42</v>
       </c>
       <c r="G132" t="n">
-        <v>0</v>
+        <v>32636.54</v>
       </c>
       <c r="H132" t="n">
-        <v>308816.06</v>
+        <v>966256.09</v>
       </c>
       <c r="I132" t="n">
-        <v>204720.76</v>
+        <v>1485765.88</v>
       </c>
       <c r="J132" t="n">
-        <v>308816.06</v>
+        <v>1485765.88</v>
       </c>
       <c r="K132" t="n">
         <v>0</v>
@@ -5601,37 +5601,37 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Marmara Perakende Çözümleri</t>
+          <t>Akdeniz Endüstriyel Ürünler</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Ürün Alpha Standart</t>
+          <t>Yedek Parça Servis Paketi</t>
         </is>
       </c>
       <c r="C133" s="2" t="n">
         <v>45922</v>
       </c>
       <c r="D133" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E133" t="n">
-        <v>1850</v>
+        <v>2400</v>
       </c>
       <c r="F133" t="n">
-        <v>128384.2</v>
+        <v>123461.29</v>
       </c>
       <c r="G133" t="n">
-        <v>0</v>
+        <v>3980.52</v>
       </c>
       <c r="H133" t="n">
-        <v>128384.2</v>
+        <v>77163.31</v>
       </c>
       <c r="I133" t="n">
-        <v>86746.08</v>
+        <v>119480.77</v>
       </c>
       <c r="J133" t="n">
-        <v>128384.2</v>
+        <v>119480.77</v>
       </c>
       <c r="K133" t="n">
         <v>0</v>
@@ -5640,37 +5640,37 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>İzmir Ticari Faaliyetler A.Ş.</t>
+          <t>Karadeniz Toptan Dağıtım A.Ş.</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Yedek Parça Servis Paketi</t>
+          <t>Ürün Delta Kompakt</t>
         </is>
       </c>
       <c r="C134" s="2" t="n">
         <v>45924</v>
       </c>
       <c r="D134" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="E134" t="n">
-        <v>2400</v>
+        <v>1200</v>
       </c>
       <c r="F134" t="n">
-        <v>83276.24000000001</v>
+        <v>77163.31</v>
       </c>
       <c r="G134" t="n">
-        <v>9993.15</v>
+        <v>1658.55</v>
       </c>
       <c r="H134" t="n">
-        <v>73283.09</v>
+        <v>52728.26</v>
       </c>
       <c r="I134" t="n">
-        <v>52047.65</v>
+        <v>75504.75999999999</v>
       </c>
       <c r="J134" t="n">
-        <v>73283.09</v>
+        <v>75504.75999999999</v>
       </c>
       <c r="K134" t="n">
         <v>0</v>
@@ -5679,37 +5679,37 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>Marmara Perakende Çözümleri</t>
+          <t>İzmir Ticari Faaliyetler A.Ş.</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Ürün Epsilon Profesyonel</t>
+          <t>Yedek Parça Servis Paketi</t>
         </is>
       </c>
       <c r="C135" s="2" t="n">
         <v>45926</v>
       </c>
       <c r="D135" t="n">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="E135" t="n">
-        <v>15400</v>
+        <v>2400</v>
       </c>
       <c r="F135" t="n">
-        <v>839702.08</v>
+        <v>195480.38</v>
       </c>
       <c r="G135" t="n">
-        <v>100764.25</v>
+        <v>0</v>
       </c>
       <c r="H135" t="n">
-        <v>738937.83</v>
+        <v>122175.24</v>
       </c>
       <c r="I135" t="n">
-        <v>534355.87</v>
+        <v>195480.38</v>
       </c>
       <c r="J135" t="n">
-        <v>738937.83</v>
+        <v>195480.38</v>
       </c>
       <c r="K135" t="n">
         <v>0</v>
@@ -5718,397 +5718,397 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Gaziantep İhracat ve Toptan</t>
+          <t>Anadolu Sanayi Grubu A.Ş.</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Ürün Beta Premium</t>
+          <t>Ürün Zeta Hızlı Tüketim</t>
         </is>
       </c>
       <c r="C136" s="2" t="n">
         <v>45928</v>
       </c>
       <c r="D136" t="n">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="E136" t="n">
-        <v>4200</v>
+        <v>650</v>
       </c>
       <c r="F136" t="n">
-        <v>62457.18</v>
+        <v>50156.15</v>
       </c>
       <c r="G136" t="n">
-        <v>3122.86</v>
+        <v>2695.14</v>
       </c>
       <c r="H136" t="n">
-        <v>59334.32</v>
+        <v>33951.86</v>
       </c>
       <c r="I136" t="n">
-        <v>41638.12</v>
+        <v>47461.01</v>
       </c>
       <c r="J136" t="n">
-        <v>29667.16</v>
+        <v>23730.51</v>
       </c>
       <c r="K136" t="n">
-        <v>29667.16</v>
+        <v>23730.5</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>Akdeniz Endüstriyel Ürünler</t>
+          <t>Ankara Proje Yönetim ve Satış</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Ürün Zeta Hızlı Tüketim</t>
+          <t>Ürün Epsilon Profesyonel</t>
         </is>
       </c>
       <c r="C137" s="2" t="n">
         <v>45931</v>
       </c>
       <c r="D137" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E137" t="n">
-        <v>650</v>
+        <v>15400</v>
       </c>
       <c r="F137" t="n">
-        <v>28997.98</v>
+        <v>660174.97</v>
       </c>
       <c r="G137" t="n">
-        <v>2319.84</v>
+        <v>0</v>
       </c>
       <c r="H137" t="n">
-        <v>26678.14</v>
+        <v>420111.34</v>
       </c>
       <c r="I137" t="n">
-        <v>19629.4</v>
+        <v>660174.97</v>
       </c>
       <c r="J137" t="n">
-        <v>8003.44</v>
+        <v>330087.48</v>
       </c>
       <c r="K137" t="n">
-        <v>18674.7</v>
+        <v>330087.49</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>Gaziantep İhracat ve Toptan</t>
+          <t>Güneydoğu Pazarlama Ltd.</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Ürün Alpha Standart</t>
+          <t>Ürün Beta Premium</t>
         </is>
       </c>
       <c r="C138" s="2" t="n">
         <v>45933</v>
       </c>
       <c r="D138" t="n">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="E138" t="n">
-        <v>1850</v>
+        <v>4200</v>
       </c>
       <c r="F138" t="n">
-        <v>210916.9</v>
+        <v>198052.49</v>
       </c>
       <c r="G138" t="n">
-        <v>16873.35</v>
+        <v>4256.94</v>
       </c>
       <c r="H138" t="n">
-        <v>194043.55</v>
+        <v>132034.99</v>
       </c>
       <c r="I138" t="n">
-        <v>142511.42</v>
+        <v>193795.55</v>
       </c>
       <c r="J138" t="n">
-        <v>97021.78</v>
+        <v>0</v>
       </c>
       <c r="K138" t="n">
-        <v>97021.78</v>
+        <v>193795.55</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>İstanbul Kurumsal Tedarik A.Ş.</t>
+          <t>İzmir Ticari Faaliyetler A.Ş.</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Yedek Parça Servis Paketi</t>
+          <t>Ürün Zeta Hızlı Tüketim</t>
         </is>
       </c>
       <c r="C139" s="2" t="n">
         <v>45935</v>
       </c>
       <c r="D139" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="E139" t="n">
-        <v>2400</v>
+        <v>650</v>
       </c>
       <c r="F139" t="n">
-        <v>47586.42</v>
+        <v>25078.07</v>
       </c>
       <c r="G139" t="n">
-        <v>2379.32</v>
+        <v>539.03</v>
       </c>
       <c r="H139" t="n">
-        <v>45207.1</v>
+        <v>16975.93</v>
       </c>
       <c r="I139" t="n">
-        <v>29741.51</v>
+        <v>24539.04</v>
       </c>
       <c r="J139" t="n">
-        <v>0</v>
+        <v>12269.52</v>
       </c>
       <c r="K139" t="n">
-        <v>45207.1</v>
+        <v>12269.52</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>Marmara Perakende Çözümleri</t>
+          <t>İzmir Ticari Faaliyetler A.Ş.</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Ürün Beta Premium</t>
+          <t>Ürün Epsilon Profesyonel</t>
         </is>
       </c>
       <c r="C140" s="2" t="n">
         <v>45937</v>
       </c>
       <c r="D140" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E140" t="n">
-        <v>4200</v>
+        <v>15400</v>
       </c>
       <c r="F140" t="n">
-        <v>83276.24000000001</v>
+        <v>462122.48</v>
       </c>
       <c r="G140" t="n">
-        <v>6662.1</v>
+        <v>0</v>
       </c>
       <c r="H140" t="n">
-        <v>76614.14</v>
+        <v>294077.94</v>
       </c>
       <c r="I140" t="n">
-        <v>55517.49</v>
+        <v>462122.48</v>
       </c>
       <c r="J140" t="n">
         <v>0</v>
       </c>
       <c r="K140" t="n">
-        <v>76614.14</v>
+        <v>462122.48</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>Kocaeli Ağır Sanayi Pazarlama</t>
+          <t>İstanbul Kurumsal Tedarik A.Ş.</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Ürün Epsilon Profesyonel</t>
+          <t>Ürün Delta Kompakt</t>
         </is>
       </c>
       <c r="C141" s="2" t="n">
         <v>45939</v>
       </c>
       <c r="D141" t="n">
-        <v>18</v>
+        <v>2</v>
       </c>
       <c r="E141" t="n">
-        <v>15400</v>
+        <v>1200</v>
       </c>
       <c r="F141" t="n">
-        <v>1374057.96</v>
+        <v>10288.44</v>
       </c>
       <c r="G141" t="n">
-        <v>41221.74</v>
+        <v>552.85</v>
       </c>
       <c r="H141" t="n">
-        <v>1332836.22</v>
+        <v>7030.43</v>
       </c>
       <c r="I141" t="n">
-        <v>874400.52</v>
+        <v>9735.59</v>
       </c>
       <c r="J141" t="n">
-        <v>399850.87</v>
+        <v>4867.8</v>
       </c>
       <c r="K141" t="n">
-        <v>932985.35</v>
+        <v>4867.79</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>Karadeniz Toptan Dağıtım A.Ş.</t>
+          <t>Akdeniz Endüstriyel Ürünler</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Yedek Parça Servis Paketi</t>
+          <t>Ürün Zeta Hızlı Tüketim</t>
         </is>
       </c>
       <c r="C142" s="2" t="n">
         <v>45941</v>
       </c>
       <c r="D142" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E142" t="n">
-        <v>2400</v>
+        <v>650</v>
       </c>
       <c r="F142" t="n">
-        <v>249828.72</v>
+        <v>61301.96</v>
       </c>
       <c r="G142" t="n">
-        <v>12491.44</v>
+        <v>0</v>
       </c>
       <c r="H142" t="n">
-        <v>237337.28</v>
+        <v>41496.71</v>
       </c>
       <c r="I142" t="n">
-        <v>156142.95</v>
+        <v>61301.96</v>
       </c>
       <c r="J142" t="n">
-        <v>118668.64</v>
+        <v>0</v>
       </c>
       <c r="K142" t="n">
-        <v>118668.64</v>
+        <v>61301.96</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>Ankara Proje Yönetim ve Satış</t>
+          <t>Bursa İmalat Tedarik Ltd.</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Özel Sipariş Modeli X</t>
+          <t>Ürün Alpha Standart</t>
         </is>
       </c>
       <c r="C143" s="2" t="n">
         <v>45943</v>
       </c>
       <c r="D143" t="n">
-        <v>2</v>
+        <v>21</v>
       </c>
       <c r="E143" t="n">
-        <v>21500</v>
+        <v>1850</v>
       </c>
       <c r="F143" t="n">
-        <v>213147.52</v>
+        <v>166544.14</v>
       </c>
       <c r="G143" t="n">
-        <v>0</v>
+        <v>5369.55</v>
       </c>
       <c r="H143" t="n">
-        <v>213147.52</v>
+        <v>112529.82</v>
       </c>
       <c r="I143" t="n">
-        <v>140776.5</v>
+        <v>161174.59</v>
       </c>
       <c r="J143" t="n">
-        <v>63944.26</v>
+        <v>80587.28999999999</v>
       </c>
       <c r="K143" t="n">
-        <v>149203.26</v>
+        <v>80587.3</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>Akdeniz Endüstriyel Ürünler</t>
+          <t>Karadeniz Toptan Dağıtım A.Ş.</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Ürün Gamma Endüstriyel</t>
+          <t>Ürün Epsilon Profesyonel</t>
         </is>
       </c>
       <c r="C144" s="2" t="n">
         <v>45945</v>
       </c>
       <c r="D144" t="n">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="E144" t="n">
-        <v>8900</v>
+        <v>15400</v>
       </c>
       <c r="F144" t="n">
-        <v>882331.59</v>
+        <v>924244.95</v>
       </c>
       <c r="G144" t="n">
-        <v>70586.53</v>
+        <v>29798.58</v>
       </c>
       <c r="H144" t="n">
-        <v>811745.0600000001</v>
+        <v>588155.88</v>
       </c>
       <c r="I144" t="n">
-        <v>584916.45</v>
+        <v>894446.37</v>
       </c>
       <c r="J144" t="n">
-        <v>405872.53</v>
+        <v>0</v>
       </c>
       <c r="K144" t="n">
-        <v>405872.53</v>
+        <v>894446.37</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>Bursa İmalat Tedarik Ltd.</t>
+          <t>Akdeniz Endüstriyel Ürünler</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Yedek Parça Servis Paketi</t>
+          <t>Ürün Alpha Standart</t>
         </is>
       </c>
       <c r="C145" s="2" t="n">
         <v>45947</v>
       </c>
       <c r="D145" t="n">
-        <v>2</v>
+        <v>19</v>
       </c>
       <c r="E145" t="n">
-        <v>2400</v>
+        <v>1850</v>
       </c>
       <c r="F145" t="n">
-        <v>23793.21</v>
+        <v>150682.79</v>
       </c>
       <c r="G145" t="n">
-        <v>1189.66</v>
+        <v>8096.94</v>
       </c>
       <c r="H145" t="n">
-        <v>22603.55</v>
+        <v>101812.7</v>
       </c>
       <c r="I145" t="n">
-        <v>14870.76</v>
+        <v>142585.85</v>
       </c>
       <c r="J145" t="n">
-        <v>6781.07</v>
+        <v>0</v>
       </c>
       <c r="K145" t="n">
-        <v>15822.49</v>
+        <v>142585.85</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>Bursa İmalat Tedarik Ltd.</t>
+          <t>Adana Bölge Bayi A.Ş.</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -6120,73 +6120,73 @@
         <v>45949</v>
       </c>
       <c r="D146" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="E146" t="n">
         <v>1200</v>
       </c>
       <c r="F146" t="n">
-        <v>11896.61</v>
+        <v>56586.43</v>
       </c>
       <c r="G146" t="n">
-        <v>1427.59</v>
+        <v>0</v>
       </c>
       <c r="H146" t="n">
-        <v>10469.01</v>
+        <v>38667.39</v>
       </c>
       <c r="I146" t="n">
-        <v>8129.35</v>
+        <v>56586.43</v>
       </c>
       <c r="J146" t="n">
-        <v>3140.7</v>
+        <v>28293.22</v>
       </c>
       <c r="K146" t="n">
-        <v>7328.31</v>
+        <v>28293.21</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>Gaziantep İhracat ve Toptan</t>
+          <t>İzmir Ticari Faaliyetler A.Ş.</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Ürün Epsilon Profesyonel</t>
+          <t>Özel Sipariş Modeli X</t>
         </is>
       </c>
       <c r="C147" s="2" t="n">
         <v>45951</v>
       </c>
       <c r="D147" t="n">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="E147" t="n">
-        <v>15400</v>
+        <v>21500</v>
       </c>
       <c r="F147" t="n">
-        <v>916038.64</v>
+        <v>2027680.25</v>
       </c>
       <c r="G147" t="n">
-        <v>0</v>
+        <v>43582.96</v>
       </c>
       <c r="H147" t="n">
-        <v>916038.64</v>
+        <v>1339212.07</v>
       </c>
       <c r="I147" t="n">
-        <v>582933.6800000001</v>
+        <v>1984097.29</v>
       </c>
       <c r="J147" t="n">
-        <v>274811.59</v>
+        <v>0</v>
       </c>
       <c r="K147" t="n">
-        <v>641227.05</v>
+        <v>1984097.29</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>Adana Bölge Bayi A.Ş.</t>
+          <t>İstanbul Kurumsal Tedarik A.Ş.</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -6198,229 +6198,229 @@
         <v>45953</v>
       </c>
       <c r="D148" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E148" t="n">
         <v>15400</v>
       </c>
       <c r="F148" t="n">
-        <v>763365.53</v>
+        <v>396104.98</v>
       </c>
       <c r="G148" t="n">
-        <v>22900.97</v>
+        <v>21284.7</v>
       </c>
       <c r="H148" t="n">
-        <v>740464.5699999999</v>
+        <v>252066.81</v>
       </c>
       <c r="I148" t="n">
-        <v>485778.07</v>
+        <v>374820.28</v>
       </c>
       <c r="J148" t="n">
-        <v>222139.37</v>
+        <v>112446.08</v>
       </c>
       <c r="K148" t="n">
-        <v>518325.2</v>
+        <v>262374.2</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>Adana Bölge Bayi A.Ş.</t>
+          <t>Marmara Perakende Çözümleri</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Ürün Beta Premium</t>
+          <t>Ürün Epsilon Profesyonel</t>
         </is>
       </c>
       <c r="C149" s="2" t="n">
         <v>45955</v>
       </c>
       <c r="D149" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E149" t="n">
-        <v>4200</v>
+        <v>15400</v>
       </c>
       <c r="F149" t="n">
-        <v>166552.48</v>
+        <v>264069.99</v>
       </c>
       <c r="G149" t="n">
-        <v>0</v>
+        <v>8513.879999999999</v>
       </c>
       <c r="H149" t="n">
-        <v>166552.48</v>
+        <v>168044.54</v>
       </c>
       <c r="I149" t="n">
-        <v>111034.99</v>
+        <v>255556.11</v>
       </c>
       <c r="J149" t="n">
-        <v>49965.74</v>
+        <v>76666.83</v>
       </c>
       <c r="K149" t="n">
-        <v>116586.74</v>
+        <v>178889.28</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>Bursa İmalat Tedarik Ltd.</t>
+          <t>Marmara Perakende Çözümleri</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Özel Sipariş Modeli X</t>
+          <t>Ürün Epsilon Profesyonel</t>
         </is>
       </c>
       <c r="C150" s="2" t="n">
         <v>45957</v>
       </c>
       <c r="D150" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E150" t="n">
-        <v>21500</v>
+        <v>15400</v>
       </c>
       <c r="F150" t="n">
-        <v>2664343.98</v>
+        <v>1584419.92</v>
       </c>
       <c r="G150" t="n">
-        <v>79930.32000000001</v>
+        <v>85138.81</v>
       </c>
       <c r="H150" t="n">
-        <v>2584413.66</v>
+        <v>1008267.22</v>
       </c>
       <c r="I150" t="n">
-        <v>1759706.26</v>
+        <v>1499281.11</v>
       </c>
       <c r="J150" t="n">
-        <v>775324.1</v>
+        <v>449784.33</v>
       </c>
       <c r="K150" t="n">
-        <v>1809089.56</v>
+        <v>1049496.78</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>Bursa İmalat Tedarik Ltd.</t>
+          <t>Kocaeli Ağır Sanayi Pazarlama</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Yedek Parça Servis Paketi</t>
+          <t>Ürün Gamma Endüstriyel</t>
         </is>
       </c>
       <c r="C151" s="2" t="n">
         <v>45959</v>
       </c>
       <c r="D151" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="E151" t="n">
-        <v>2400</v>
+        <v>8900</v>
       </c>
       <c r="F151" t="n">
-        <v>237932.11</v>
+        <v>839365.3100000001</v>
       </c>
       <c r="G151" t="n">
-        <v>28551.85</v>
+        <v>18041.32</v>
       </c>
       <c r="H151" t="n">
-        <v>209380.26</v>
+        <v>556433.1899999999</v>
       </c>
       <c r="I151" t="n">
-        <v>148707.57</v>
+        <v>821323.99</v>
       </c>
       <c r="J151" t="n">
         <v>0</v>
       </c>
       <c r="K151" t="n">
-        <v>209380.26</v>
+        <v>821323.99</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>Toroslar Lojistik ve Ticaret</t>
+          <t>İzmir Ticari Faaliyetler A.Ş.</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Özel Sipariş Modeli X</t>
+          <t>Ürün Beta Premium</t>
         </is>
       </c>
       <c r="C152" s="2" t="n">
         <v>45961</v>
       </c>
       <c r="D152" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E152" t="n">
-        <v>21500</v>
+        <v>4200</v>
       </c>
       <c r="F152" t="n">
-        <v>746016.3100000001</v>
+        <v>144038.17</v>
       </c>
       <c r="G152" t="n">
-        <v>37300.82</v>
+        <v>3095.96</v>
       </c>
       <c r="H152" t="n">
-        <v>708715.5</v>
+        <v>96025.45</v>
       </c>
       <c r="I152" t="n">
-        <v>492717.75</v>
+        <v>140942.21</v>
       </c>
       <c r="J152" t="n">
-        <v>354357.75</v>
+        <v>70471.10000000001</v>
       </c>
       <c r="K152" t="n">
-        <v>354357.75</v>
+        <v>70471.11</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>Güneydoğu Pazarlama Ltd.</t>
+          <t>Toroslar Lojistik ve Ticaret</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>Ürün Zeta Hızlı Tüketim</t>
+          <t>Ürün Epsilon Profesyonel</t>
         </is>
       </c>
       <c r="C153" s="2" t="n">
         <v>45963</v>
       </c>
       <c r="D153" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="E153" t="n">
-        <v>650</v>
+        <v>15400</v>
       </c>
       <c r="F153" t="n">
-        <v>6443.99</v>
+        <v>924244.95</v>
       </c>
       <c r="G153" t="n">
-        <v>515.52</v>
+        <v>19865.72</v>
       </c>
       <c r="H153" t="n">
-        <v>5928.48</v>
+        <v>588155.88</v>
       </c>
       <c r="I153" t="n">
-        <v>4362.09</v>
+        <v>904379.23</v>
       </c>
       <c r="J153" t="n">
-        <v>0</v>
+        <v>271313.77</v>
       </c>
       <c r="K153" t="n">
-        <v>5928.48</v>
+        <v>633065.46</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>Ege Dağıtım ve Ticaret Ltd.</t>
+          <t>İç Anadolu Tüketim Malları</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -6432,67 +6432,67 @@
         <v>45965</v>
       </c>
       <c r="D154" t="n">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="E154" t="n">
         <v>15400</v>
       </c>
       <c r="F154" t="n">
-        <v>1755740.72</v>
+        <v>1254332.43</v>
       </c>
       <c r="G154" t="n">
-        <v>140459.26</v>
+        <v>26960.62</v>
       </c>
       <c r="H154" t="n">
-        <v>1615281.46</v>
+        <v>798211.55</v>
       </c>
       <c r="I154" t="n">
-        <v>1117289.55</v>
+        <v>1227371.81</v>
       </c>
       <c r="J154" t="n">
-        <v>484584.44</v>
+        <v>368211.54</v>
       </c>
       <c r="K154" t="n">
-        <v>1130697.03</v>
+        <v>859160.27</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>Marmara Perakende Çözümleri</t>
+          <t>Güneydoğu Pazarlama Ltd.</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>Ürün Alpha Standart</t>
+          <t>Ürün Beta Premium</t>
         </is>
       </c>
       <c r="C155" s="2" t="n">
         <v>45967</v>
       </c>
       <c r="D155" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="E155" t="n">
-        <v>1850</v>
+        <v>4200</v>
       </c>
       <c r="F155" t="n">
-        <v>55021.8</v>
+        <v>288076.35</v>
       </c>
       <c r="G155" t="n">
         <v>0</v>
       </c>
       <c r="H155" t="n">
-        <v>55021.8</v>
+        <v>192050.9</v>
       </c>
       <c r="I155" t="n">
-        <v>37176.89</v>
+        <v>288076.35</v>
       </c>
       <c r="J155" t="n">
-        <v>0</v>
+        <v>144038.17</v>
       </c>
       <c r="K155" t="n">
-        <v>55021.8</v>
+        <v>144038.18</v>
       </c>
     </row>
     <row r="156">
@@ -6503,152 +6503,152 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>Ürün Alpha Standart</t>
+          <t>Ürün Beta Premium</t>
         </is>
       </c>
       <c r="C156" s="2" t="n">
         <v>45969</v>
       </c>
       <c r="D156" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="E156" t="n">
-        <v>1850</v>
+        <v>4200</v>
       </c>
       <c r="F156" t="n">
-        <v>73362.39999999999</v>
+        <v>288076.35</v>
       </c>
       <c r="G156" t="n">
         <v>0</v>
       </c>
       <c r="H156" t="n">
-        <v>73362.39999999999</v>
+        <v>192050.9</v>
       </c>
       <c r="I156" t="n">
-        <v>49569.19</v>
+        <v>288076.35</v>
       </c>
       <c r="J156" t="n">
-        <v>22008.72</v>
+        <v>0</v>
       </c>
       <c r="K156" t="n">
-        <v>51353.68</v>
+        <v>288076.35</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>Anadolu Sanayi Grubu A.Ş.</t>
+          <t>İstanbul Kurumsal Tedarik A.Ş.</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>Ürün Zeta Hızlı Tüketim</t>
+          <t>Ürün Beta Premium</t>
         </is>
       </c>
       <c r="C157" s="2" t="n">
         <v>45971</v>
       </c>
       <c r="D157" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E157" t="n">
-        <v>650</v>
+        <v>4200</v>
       </c>
       <c r="F157" t="n">
-        <v>74105.94</v>
+        <v>396104.98</v>
       </c>
       <c r="G157" t="n">
-        <v>0</v>
+        <v>12770.82</v>
       </c>
       <c r="H157" t="n">
-        <v>74105.94</v>
+        <v>264069.99</v>
       </c>
       <c r="I157" t="n">
-        <v>50164.02</v>
+        <v>383334.16</v>
       </c>
       <c r="J157" t="n">
-        <v>22231.78</v>
+        <v>0</v>
       </c>
       <c r="K157" t="n">
-        <v>51874.16</v>
+        <v>383334.16</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>İç Anadolu Tüketim Malları</t>
+          <t>İstanbul Kurumsal Tedarik A.Ş.</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>Özel Sipariş Modeli X</t>
+          <t>Ürün Epsilon Profesyonel</t>
         </is>
       </c>
       <c r="C158" s="2" t="n">
         <v>45973</v>
       </c>
       <c r="D158" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="E158" t="n">
-        <v>21500</v>
+        <v>15400</v>
       </c>
       <c r="F158" t="n">
-        <v>1811753.91</v>
+        <v>924244.95</v>
       </c>
       <c r="G158" t="n">
-        <v>90587.7</v>
+        <v>0</v>
       </c>
       <c r="H158" t="n">
-        <v>1721166.21</v>
+        <v>588155.88</v>
       </c>
       <c r="I158" t="n">
-        <v>1196600.26</v>
+        <v>924244.95</v>
       </c>
       <c r="J158" t="n">
-        <v>860583.11</v>
+        <v>462122.47</v>
       </c>
       <c r="K158" t="n">
-        <v>860583.11</v>
+        <v>462122.48</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>Gaziantep İhracat ve Toptan</t>
+          <t>Adana Bölge Bayi A.Ş.</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>Ürün Beta Premium</t>
+          <t>Ürün Gamma Endüstriyel</t>
         </is>
       </c>
       <c r="C159" s="2" t="n">
         <v>45975</v>
       </c>
       <c r="D159" t="n">
-        <v>22</v>
+        <v>5</v>
       </c>
       <c r="E159" t="n">
-        <v>4200</v>
+        <v>8900</v>
       </c>
       <c r="F159" t="n">
-        <v>458019.32</v>
+        <v>190764.84</v>
       </c>
       <c r="G159" t="n">
         <v>0</v>
       </c>
       <c r="H159" t="n">
-        <v>458019.32</v>
+        <v>126462.09</v>
       </c>
       <c r="I159" t="n">
-        <v>305346.21</v>
+        <v>190764.84</v>
       </c>
       <c r="J159" t="n">
-        <v>0</v>
+        <v>95382.42</v>
       </c>
       <c r="K159" t="n">
-        <v>458019.32</v>
+        <v>95382.42</v>
       </c>
     </row>
     <row r="160">
@@ -6659,548 +6659,548 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>Özel Sipariş Modeli X</t>
+          <t>Yedek Parça Servis Paketi</t>
         </is>
       </c>
       <c r="C160" s="2" t="n">
         <v>45977</v>
       </c>
       <c r="D160" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E160" t="n">
-        <v>21500</v>
+        <v>2400</v>
       </c>
       <c r="F160" t="n">
-        <v>2131475.19</v>
+        <v>195480.38</v>
       </c>
       <c r="G160" t="n">
-        <v>106573.76</v>
+        <v>6302.48</v>
       </c>
       <c r="H160" t="n">
-        <v>2024901.43</v>
+        <v>122175.24</v>
       </c>
       <c r="I160" t="n">
-        <v>1407765.01</v>
+        <v>189177.9</v>
       </c>
       <c r="J160" t="n">
-        <v>0</v>
+        <v>94588.95</v>
       </c>
       <c r="K160" t="n">
-        <v>2024901.43</v>
+        <v>94588.95</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>Adana Bölge Bayi A.Ş.</t>
+          <t>Marmara Perakende Çözümleri</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>Özel Sipariş Modeli X</t>
+          <t>Ürün Zeta Hızlı Tüketim</t>
         </is>
       </c>
       <c r="C161" s="2" t="n">
         <v>45979</v>
       </c>
       <c r="D161" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="E161" t="n">
-        <v>21500</v>
+        <v>650</v>
       </c>
       <c r="F161" t="n">
-        <v>2024901.43</v>
+        <v>64088.41</v>
       </c>
       <c r="G161" t="n">
-        <v>161992.11</v>
+        <v>0</v>
       </c>
       <c r="H161" t="n">
-        <v>1862909.31</v>
+        <v>43382.93</v>
       </c>
       <c r="I161" t="n">
-        <v>1337376.76</v>
+        <v>64088.41</v>
       </c>
       <c r="J161" t="n">
-        <v>558872.79</v>
+        <v>0</v>
       </c>
       <c r="K161" t="n">
-        <v>1304036.52</v>
+        <v>64088.41</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>İç Anadolu Tüketim Malları</t>
+          <t>Kocaeli Ağır Sanayi Pazarlama</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>Ürün Gamma Endüstriyel</t>
+          <t>Ürün Beta Premium</t>
         </is>
       </c>
       <c r="C162" s="2" t="n">
         <v>45981</v>
       </c>
       <c r="D162" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="E162" t="n">
-        <v>8900</v>
+        <v>4200</v>
       </c>
       <c r="F162" t="n">
-        <v>397049.21</v>
+        <v>288076.35</v>
       </c>
       <c r="G162" t="n">
-        <v>47645.91</v>
+        <v>6191.91</v>
       </c>
       <c r="H162" t="n">
-        <v>349403.31</v>
+        <v>192050.9</v>
       </c>
       <c r="I162" t="n">
-        <v>263212.4</v>
+        <v>281884.44</v>
       </c>
       <c r="J162" t="n">
-        <v>174701.65</v>
+        <v>84565.33</v>
       </c>
       <c r="K162" t="n">
-        <v>174701.65</v>
+        <v>197319.11</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>Ege Dağıtım ve Ticaret Ltd.</t>
+          <t>İzmir Ticari Faaliyetler A.Ş.</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>Ürün Epsilon Profesyonel</t>
+          <t>Ürün Gamma Endüstriyel</t>
         </is>
       </c>
       <c r="C163" s="2" t="n">
         <v>45983</v>
       </c>
       <c r="D163" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="E163" t="n">
-        <v>15400</v>
+        <v>8900</v>
       </c>
       <c r="F163" t="n">
-        <v>76336.55</v>
+        <v>419682.66</v>
       </c>
       <c r="G163" t="n">
-        <v>3816.83</v>
+        <v>0</v>
       </c>
       <c r="H163" t="n">
-        <v>72519.73</v>
+        <v>278216.59</v>
       </c>
       <c r="I163" t="n">
-        <v>48577.81</v>
+        <v>419682.66</v>
       </c>
       <c r="J163" t="n">
-        <v>0</v>
+        <v>125904.8</v>
       </c>
       <c r="K163" t="n">
-        <v>72519.73</v>
+        <v>293777.86</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>Marmara Perakende Çözümleri</t>
+          <t>Anadolu Sanayi Grubu A.Ş.</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>Ürün Delta Kompakt</t>
+          <t>Özel Sipariş Modeli X</t>
         </is>
       </c>
       <c r="C164" s="2" t="n">
         <v>45985</v>
       </c>
       <c r="D164" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E164" t="n">
-        <v>1200</v>
+        <v>21500</v>
       </c>
       <c r="F164" t="n">
-        <v>47586.42</v>
+        <v>829505.5600000001</v>
       </c>
       <c r="G164" t="n">
-        <v>5710.37</v>
+        <v>0</v>
       </c>
       <c r="H164" t="n">
-        <v>41876.05</v>
+        <v>547859.48</v>
       </c>
       <c r="I164" t="n">
-        <v>32517.39</v>
+        <v>829505.5600000001</v>
       </c>
       <c r="J164" t="n">
-        <v>0</v>
+        <v>414752.78</v>
       </c>
       <c r="K164" t="n">
-        <v>41876.05</v>
+        <v>414752.78</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>İzmir Ticari Faaliyetler A.Ş.</t>
+          <t>Kocaeli Ağır Sanayi Pazarlama</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>Ürün Delta Kompakt</t>
+          <t>Ürün Gamma Endüstriyel</t>
         </is>
       </c>
       <c r="C165" s="2" t="n">
         <v>45987</v>
       </c>
       <c r="D165" t="n">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="E165" t="n">
-        <v>1200</v>
+        <v>8900</v>
       </c>
       <c r="F165" t="n">
-        <v>53534.73</v>
+        <v>724906.41</v>
       </c>
       <c r="G165" t="n">
-        <v>6424.17</v>
+        <v>0</v>
       </c>
       <c r="H165" t="n">
-        <v>47110.56</v>
+        <v>480555.93</v>
       </c>
       <c r="I165" t="n">
-        <v>36582.06</v>
+        <v>724906.41</v>
       </c>
       <c r="J165" t="n">
-        <v>14133.17</v>
+        <v>0</v>
       </c>
       <c r="K165" t="n">
-        <v>32977.39</v>
+        <v>724906.41</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>İstanbul Kurumsal Tedarik A.Ş.</t>
+          <t>Güneydoğu Pazarlama Ltd.</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>Ürün Alpha Standart</t>
+          <t>Ürün Beta Premium</t>
         </is>
       </c>
       <c r="C166" s="2" t="n">
         <v>45989</v>
       </c>
       <c r="D166" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="E166" t="n">
-        <v>1850</v>
+        <v>4200</v>
       </c>
       <c r="F166" t="n">
-        <v>229257.51</v>
+        <v>90023.86</v>
       </c>
       <c r="G166" t="n">
-        <v>27510.9</v>
+        <v>4837.43</v>
       </c>
       <c r="H166" t="n">
-        <v>201746.6</v>
+        <v>60015.91</v>
       </c>
       <c r="I166" t="n">
-        <v>154903.72</v>
+        <v>85186.42999999999</v>
       </c>
       <c r="J166" t="n">
-        <v>0</v>
+        <v>42593.21</v>
       </c>
       <c r="K166" t="n">
-        <v>201746.6</v>
+        <v>42593.22</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>Güneydoğu Pazarlama Ltd.</t>
+          <t>Akdeniz Endüstriyel Ürünler</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>Ürün Gamma Endüstriyel</t>
+          <t>Yedek Parça Servis Paketi</t>
         </is>
       </c>
       <c r="C167" s="2" t="n">
         <v>45991</v>
       </c>
       <c r="D167" t="n">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="E167" t="n">
-        <v>8900</v>
+        <v>2400</v>
       </c>
       <c r="F167" t="n">
-        <v>926448.17</v>
+        <v>133749.73</v>
       </c>
       <c r="G167" t="n">
-        <v>0</v>
+        <v>4312.23</v>
       </c>
       <c r="H167" t="n">
-        <v>926448.17</v>
+        <v>83593.58</v>
       </c>
       <c r="I167" t="n">
-        <v>614162.27</v>
+        <v>129437.5</v>
       </c>
       <c r="J167" t="n">
-        <v>463224.08</v>
+        <v>64718.75</v>
       </c>
       <c r="K167" t="n">
-        <v>463224.08</v>
+        <v>64718.75</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>Kocaeli Ağır Sanayi Pazarlama</t>
+          <t>Güneydoğu Pazarlama Ltd.</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>Ürün Alpha Standart</t>
+          <t>Yedek Parça Servis Paketi</t>
         </is>
       </c>
       <c r="C168" s="2" t="n">
         <v>45993</v>
       </c>
       <c r="D168" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="E168" t="n">
-        <v>1850</v>
+        <v>2400</v>
       </c>
       <c r="F168" t="n">
-        <v>73362.39999999999</v>
+        <v>10288.44</v>
       </c>
       <c r="G168" t="n">
-        <v>2200.87</v>
+        <v>0</v>
       </c>
       <c r="H168" t="n">
-        <v>71161.53</v>
+        <v>6430.28</v>
       </c>
       <c r="I168" t="n">
-        <v>49569.19</v>
+        <v>10288.44</v>
       </c>
       <c r="J168" t="n">
-        <v>35580.76</v>
+        <v>3086.53</v>
       </c>
       <c r="K168" t="n">
-        <v>35580.76</v>
+        <v>7201.91</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>Kocaeli Ağır Sanayi Pazarlama</t>
+          <t>İstanbul Kurumsal Tedarik A.Ş.</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>Ürün Epsilon Profesyonel</t>
+          <t>Ürün Delta Kompakt</t>
         </is>
       </c>
       <c r="C169" s="2" t="n">
         <v>45995</v>
       </c>
       <c r="D169" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E169" t="n">
-        <v>15400</v>
+        <v>1200</v>
       </c>
       <c r="F169" t="n">
-        <v>1755740.72</v>
+        <v>123461.29</v>
       </c>
       <c r="G169" t="n">
-        <v>210688.89</v>
+        <v>2653.68</v>
       </c>
       <c r="H169" t="n">
-        <v>1545051.84</v>
+        <v>84365.22</v>
       </c>
       <c r="I169" t="n">
-        <v>1117289.55</v>
+        <v>120807.61</v>
       </c>
       <c r="J169" t="n">
-        <v>772525.92</v>
+        <v>60403.81</v>
       </c>
       <c r="K169" t="n">
-        <v>772525.92</v>
+        <v>60403.8</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>Karadeniz Toptan Dağıtım A.Ş.</t>
+          <t>Anadolu Sanayi Grubu A.Ş.</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>Yedek Parça Servis Paketi</t>
+          <t>Ürün Zeta Hızlı Tüketim</t>
         </is>
       </c>
       <c r="C170" s="2" t="n">
         <v>45997</v>
       </c>
       <c r="D170" t="n">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="E170" t="n">
-        <v>2400</v>
+        <v>650</v>
       </c>
       <c r="F170" t="n">
-        <v>154655.87</v>
+        <v>69661.32000000001</v>
       </c>
       <c r="G170" t="n">
-        <v>4639.68</v>
+        <v>3743.25</v>
       </c>
       <c r="H170" t="n">
-        <v>150016.2</v>
+        <v>47155.35</v>
       </c>
       <c r="I170" t="n">
-        <v>96659.92</v>
+        <v>65918.07000000001</v>
       </c>
       <c r="J170" t="n">
-        <v>45004.86</v>
+        <v>32959.04</v>
       </c>
       <c r="K170" t="n">
-        <v>105011.34</v>
+        <v>32959.03</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>Karadeniz Toptan Dağıtım A.Ş.</t>
+          <t>Toroslar Lojistik ve Ticaret</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>Ürün Delta Kompakt</t>
+          <t>Ürün Alpha Standart</t>
         </is>
       </c>
       <c r="C171" s="2" t="n">
         <v>45999</v>
       </c>
       <c r="D171" t="n">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="E171" t="n">
-        <v>1200</v>
+        <v>1850</v>
       </c>
       <c r="F171" t="n">
-        <v>89224.53999999999</v>
+        <v>174474.81</v>
       </c>
       <c r="G171" t="n">
-        <v>2676.74</v>
+        <v>0</v>
       </c>
       <c r="H171" t="n">
-        <v>86547.81</v>
+        <v>117888.39</v>
       </c>
       <c r="I171" t="n">
-        <v>60970.1</v>
+        <v>174474.81</v>
       </c>
       <c r="J171" t="n">
-        <v>43273.9</v>
+        <v>87237.39999999999</v>
       </c>
       <c r="K171" t="n">
-        <v>43273.9</v>
+        <v>87237.41</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>İstanbul Kurumsal Tedarik A.Ş.</t>
+          <t>İzmir Ticari Faaliyetler A.Ş.</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Yedek Parça Servis Paketi</t>
+          <t>Ürün Delta Kompakt</t>
         </is>
       </c>
       <c r="C172" s="2" t="n">
         <v>46001</v>
       </c>
       <c r="D172" t="n">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="E172" t="n">
-        <v>2400</v>
+        <v>1200</v>
       </c>
       <c r="F172" t="n">
-        <v>226035.51</v>
+        <v>41153.76</v>
       </c>
       <c r="G172" t="n">
-        <v>0</v>
+        <v>884.5599999999999</v>
       </c>
       <c r="H172" t="n">
-        <v>226035.51</v>
+        <v>28121.74</v>
       </c>
       <c r="I172" t="n">
-        <v>141272.19</v>
+        <v>40269.2</v>
       </c>
       <c r="J172" t="n">
         <v>0</v>
       </c>
       <c r="K172" t="n">
-        <v>226035.51</v>
+        <v>40269.2</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>İstanbul Kurumsal Tedarik A.Ş.</t>
+          <t>Karadeniz Toptan Dağıtım A.Ş.</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>Ürün Zeta Hızlı Tüketim</t>
+          <t>Ürün Gamma Endüstriyel</t>
         </is>
       </c>
       <c r="C173" s="2" t="n">
         <v>46003</v>
       </c>
       <c r="D173" t="n">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="E173" t="n">
-        <v>650</v>
+        <v>8900</v>
       </c>
       <c r="F173" t="n">
-        <v>57995.95</v>
+        <v>152611.88</v>
       </c>
       <c r="G173" t="n">
-        <v>6959.51</v>
+        <v>4920.36</v>
       </c>
       <c r="H173" t="n">
-        <v>51036.44</v>
+        <v>101169.67</v>
       </c>
       <c r="I173" t="n">
-        <v>39258.8</v>
+        <v>147691.52</v>
       </c>
       <c r="J173" t="n">
-        <v>25518.22</v>
+        <v>44307.46</v>
       </c>
       <c r="K173" t="n">
-        <v>25518.22</v>
+        <v>103384.06</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>Ankara Proje Yönetim ve Satış</t>
+          <t>İstanbul Kurumsal Tedarik A.Ş.</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -7212,301 +7212,301 @@
         <v>46005</v>
       </c>
       <c r="D174" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E174" t="n">
         <v>15400</v>
       </c>
       <c r="F174" t="n">
-        <v>763365.53</v>
+        <v>396104.98</v>
       </c>
       <c r="G174" t="n">
-        <v>91603.86</v>
+        <v>0</v>
       </c>
       <c r="H174" t="n">
-        <v>671761.67</v>
+        <v>252066.81</v>
       </c>
       <c r="I174" t="n">
-        <v>485778.07</v>
+        <v>396104.98</v>
       </c>
       <c r="J174" t="n">
         <v>0</v>
       </c>
       <c r="K174" t="n">
-        <v>671761.67</v>
+        <v>396104.98</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>Güneydoğu Pazarlama Ltd.</t>
+          <t>Adana Bölge Bayi A.Ş.</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Ürün Beta Premium</t>
+          <t>Ürün Alpha Standart</t>
         </is>
       </c>
       <c r="C175" s="2" t="n">
         <v>46007</v>
       </c>
       <c r="D175" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E175" t="n">
-        <v>4200</v>
+        <v>1850</v>
       </c>
       <c r="F175" t="n">
-        <v>229009.66</v>
+        <v>79306.73</v>
       </c>
       <c r="G175" t="n">
-        <v>6870.29</v>
+        <v>1704.62</v>
       </c>
       <c r="H175" t="n">
-        <v>222139.37</v>
+        <v>53585.63</v>
       </c>
       <c r="I175" t="n">
-        <v>152673.11</v>
+        <v>77602.11</v>
       </c>
       <c r="J175" t="n">
-        <v>111069.68</v>
+        <v>38801.06</v>
       </c>
       <c r="K175" t="n">
-        <v>111069.68</v>
+        <v>38801.05</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>İç Anadolu Tüketim Malları</t>
+          <t>Güneydoğu Pazarlama Ltd.</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>Ürün Epsilon Profesyonel</t>
+          <t>Ürün Zeta Hızlı Tüketim</t>
         </is>
       </c>
       <c r="C176" s="2" t="n">
         <v>46009</v>
       </c>
       <c r="D176" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="E176" t="n">
-        <v>15400</v>
+        <v>650</v>
       </c>
       <c r="F176" t="n">
-        <v>687028.98</v>
+        <v>39010.34</v>
       </c>
       <c r="G176" t="n">
-        <v>82443.48</v>
+        <v>0</v>
       </c>
       <c r="H176" t="n">
-        <v>604585.5</v>
+        <v>26407</v>
       </c>
       <c r="I176" t="n">
-        <v>437200.26</v>
+        <v>39010.34</v>
       </c>
       <c r="J176" t="n">
-        <v>302292.75</v>
+        <v>19505.17</v>
       </c>
       <c r="K176" t="n">
-        <v>302292.75</v>
+        <v>19505.17</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>Gaziantep İhracat ve Toptan</t>
+          <t>İç Anadolu Tüketim Malları</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>Ürün Epsilon Profesyonel</t>
+          <t>Özel Sipariş Modeli X</t>
         </is>
       </c>
       <c r="C177" s="2" t="n">
         <v>46011</v>
       </c>
       <c r="D177" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="E177" t="n">
-        <v>15400</v>
+        <v>21500</v>
       </c>
       <c r="F177" t="n">
-        <v>534355.87</v>
+        <v>1106007.41</v>
       </c>
       <c r="G177" t="n">
         <v>0</v>
       </c>
       <c r="H177" t="n">
-        <v>534355.87</v>
+        <v>730479.3100000001</v>
       </c>
       <c r="I177" t="n">
-        <v>340044.65</v>
+        <v>1106007.41</v>
       </c>
       <c r="J177" t="n">
-        <v>267177.94</v>
+        <v>553003.7</v>
       </c>
       <c r="K177" t="n">
-        <v>267177.94</v>
+        <v>553003.71</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>Kocaeli Ağır Sanayi Pazarlama</t>
+          <t>Marmara Perakende Çözümleri</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>Ürün Delta Kompakt</t>
+          <t>Yedek Parça Servis Paketi</t>
         </is>
       </c>
       <c r="C178" s="2" t="n">
         <v>46013</v>
       </c>
       <c r="D178" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E178" t="n">
-        <v>1200</v>
+        <v>2400</v>
       </c>
       <c r="F178" t="n">
-        <v>11896.61</v>
+        <v>10288.44</v>
       </c>
       <c r="G178" t="n">
-        <v>951.73</v>
+        <v>0</v>
       </c>
       <c r="H178" t="n">
-        <v>10944.88</v>
+        <v>6430.28</v>
       </c>
       <c r="I178" t="n">
-        <v>8129.35</v>
+        <v>10288.44</v>
       </c>
       <c r="J178" t="n">
-        <v>3283.46</v>
+        <v>0</v>
       </c>
       <c r="K178" t="n">
-        <v>7661.41</v>
+        <v>10288.44</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>İzmir Ticari Faaliyetler A.Ş.</t>
+          <t>Toroslar Lojistik ve Ticaret</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>Ürün Zeta Hızlı Tüketim</t>
+          <t>Ürün Gamma Endüstriyel</t>
         </is>
       </c>
       <c r="C179" s="2" t="n">
         <v>46015</v>
       </c>
       <c r="D179" t="n">
-        <v>22</v>
+        <v>7</v>
       </c>
       <c r="E179" t="n">
-        <v>650</v>
+        <v>8900</v>
       </c>
       <c r="F179" t="n">
-        <v>70883.94</v>
+        <v>267070.78</v>
       </c>
       <c r="G179" t="n">
         <v>0</v>
       </c>
       <c r="H179" t="n">
-        <v>70883.94</v>
+        <v>177046.92</v>
       </c>
       <c r="I179" t="n">
-        <v>47982.98</v>
+        <v>267070.78</v>
       </c>
       <c r="J179" t="n">
-        <v>35441.97</v>
+        <v>80121.23</v>
       </c>
       <c r="K179" t="n">
-        <v>35441.97</v>
+        <v>186949.55</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>Anadolu Sanayi Grubu A.Ş.</t>
+          <t>Ankara Proje Yönetim ve Satış</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>Özel Sipariş Modeli X</t>
+          <t>Ürün Gamma Endüstriyel</t>
         </is>
       </c>
       <c r="C180" s="2" t="n">
         <v>46017</v>
       </c>
       <c r="D180" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="E180" t="n">
-        <v>21500</v>
+        <v>8900</v>
       </c>
       <c r="F180" t="n">
-        <v>1065737.59</v>
+        <v>152611.88</v>
       </c>
       <c r="G180" t="n">
-        <v>31972.13</v>
+        <v>3280.24</v>
       </c>
       <c r="H180" t="n">
-        <v>1033765.46</v>
+        <v>101169.67</v>
       </c>
       <c r="I180" t="n">
-        <v>703882.5</v>
+        <v>149331.64</v>
       </c>
       <c r="J180" t="n">
-        <v>310129.64</v>
+        <v>0</v>
       </c>
       <c r="K180" t="n">
-        <v>723635.83</v>
+        <v>149331.64</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>Akdeniz Endüstriyel Ürünler</t>
+          <t>Bursa İmalat Tedarik Ltd.</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>Yedek Parça Servis Paketi</t>
+          <t>Ürün Alpha Standart</t>
         </is>
       </c>
       <c r="C181" s="2" t="n">
         <v>46019</v>
       </c>
       <c r="D181" t="n">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="E181" t="n">
-        <v>2400</v>
+        <v>1850</v>
       </c>
       <c r="F181" t="n">
-        <v>285518.54</v>
+        <v>103098.75</v>
       </c>
       <c r="G181" t="n">
-        <v>0</v>
+        <v>2216</v>
       </c>
       <c r="H181" t="n">
-        <v>285518.54</v>
+        <v>69661.32000000001</v>
       </c>
       <c r="I181" t="n">
-        <v>178449.09</v>
+        <v>100882.75</v>
       </c>
       <c r="J181" t="n">
-        <v>142759.27</v>
+        <v>0</v>
       </c>
       <c r="K181" t="n">
-        <v>142759.27</v>
+        <v>100882.75</v>
       </c>
     </row>
   </sheetData>

--- a/demo_data/sectors/insaat_taahhut/sales_ledger.xlsx
+++ b/demo_data/sectors/insaat_taahhut/sales_ledger.xlsx
@@ -492,37 +492,37 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Ege Dağıtım ve Ticaret Ltd.</t>
+          <t>Müşteri Grubu A - Atlas</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Özel Sipariş Modeli X</t>
+          <t>Çelik Konstrüksiyon Montaj Paketi</t>
         </is>
       </c>
       <c r="C2" s="2" t="n">
         <v>45658</v>
       </c>
       <c r="D2" t="n">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="E2" t="n">
-        <v>21500</v>
+        <v>280000</v>
       </c>
       <c r="F2" t="n">
-        <v>368669.12</v>
+        <v>647548.45</v>
       </c>
       <c r="G2" t="n">
-        <v>-0.02</v>
+        <v>14775.83</v>
       </c>
       <c r="H2" t="n">
-        <v>243493.1</v>
+        <v>520351.44</v>
       </c>
       <c r="I2" t="n">
-        <v>368669.14</v>
+        <v>632772.62</v>
       </c>
       <c r="J2" t="n">
-        <v>368669.14</v>
+        <v>632772.62</v>
       </c>
       <c r="K2" t="n">
         <v>0</v>
@@ -531,37 +531,37 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Ege Dağıtım ve Ticaret Ltd.</t>
+          <t>Stratejik Ortak E - Atlas</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Ürün Alpha Standart</t>
+          <t>Çelik Konstrüksiyon Montaj Paketi</t>
         </is>
       </c>
       <c r="C3" s="2" t="n">
         <v>45660</v>
       </c>
       <c r="D3" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="E3" t="n">
-        <v>1850</v>
+        <v>280000</v>
       </c>
       <c r="F3" t="n">
-        <v>15861.35</v>
+        <v>485661.34</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>10717.13</v>
+        <v>390263.58</v>
       </c>
       <c r="I3" t="n">
-        <v>15861.35</v>
+        <v>485661.34</v>
       </c>
       <c r="J3" t="n">
-        <v>15861.35</v>
+        <v>485661.34</v>
       </c>
       <c r="K3" t="n">
         <v>0</v>
@@ -570,37 +570,37 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Marmara Perakende Çözümleri</t>
+          <t>Stratejik Ortak E - Atlas</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Ürün Delta Kompakt</t>
+          <t>Şantiye Altyapı ve Drenaj İşi</t>
         </is>
       </c>
       <c r="C4" s="2" t="n">
         <v>45662</v>
       </c>
       <c r="D4" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="E4" t="n">
-        <v>1200</v>
+        <v>85000</v>
       </c>
       <c r="F4" t="n">
-        <v>66874.87</v>
+        <v>49144.3</v>
       </c>
       <c r="G4" t="n">
-        <v>1437.41</v>
+        <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>45697.83</v>
+        <v>39315.44</v>
       </c>
       <c r="I4" t="n">
-        <v>65437.46</v>
+        <v>49144.3</v>
       </c>
       <c r="J4" t="n">
-        <v>65437.46</v>
+        <v>49144.3</v>
       </c>
       <c r="K4" t="n">
         <v>0</v>
@@ -609,37 +609,37 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>İzmir Ticari Faaliyetler A.Ş.</t>
+          <t>Toptan Müşteri F - Atlas</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Ürün Beta Premium</t>
+          <t>Dış Cephe Yalıtım ve Kompozit Giydirme</t>
         </is>
       </c>
       <c r="C5" s="2" t="n">
         <v>45664</v>
       </c>
       <c r="D5" t="n">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="E5" t="n">
-        <v>4200</v>
+        <v>165000</v>
       </c>
       <c r="F5" t="n">
-        <v>342090.66</v>
+        <v>214644.97</v>
       </c>
       <c r="G5" t="n">
-        <v>18382.24</v>
+        <v>12244.47</v>
       </c>
       <c r="H5" t="n">
-        <v>228060.44</v>
+        <v>169114.22</v>
       </c>
       <c r="I5" t="n">
-        <v>323708.42</v>
+        <v>202400.5</v>
       </c>
       <c r="J5" t="n">
-        <v>323708.42</v>
+        <v>202400.5</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
@@ -648,37 +648,37 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Karadeniz Toptan Dağıtım A.Ş.</t>
+          <t>Müşteri Grubu B - Atlas</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Ürün Beta Premium</t>
+          <t>Mekanik ve Havalandırma Tesisatı</t>
         </is>
       </c>
       <c r="C6" s="2" t="n">
         <v>45666</v>
       </c>
       <c r="D6" t="n">
-        <v>1</v>
+        <v>19</v>
       </c>
       <c r="E6" t="n">
-        <v>4200</v>
+        <v>195000</v>
       </c>
       <c r="F6" t="n">
-        <v>18004.77</v>
+        <v>535528.35</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>12003.18</v>
+        <v>425676.38</v>
       </c>
       <c r="I6" t="n">
-        <v>18004.77</v>
+        <v>535528.35</v>
       </c>
       <c r="J6" t="n">
-        <v>18004.77</v>
+        <v>535528.35</v>
       </c>
       <c r="K6" t="n">
         <v>0</v>
@@ -687,37 +687,37 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Toroslar Lojistik ve Ticaret</t>
+          <t>Ulusal Hesap H - Atlas</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Özel Sipariş Modeli X</t>
+          <t>Dış Cephe Yalıtım ve Kompozit Giydirme</t>
         </is>
       </c>
       <c r="C7" s="2" t="n">
         <v>45668</v>
       </c>
       <c r="D7" t="n">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="E7" t="n">
-        <v>21500</v>
+        <v>165000</v>
       </c>
       <c r="F7" t="n">
-        <v>460836.42</v>
+        <v>405440.49</v>
       </c>
       <c r="G7" t="n">
-        <v>0</v>
+        <v>9251.379999999999</v>
       </c>
       <c r="H7" t="n">
-        <v>304366.38</v>
+        <v>319437.96</v>
       </c>
       <c r="I7" t="n">
-        <v>460836.42</v>
+        <v>396189.11</v>
       </c>
       <c r="J7" t="n">
-        <v>460836.42</v>
+        <v>396189.11</v>
       </c>
       <c r="K7" t="n">
         <v>0</v>
@@ -726,37 +726,37 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Gaziantep İhracat ve Toptan</t>
+          <t>Müşteri Grubu A - Atlas</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Ürün Zeta Hızlı Tüketim</t>
+          <t>Dış Cephe Yalıtım ve Kompozit Giydirme</t>
         </is>
       </c>
       <c r="C8" s="2" t="n">
         <v>45670</v>
       </c>
       <c r="D8" t="n">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="E8" t="n">
-        <v>650</v>
+        <v>165000</v>
       </c>
       <c r="F8" t="n">
-        <v>11145.81</v>
+        <v>453139.38</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>7544.86</v>
+        <v>357018.9</v>
       </c>
       <c r="I8" t="n">
-        <v>11145.81</v>
+        <v>453139.38</v>
       </c>
       <c r="J8" t="n">
-        <v>11145.81</v>
+        <v>453139.38</v>
       </c>
       <c r="K8" t="n">
         <v>0</v>
@@ -765,37 +765,37 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Güneydoğu Pazarlama Ltd.</t>
+          <t>Toptan Müşteri F - Atlas</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Ürün Alpha Standart</t>
+          <t>Çelik Konstrüksiyon Montaj Paketi</t>
         </is>
       </c>
       <c r="C9" s="2" t="n">
         <v>45672</v>
       </c>
       <c r="D9" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E9" t="n">
-        <v>1850</v>
+        <v>280000</v>
       </c>
       <c r="F9" t="n">
-        <v>47584.04</v>
+        <v>364246</v>
       </c>
       <c r="G9" t="n">
-        <v>2556.93</v>
+        <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>32151.38</v>
+        <v>292697.68</v>
       </c>
       <c r="I9" t="n">
-        <v>45027.11</v>
+        <v>364246</v>
       </c>
       <c r="J9" t="n">
-        <v>45027.11</v>
+        <v>364246</v>
       </c>
       <c r="K9" t="n">
         <v>0</v>
@@ -804,37 +804,37 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Akdeniz Endüstriyel Ürünler</t>
+          <t>Müşteri Grubu B - Atlas</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Yedek Parça Servis Paketi</t>
+          <t>Çelik Konstrüksiyon Montaj Paketi</t>
         </is>
       </c>
       <c r="C10" s="2" t="n">
         <v>45674</v>
       </c>
       <c r="D10" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E10" t="n">
-        <v>2400</v>
+        <v>280000</v>
       </c>
       <c r="F10" t="n">
-        <v>164615.06</v>
+        <v>688020.23</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>102884.41</v>
+        <v>552873.4</v>
       </c>
       <c r="I10" t="n">
-        <v>164615.06</v>
+        <v>688020.23</v>
       </c>
       <c r="J10" t="n">
-        <v>164615.06</v>
+        <v>688020.23</v>
       </c>
       <c r="K10" t="n">
         <v>0</v>
@@ -843,37 +843,37 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Akdeniz Endüstriyel Ürünler</t>
+          <t>Müşteri Grubu A - Atlas</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Yedek Parça Servis Paketi</t>
+          <t>Kaba İnşaat Taşeron Hakediş Paketi</t>
         </is>
       </c>
       <c r="C11" s="2" t="n">
         <v>45676</v>
       </c>
       <c r="D11" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E11" t="n">
-        <v>2400</v>
+        <v>450000</v>
       </c>
       <c r="F11" t="n">
-        <v>61730.65</v>
+        <v>520351.44</v>
       </c>
       <c r="G11" t="n">
-        <v>1326.84</v>
+        <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>38581.65</v>
+        <v>416281.15</v>
       </c>
       <c r="I11" t="n">
-        <v>60403.81</v>
+        <v>520351.44</v>
       </c>
       <c r="J11" t="n">
-        <v>60403.81</v>
+        <v>520351.44</v>
       </c>
       <c r="K11" t="n">
         <v>0</v>
@@ -882,37 +882,37 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Toroslar Lojistik ve Ticaret</t>
+          <t>Ulusal Hesap H - Atlas</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Ürün Gamma Endüstriyel</t>
+          <t>Mekanik ve Havalandırma Tesisatı</t>
         </is>
       </c>
       <c r="C12" s="2" t="n">
         <v>45678</v>
       </c>
       <c r="D12" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E12" t="n">
-        <v>8900</v>
+        <v>195000</v>
       </c>
       <c r="F12" t="n">
-        <v>343376.72</v>
+        <v>366414.14</v>
       </c>
       <c r="G12" t="n">
-        <v>7380.54</v>
+        <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>227631.76</v>
+        <v>291252.26</v>
       </c>
       <c r="I12" t="n">
-        <v>335996.18</v>
+        <v>366414.14</v>
       </c>
       <c r="J12" t="n">
-        <v>335996.18</v>
+        <v>366414.14</v>
       </c>
       <c r="K12" t="n">
         <v>0</v>
@@ -921,37 +921,37 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Güneydoğu Pazarlama Ltd.</t>
+          <t>Bölge Bayi C - Atlas</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Ürün Gamma Endüstriyel</t>
+          <t>Kaba İnşaat Taşeron Hakediş Paketi</t>
         </is>
       </c>
       <c r="C13" s="2" t="n">
         <v>45680</v>
       </c>
       <c r="D13" t="n">
-        <v>2</v>
+        <v>18</v>
       </c>
       <c r="E13" t="n">
-        <v>8900</v>
+        <v>450000</v>
       </c>
       <c r="F13" t="n">
-        <v>76305.94</v>
+        <v>1170790.73</v>
       </c>
       <c r="G13" t="n">
-        <v>4100.3</v>
+        <v>40072.81</v>
       </c>
       <c r="H13" t="n">
-        <v>50584.84</v>
+        <v>936632.58</v>
       </c>
       <c r="I13" t="n">
-        <v>72205.64</v>
+        <v>1130717.92</v>
       </c>
       <c r="J13" t="n">
-        <v>72205.64</v>
+        <v>1130717.92</v>
       </c>
       <c r="K13" t="n">
         <v>0</v>
@@ -960,37 +960,37 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Ankara Proje Yönetim ve Satış</t>
+          <t>Kurumsal Müşteri D - Atlas</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Ürün Delta Kompakt</t>
+          <t>Mekanik ve Havalandırma Tesisatı</t>
         </is>
       </c>
       <c r="C14" s="2" t="n">
         <v>45682</v>
       </c>
       <c r="D14" t="n">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="E14" t="n">
-        <v>1200</v>
+        <v>195000</v>
       </c>
       <c r="F14" t="n">
-        <v>108028.63</v>
+        <v>225485.62</v>
       </c>
       <c r="G14" t="n">
-        <v>2321.97</v>
+        <v>7717.73</v>
       </c>
       <c r="H14" t="n">
-        <v>73819.56</v>
+        <v>179232.16</v>
       </c>
       <c r="I14" t="n">
-        <v>105706.66</v>
+        <v>217767.89</v>
       </c>
       <c r="J14" t="n">
-        <v>105706.66</v>
+        <v>217767.89</v>
       </c>
       <c r="K14" t="n">
         <v>0</v>
@@ -999,37 +999,37 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Güneydoğu Pazarlama Ltd.</t>
+          <t>Toptan Müşteri F - Atlas</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Yedek Parça Servis Paketi</t>
+          <t>Mekanik ve Havalandırma Tesisatı</t>
         </is>
       </c>
       <c r="C15" s="2" t="n">
         <v>45684</v>
       </c>
       <c r="D15" t="n">
-        <v>18</v>
+        <v>3</v>
       </c>
       <c r="E15" t="n">
-        <v>2400</v>
+        <v>195000</v>
       </c>
       <c r="F15" t="n">
-        <v>185191.94</v>
+        <v>84557.11</v>
       </c>
       <c r="G15" t="n">
-        <v>5970.77</v>
+        <v>4823.58</v>
       </c>
       <c r="H15" t="n">
-        <v>115744.96</v>
+        <v>67212.06</v>
       </c>
       <c r="I15" t="n">
-        <v>179221.17</v>
+        <v>79733.53</v>
       </c>
       <c r="J15" t="n">
-        <v>179221.17</v>
+        <v>79733.53</v>
       </c>
       <c r="K15" t="n">
         <v>0</v>
@@ -1038,37 +1038,37 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Anadolu Sanayi Grubu A.Ş.</t>
+          <t>Toptan Müşteri F - Atlas</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Ürün Beta Premium</t>
+          <t>Kaba İnşaat Taşeron Hakediş Paketi</t>
         </is>
       </c>
       <c r="C16" s="2" t="n">
         <v>45686</v>
       </c>
       <c r="D16" t="n">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="E16" t="n">
-        <v>4200</v>
+        <v>450000</v>
       </c>
       <c r="F16" t="n">
-        <v>162042.95</v>
+        <v>1105746.8</v>
       </c>
       <c r="G16" t="n">
-        <v>5224.43</v>
+        <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>108028.63</v>
+        <v>884597.4399999999</v>
       </c>
       <c r="I16" t="n">
-        <v>156818.52</v>
+        <v>1105746.8</v>
       </c>
       <c r="J16" t="n">
-        <v>156818.52</v>
+        <v>1105746.8</v>
       </c>
       <c r="K16" t="n">
         <v>0</v>
@@ -1077,37 +1077,37 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Marmara Perakende Çözümleri</t>
+          <t>Bölge Bayi C - Atlas</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Yedek Parça Servis Paketi</t>
+          <t>Çelik Konstrüksiyon Montaj Paketi</t>
         </is>
       </c>
       <c r="C17" s="2" t="n">
         <v>45688</v>
       </c>
       <c r="D17" t="n">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="E17" t="n">
-        <v>2400</v>
+        <v>280000</v>
       </c>
       <c r="F17" t="n">
-        <v>72019.09</v>
+        <v>688020.23</v>
       </c>
       <c r="G17" t="n">
-        <v>3869.95</v>
+        <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>45011.93</v>
+        <v>552873.4</v>
       </c>
       <c r="I17" t="n">
-        <v>68149.14</v>
+        <v>688020.23</v>
       </c>
       <c r="J17" t="n">
-        <v>68149.14</v>
+        <v>688020.23</v>
       </c>
       <c r="K17" t="n">
         <v>0</v>
@@ -1116,37 +1116,37 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Toroslar Lojistik ve Ticaret</t>
+          <t>Ticari Kanal G - Atlas</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Ürün Alpha Standart</t>
+          <t>Kaba İnşaat Taşeron Hakediş Paketi</t>
         </is>
       </c>
       <c r="C18" s="2" t="n">
         <v>45690</v>
       </c>
       <c r="D18" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E18" t="n">
-        <v>1850</v>
+        <v>450000</v>
       </c>
       <c r="F18" t="n">
-        <v>103098.75</v>
+        <v>975658.9399999999</v>
       </c>
       <c r="G18" t="n">
-        <v>2216</v>
+        <v>22262.67</v>
       </c>
       <c r="H18" t="n">
-        <v>69661.32000000001</v>
+        <v>780527.15</v>
       </c>
       <c r="I18" t="n">
-        <v>100882.75</v>
+        <v>953396.27</v>
       </c>
       <c r="J18" t="n">
-        <v>100882.75</v>
+        <v>953396.27</v>
       </c>
       <c r="K18" t="n">
         <v>0</v>
@@ -1155,37 +1155,37 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Güneydoğu Pazarlama Ltd.</t>
+          <t>Stratejik Ortak E - Atlas</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Özel Sipariş Modeli X</t>
+          <t>Mekanik ve Havalandırma Tesisatı</t>
         </is>
       </c>
       <c r="C19" s="2" t="n">
         <v>45692</v>
       </c>
       <c r="D19" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="E19" t="n">
-        <v>21500</v>
+        <v>195000</v>
       </c>
       <c r="F19" t="n">
-        <v>1106007.41</v>
+        <v>84557.11</v>
       </c>
       <c r="G19" t="n">
-        <v>59431.31</v>
+        <v>4823.58</v>
       </c>
       <c r="H19" t="n">
-        <v>730479.3100000001</v>
+        <v>67212.06</v>
       </c>
       <c r="I19" t="n">
-        <v>1046576.1</v>
+        <v>79733.53</v>
       </c>
       <c r="J19" t="n">
-        <v>1046576.1</v>
+        <v>79733.53</v>
       </c>
       <c r="K19" t="n">
         <v>0</v>
@@ -1194,37 +1194,37 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>İstanbul Kurumsal Tedarik A.Ş.</t>
+          <t>Ulusal Hesap H - Atlas</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Ürün Zeta Hızlı Tüketim</t>
+          <t>Kaba İnşaat Taşeron Hakediş Paketi</t>
         </is>
       </c>
       <c r="C20" s="2" t="n">
         <v>45694</v>
       </c>
       <c r="D20" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E20" t="n">
-        <v>650</v>
+        <v>450000</v>
       </c>
       <c r="F20" t="n">
-        <v>36223.89</v>
+        <v>780527.15</v>
       </c>
       <c r="G20" t="n">
-        <v>778.6</v>
+        <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>24520.78</v>
+        <v>624421.72</v>
       </c>
       <c r="I20" t="n">
-        <v>35445.29</v>
+        <v>780527.15</v>
       </c>
       <c r="J20" t="n">
-        <v>35445.29</v>
+        <v>780527.15</v>
       </c>
       <c r="K20" t="n">
         <v>0</v>
@@ -1233,37 +1233,37 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Marmara Perakende Çözümleri</t>
+          <t>Stratejik Ortak E - Atlas</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Ürün Alpha Standart</t>
+          <t>İnce İşler Zemin Seramik &amp; Şap İşi</t>
         </is>
       </c>
       <c r="C21" s="2" t="n">
         <v>45696</v>
       </c>
       <c r="D21" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E21" t="n">
-        <v>1850</v>
+        <v>120000</v>
       </c>
       <c r="F21" t="n">
-        <v>87237.41</v>
+        <v>173450.48</v>
       </c>
       <c r="G21" t="n">
-        <v>4687.7</v>
+        <v>9894.52</v>
       </c>
       <c r="H21" t="n">
-        <v>58944.19</v>
+        <v>137314.96</v>
       </c>
       <c r="I21" t="n">
-        <v>82549.71000000001</v>
+        <v>163555.96</v>
       </c>
       <c r="J21" t="n">
-        <v>82549.71000000001</v>
+        <v>163555.96</v>
       </c>
       <c r="K21" t="n">
         <v>0</v>
@@ -1272,37 +1272,37 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Toroslar Lojistik ve Ticaret</t>
+          <t>Kurumsal Müşteri D - Atlas</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Ürün Alpha Standart</t>
+          <t>Dış Cephe Yalıtım ve Kompozit Giydirme</t>
         </is>
       </c>
       <c r="C22" s="2" t="n">
         <v>45698</v>
       </c>
       <c r="D22" t="n">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="E22" t="n">
-        <v>1850</v>
+        <v>165000</v>
       </c>
       <c r="F22" t="n">
-        <v>198266.83</v>
+        <v>286193.29</v>
       </c>
       <c r="G22" t="n">
-        <v>4261.55</v>
+        <v>16325.96</v>
       </c>
       <c r="H22" t="n">
-        <v>133964.08</v>
+        <v>225485.62</v>
       </c>
       <c r="I22" t="n">
-        <v>194005.28</v>
+        <v>269867.33</v>
       </c>
       <c r="J22" t="n">
-        <v>194005.28</v>
+        <v>269867.33</v>
       </c>
       <c r="K22" t="n">
         <v>0</v>
@@ -1311,37 +1311,37 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Anadolu Sanayi Grubu A.Ş.</t>
+          <t>Ulusal Hesap H - Atlas</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Özel Sipariş Modeli X</t>
+          <t>Çelik Konstrüksiyon Montaj Paketi</t>
         </is>
       </c>
       <c r="C23" s="2" t="n">
         <v>45700</v>
       </c>
       <c r="D23" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E23" t="n">
-        <v>21500</v>
+        <v>280000</v>
       </c>
       <c r="F23" t="n">
-        <v>1566843.83</v>
+        <v>728492.01</v>
       </c>
       <c r="G23" t="n">
-        <v>33677.74</v>
+        <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>1034845.69</v>
+        <v>585395.37</v>
       </c>
       <c r="I23" t="n">
-        <v>1533166.09</v>
+        <v>728492.01</v>
       </c>
       <c r="J23" t="n">
-        <v>1533166.09</v>
+        <v>728492.01</v>
       </c>
       <c r="K23" t="n">
         <v>0</v>
@@ -1350,37 +1350,37 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Kocaeli Ağır Sanayi Pazarlama</t>
+          <t>Bölge Bayi C - Atlas</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Ürün Delta Kompakt</t>
+          <t>Kaba İnşaat Taşeron Hakediş Paketi</t>
         </is>
       </c>
       <c r="C24" s="2" t="n">
         <v>45702</v>
       </c>
       <c r="D24" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="E24" t="n">
-        <v>1200</v>
+        <v>450000</v>
       </c>
       <c r="F24" t="n">
-        <v>30865.32</v>
+        <v>910615.01</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>21091.3</v>
+        <v>728492.01</v>
       </c>
       <c r="I24" t="n">
-        <v>30865.32</v>
+        <v>910615.01</v>
       </c>
       <c r="J24" t="n">
-        <v>30865.32</v>
+        <v>910615.01</v>
       </c>
       <c r="K24" t="n">
         <v>0</v>
@@ -1389,37 +1389,37 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Toroslar Lojistik ve Ticaret</t>
+          <t>Kurumsal Müşteri D - Atlas</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Ürün Delta Kompakt</t>
+          <t>İnce İşler Zemin Seramik &amp; Şap İşi</t>
         </is>
       </c>
       <c r="C25" s="2" t="n">
         <v>45704</v>
       </c>
       <c r="D25" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="E25" t="n">
-        <v>1200</v>
+        <v>120000</v>
       </c>
       <c r="F25" t="n">
-        <v>46297.98</v>
+        <v>208140.57</v>
       </c>
       <c r="G25" t="n">
-        <v>2487.82</v>
+        <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>31636.96</v>
+        <v>164777.95</v>
       </c>
       <c r="I25" t="n">
-        <v>43810.16</v>
+        <v>208140.57</v>
       </c>
       <c r="J25" t="n">
-        <v>43810.16</v>
+        <v>208140.57</v>
       </c>
       <c r="K25" t="n">
         <v>0</v>
@@ -1428,37 +1428,37 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Adana Bölge Bayi A.Ş.</t>
+          <t>Toptan Müşteri F - Atlas</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Ürün Alpha Standart</t>
+          <t>Kaba İnşaat Taşeron Hakediş Paketi</t>
         </is>
       </c>
       <c r="C26" s="2" t="n">
         <v>45706</v>
       </c>
       <c r="D26" t="n">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="E26" t="n">
-        <v>1850</v>
+        <v>450000</v>
       </c>
       <c r="F26" t="n">
-        <v>198266.83</v>
+        <v>845571.08</v>
       </c>
       <c r="G26" t="n">
-        <v>0</v>
+        <v>19294.32</v>
       </c>
       <c r="H26" t="n">
-        <v>133964.08</v>
+        <v>676456.87</v>
       </c>
       <c r="I26" t="n">
-        <v>198266.83</v>
+        <v>826276.76</v>
       </c>
       <c r="J26" t="n">
-        <v>198266.83</v>
+        <v>826276.76</v>
       </c>
       <c r="K26" t="n">
         <v>0</v>
@@ -1467,37 +1467,37 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Ankara Proje Yönetim ve Satış</t>
+          <t>Müşteri Grubu B - Atlas</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Yedek Parça Servis Paketi</t>
+          <t>Çelik Konstrüksiyon Montaj Paketi</t>
         </is>
       </c>
       <c r="C27" s="2" t="n">
         <v>45708</v>
       </c>
       <c r="D27" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="E27" t="n">
-        <v>2400</v>
+        <v>280000</v>
       </c>
       <c r="F27" t="n">
-        <v>123461.29</v>
+        <v>688020.23</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>77163.31</v>
+        <v>552873.4</v>
       </c>
       <c r="I27" t="n">
-        <v>123461.29</v>
+        <v>688020.23</v>
       </c>
       <c r="J27" t="n">
-        <v>123461.29</v>
+        <v>688020.23</v>
       </c>
       <c r="K27" t="n">
         <v>0</v>
@@ -1506,37 +1506,37 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Marmara Perakende Çözümleri</t>
+          <t>Ticari Kanal G - Atlas</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Ürün Delta Kompakt</t>
+          <t>Dış Cephe Yalıtım ve Kompozit Giydirme</t>
         </is>
       </c>
       <c r="C28" s="2" t="n">
         <v>45710</v>
       </c>
       <c r="D28" t="n">
-        <v>19</v>
+        <v>2</v>
       </c>
       <c r="E28" t="n">
-        <v>1200</v>
+        <v>165000</v>
       </c>
       <c r="F28" t="n">
-        <v>97740.19</v>
+        <v>47698.88</v>
       </c>
       <c r="G28" t="n">
-        <v>2100.83</v>
+        <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>66789.13</v>
+        <v>37580.94</v>
       </c>
       <c r="I28" t="n">
-        <v>95639.36</v>
+        <v>47698.88</v>
       </c>
       <c r="J28" t="n">
-        <v>95639.36</v>
+        <v>47698.88</v>
       </c>
       <c r="K28" t="n">
         <v>0</v>
@@ -1545,37 +1545,37 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Kocaeli Ağır Sanayi Pazarlama</t>
+          <t>Stratejik Ortak E - Atlas</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Ürün Zeta Hızlı Tüketim</t>
+          <t>Kaba İnşaat Taşeron Hakediş Paketi</t>
         </is>
       </c>
       <c r="C29" s="2" t="n">
         <v>45712</v>
       </c>
       <c r="D29" t="n">
-        <v>19</v>
+        <v>2</v>
       </c>
       <c r="E29" t="n">
-        <v>650</v>
+        <v>450000</v>
       </c>
       <c r="F29" t="n">
-        <v>52942.6</v>
+        <v>130087.86</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>35838.07</v>
+        <v>104070.29</v>
       </c>
       <c r="I29" t="n">
-        <v>52942.6</v>
+        <v>130087.86</v>
       </c>
       <c r="J29" t="n">
-        <v>52942.6</v>
+        <v>130087.86</v>
       </c>
       <c r="K29" t="n">
         <v>0</v>
@@ -1584,37 +1584,37 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Bursa İmalat Tedarik Ltd.</t>
+          <t>Ticari Kanal G - Atlas</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Ürün Zeta Hızlı Tüketim</t>
+          <t>Şantiye Altyapı ve Drenaj İşi</t>
         </is>
       </c>
       <c r="C30" s="2" t="n">
         <v>45714</v>
       </c>
       <c r="D30" t="n">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="E30" t="n">
-        <v>650</v>
+        <v>85000</v>
       </c>
       <c r="F30" t="n">
-        <v>52942.6</v>
+        <v>147432.91</v>
       </c>
       <c r="G30" t="n">
-        <v>2844.87</v>
+        <v>5046.21</v>
       </c>
       <c r="H30" t="n">
-        <v>35838.07</v>
+        <v>117946.33</v>
       </c>
       <c r="I30" t="n">
-        <v>50097.73</v>
+        <v>142386.7</v>
       </c>
       <c r="J30" t="n">
-        <v>50097.73</v>
+        <v>142386.7</v>
       </c>
       <c r="K30" t="n">
         <v>0</v>
@@ -1623,37 +1623,37 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Marmara Perakende Çözümleri</t>
+          <t>Müşteri Grubu B - Atlas</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Ürün Delta Kompakt</t>
+          <t>İnce İşler Zemin Seramik &amp; Şap İşi</t>
         </is>
       </c>
       <c r="C31" s="2" t="n">
         <v>45716</v>
       </c>
       <c r="D31" t="n">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="E31" t="n">
-        <v>1200</v>
+        <v>120000</v>
       </c>
       <c r="F31" t="n">
-        <v>82307.53</v>
+        <v>69380.19</v>
       </c>
       <c r="G31" t="n">
-        <v>4422.8</v>
+        <v>3957.81</v>
       </c>
       <c r="H31" t="n">
-        <v>56243.48</v>
+        <v>54925.98</v>
       </c>
       <c r="I31" t="n">
-        <v>77884.73</v>
+        <v>65422.38</v>
       </c>
       <c r="J31" t="n">
-        <v>77884.73</v>
+        <v>65422.38</v>
       </c>
       <c r="K31" t="n">
         <v>0</v>
@@ -1662,37 +1662,37 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Karadeniz Toptan Dağıtım A.Ş.</t>
+          <t>Bölge Bayi C - Atlas</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Ürün Gamma Endüstriyel</t>
+          <t>Şantiye Altyapı ve Drenaj İşi</t>
         </is>
       </c>
       <c r="C32" s="2" t="n">
         <v>45718</v>
       </c>
       <c r="D32" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E32" t="n">
-        <v>8900</v>
+        <v>85000</v>
       </c>
       <c r="F32" t="n">
-        <v>610447.5</v>
+        <v>159718.98</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>404678.68</v>
+        <v>127775.19</v>
       </c>
       <c r="I32" t="n">
-        <v>610447.5</v>
+        <v>159718.98</v>
       </c>
       <c r="J32" t="n">
-        <v>610447.5</v>
+        <v>159718.98</v>
       </c>
       <c r="K32" t="n">
         <v>0</v>
@@ -1701,37 +1701,37 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Ege Dağıtım ve Ticaret Ltd.</t>
+          <t>Müşteri Grubu A - Atlas</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Ürün Alpha Standart</t>
+          <t>Dış Cephe Yalıtım ve Kompozit Giydirme</t>
         </is>
       </c>
       <c r="C33" s="2" t="n">
         <v>45720</v>
       </c>
       <c r="D33" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E33" t="n">
-        <v>1850</v>
+        <v>165000</v>
       </c>
       <c r="F33" t="n">
-        <v>63445.39</v>
+        <v>119247.2</v>
       </c>
       <c r="G33" t="n">
-        <v>3409.24</v>
+        <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>42868.5</v>
+        <v>93952.34</v>
       </c>
       <c r="I33" t="n">
-        <v>60036.15</v>
+        <v>119247.2</v>
       </c>
       <c r="J33" t="n">
-        <v>60036.15</v>
+        <v>119247.2</v>
       </c>
       <c r="K33" t="n">
         <v>0</v>
@@ -1740,37 +1740,37 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Toroslar Lojistik ve Ticaret</t>
+          <t>Stratejik Ortak E - Atlas</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Ürün Alpha Standart</t>
+          <t>Mekanik ve Havalandırma Tesisatı</t>
         </is>
       </c>
       <c r="C34" s="2" t="n">
         <v>45722</v>
       </c>
       <c r="D34" t="n">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="E34" t="n">
-        <v>1850</v>
+        <v>195000</v>
       </c>
       <c r="F34" t="n">
-        <v>134821.45</v>
+        <v>310042.73</v>
       </c>
       <c r="G34" t="n">
-        <v>4346.78</v>
+        <v>10611.87</v>
       </c>
       <c r="H34" t="n">
-        <v>91095.57000000001</v>
+        <v>246444.22</v>
       </c>
       <c r="I34" t="n">
-        <v>130474.67</v>
+        <v>299430.86</v>
       </c>
       <c r="J34" t="n">
-        <v>130474.67</v>
+        <v>299430.86</v>
       </c>
       <c r="K34" t="n">
         <v>0</v>
@@ -1779,37 +1779,37 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Anadolu Sanayi Grubu A.Ş.</t>
+          <t>Toptan Müşteri F - Atlas</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Ürün Zeta Hızlı Tüketim</t>
+          <t>Mekanik ve Havalandırma Tesisatı</t>
         </is>
       </c>
       <c r="C35" s="2" t="n">
         <v>45724</v>
       </c>
       <c r="D35" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="E35" t="n">
-        <v>650</v>
+        <v>195000</v>
       </c>
       <c r="F35" t="n">
-        <v>55729.06</v>
+        <v>422785.54</v>
       </c>
       <c r="G35" t="n">
-        <v>0</v>
+        <v>9647.16</v>
       </c>
       <c r="H35" t="n">
-        <v>37724.28</v>
+        <v>336060.3</v>
       </c>
       <c r="I35" t="n">
-        <v>55729.06</v>
+        <v>413138.38</v>
       </c>
       <c r="J35" t="n">
-        <v>55729.06</v>
+        <v>413138.38</v>
       </c>
       <c r="K35" t="n">
         <v>0</v>
@@ -1818,37 +1818,37 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Kocaeli Ağır Sanayi Pazarlama</t>
+          <t>Kurumsal Müşteri D - Atlas</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Ürün Gamma Endüstriyel</t>
+          <t>Kaba İnşaat Taşeron Hakediş Paketi</t>
         </is>
       </c>
       <c r="C36" s="2" t="n">
         <v>45726</v>
       </c>
       <c r="D36" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="E36" t="n">
-        <v>8900</v>
+        <v>450000</v>
       </c>
       <c r="F36" t="n">
-        <v>419682.66</v>
+        <v>455307.51</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>278216.59</v>
+        <v>364246</v>
       </c>
       <c r="I36" t="n">
-        <v>419682.66</v>
+        <v>455307.51</v>
       </c>
       <c r="J36" t="n">
-        <v>419682.66</v>
+        <v>455307.51</v>
       </c>
       <c r="K36" t="n">
         <v>0</v>
@@ -1857,37 +1857,37 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Gaziantep İhracat ve Toptan</t>
+          <t>Müşteri Grubu B - Atlas</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Ürün Zeta Hızlı Tüketim</t>
+          <t>Çelik Konstrüksiyon Montaj Paketi</t>
         </is>
       </c>
       <c r="C37" s="2" t="n">
         <v>45728</v>
       </c>
       <c r="D37" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E37" t="n">
-        <v>650</v>
+        <v>280000</v>
       </c>
       <c r="F37" t="n">
-        <v>5572.91</v>
+        <v>161887.11</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>3772.43</v>
+        <v>130087.86</v>
       </c>
       <c r="I37" t="n">
-        <v>5572.91</v>
+        <v>161887.11</v>
       </c>
       <c r="J37" t="n">
-        <v>5572.91</v>
+        <v>161887.11</v>
       </c>
       <c r="K37" t="n">
         <v>0</v>
@@ -1896,37 +1896,37 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Marmara Perakende Çözümleri</t>
+          <t>Ulusal Hesap H - Atlas</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Ürün Gamma Endüstriyel</t>
+          <t>Dış Cephe Yalıtım ve Kompozit Giydirme</t>
         </is>
       </c>
       <c r="C38" s="2" t="n">
         <v>45730</v>
       </c>
       <c r="D38" t="n">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="E38" t="n">
-        <v>8900</v>
+        <v>165000</v>
       </c>
       <c r="F38" t="n">
-        <v>953824.22</v>
+        <v>262343.85</v>
       </c>
       <c r="G38" t="n">
-        <v>0</v>
+        <v>8979.280000000001</v>
       </c>
       <c r="H38" t="n">
-        <v>632310.4399999999</v>
+        <v>206695.15</v>
       </c>
       <c r="I38" t="n">
-        <v>953824.22</v>
+        <v>253364.57</v>
       </c>
       <c r="J38" t="n">
-        <v>953824.22</v>
+        <v>253364.57</v>
       </c>
       <c r="K38" t="n">
         <v>0</v>
@@ -1935,37 +1935,37 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Adana Bölge Bayi A.Ş.</t>
+          <t>Müşteri Grubu B - Atlas</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Ürün Zeta Hızlı Tüketim</t>
+          <t>İnce İşler Zemin Seramik &amp; Şap İşi</t>
         </is>
       </c>
       <c r="C39" s="2" t="n">
         <v>45732</v>
       </c>
       <c r="D39" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="E39" t="n">
-        <v>650</v>
+        <v>120000</v>
       </c>
       <c r="F39" t="n">
-        <v>8359.360000000001</v>
+        <v>208140.57</v>
       </c>
       <c r="G39" t="n">
-        <v>179.68</v>
+        <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>5658.64</v>
+        <v>164777.95</v>
       </c>
       <c r="I39" t="n">
-        <v>8179.68</v>
+        <v>208140.57</v>
       </c>
       <c r="J39" t="n">
-        <v>8179.68</v>
+        <v>208140.57</v>
       </c>
       <c r="K39" t="n">
         <v>0</v>
@@ -1974,37 +1974,37 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Bursa İmalat Tedarik Ltd.</t>
+          <t>Ulusal Hesap H - Atlas</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Yedek Parça Servis Paketi</t>
+          <t>Mekanik ve Havalandırma Tesisatı</t>
         </is>
       </c>
       <c r="C40" s="2" t="n">
         <v>45734</v>
       </c>
       <c r="D40" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="E40" t="n">
-        <v>2400</v>
+        <v>195000</v>
       </c>
       <c r="F40" t="n">
-        <v>195480.38</v>
+        <v>422785.54</v>
       </c>
       <c r="G40" t="n">
-        <v>0</v>
+        <v>9647.16</v>
       </c>
       <c r="H40" t="n">
-        <v>122175.24</v>
+        <v>336060.3</v>
       </c>
       <c r="I40" t="n">
-        <v>195480.38</v>
+        <v>413138.38</v>
       </c>
       <c r="J40" t="n">
-        <v>195480.38</v>
+        <v>413138.38</v>
       </c>
       <c r="K40" t="n">
         <v>0</v>
@@ -2013,37 +2013,37 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>İç Anadolu Tüketim Malları</t>
+          <t>Müşteri Grubu B - Atlas</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Ürün Epsilon Profesyonel</t>
+          <t>Kaba İnşaat Taşeron Hakediş Paketi</t>
         </is>
       </c>
       <c r="C41" s="2" t="n">
         <v>45736</v>
       </c>
       <c r="D41" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="E41" t="n">
-        <v>15400</v>
+        <v>450000</v>
       </c>
       <c r="F41" t="n">
-        <v>726192.46</v>
+        <v>390263.58</v>
       </c>
       <c r="G41" t="n">
-        <v>0</v>
+        <v>8905.07</v>
       </c>
       <c r="H41" t="n">
-        <v>462122.48</v>
+        <v>312210.86</v>
       </c>
       <c r="I41" t="n">
-        <v>726192.46</v>
+        <v>381358.51</v>
       </c>
       <c r="J41" t="n">
-        <v>726192.46</v>
+        <v>381358.51</v>
       </c>
       <c r="K41" t="n">
         <v>0</v>
@@ -2052,37 +2052,37 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Marmara Perakende Çözümleri</t>
+          <t>Müşteri Grubu A - Atlas</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Yedek Parça Servis Paketi</t>
+          <t>Çelik Konstrüksiyon Montaj Paketi</t>
         </is>
       </c>
       <c r="C42" s="2" t="n">
         <v>45738</v>
       </c>
       <c r="D42" t="n">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="E42" t="n">
-        <v>2400</v>
+        <v>280000</v>
       </c>
       <c r="F42" t="n">
-        <v>216057.26</v>
+        <v>445189.56</v>
       </c>
       <c r="G42" t="n">
-        <v>6965.9</v>
+        <v>0</v>
       </c>
       <c r="H42" t="n">
-        <v>135035.79</v>
+        <v>357741.61</v>
       </c>
       <c r="I42" t="n">
-        <v>209091.36</v>
+        <v>445189.56</v>
       </c>
       <c r="J42" t="n">
-        <v>209091.36</v>
+        <v>445189.56</v>
       </c>
       <c r="K42" t="n">
         <v>0</v>
@@ -2091,37 +2091,37 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>İzmir Ticari Faaliyetler A.Ş.</t>
+          <t>Müşteri Grubu B - Atlas</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Ürün Zeta Hızlı Tüketim</t>
+          <t>Şantiye Altyapı ve Drenaj İşi</t>
         </is>
       </c>
       <c r="C43" s="2" t="n">
         <v>45740</v>
       </c>
       <c r="D43" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E43" t="n">
-        <v>650</v>
+        <v>85000</v>
       </c>
       <c r="F43" t="n">
-        <v>16718.72</v>
+        <v>98288.60000000001</v>
       </c>
       <c r="G43" t="n">
-        <v>898.38</v>
+        <v>2242.76</v>
       </c>
       <c r="H43" t="n">
-        <v>11317.29</v>
+        <v>78630.88</v>
       </c>
       <c r="I43" t="n">
-        <v>15820.34</v>
+        <v>96045.84</v>
       </c>
       <c r="J43" t="n">
-        <v>15820.34</v>
+        <v>96045.84</v>
       </c>
       <c r="K43" t="n">
         <v>0</v>
@@ -2130,37 +2130,37 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Bursa İmalat Tedarik Ltd.</t>
+          <t>Ticari Kanal G - Atlas</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Ürün Zeta Hızlı Tüketim</t>
+          <t>İnce İşler Zemin Seramik &amp; Şap İşi</t>
         </is>
       </c>
       <c r="C44" s="2" t="n">
         <v>45742</v>
       </c>
       <c r="D44" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="E44" t="n">
-        <v>650</v>
+        <v>120000</v>
       </c>
       <c r="F44" t="n">
-        <v>22291.62</v>
+        <v>34690.1</v>
       </c>
       <c r="G44" t="n">
-        <v>1197.84</v>
+        <v>791.5599999999999</v>
       </c>
       <c r="H44" t="n">
-        <v>15089.71</v>
+        <v>27462.99</v>
       </c>
       <c r="I44" t="n">
-        <v>21093.78</v>
+        <v>33898.54</v>
       </c>
       <c r="J44" t="n">
-        <v>21093.78</v>
+        <v>33898.54</v>
       </c>
       <c r="K44" t="n">
         <v>0</v>
@@ -2169,37 +2169,37 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Adana Bölge Bayi A.Ş.</t>
+          <t>Stratejik Ortak E - Atlas</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Ürün Gamma Endüstriyel</t>
+          <t>Çelik Konstrüksiyon Montaj Paketi</t>
         </is>
       </c>
       <c r="C45" s="2" t="n">
         <v>45744</v>
       </c>
       <c r="D45" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="E45" t="n">
-        <v>8900</v>
+        <v>280000</v>
       </c>
       <c r="F45" t="n">
-        <v>495988.59</v>
+        <v>40471.78</v>
       </c>
       <c r="G45" t="n">
-        <v>10660.78</v>
+        <v>1385.23</v>
       </c>
       <c r="H45" t="n">
-        <v>328801.43</v>
+        <v>32521.96</v>
       </c>
       <c r="I45" t="n">
-        <v>485327.81</v>
+        <v>39086.55</v>
       </c>
       <c r="J45" t="n">
-        <v>485327.81</v>
+        <v>39086.55</v>
       </c>
       <c r="K45" t="n">
         <v>0</v>
@@ -2208,37 +2208,37 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Bursa İmalat Tedarik Ltd.</t>
+          <t>Ulusal Hesap H - Atlas</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Ürün Epsilon Profesyonel</t>
+          <t>İnce İşler Zemin Seramik &amp; Şap İşi</t>
         </is>
       </c>
       <c r="C46" s="2" t="n">
         <v>45746</v>
       </c>
       <c r="D46" t="n">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="E46" t="n">
-        <v>15400</v>
+        <v>120000</v>
       </c>
       <c r="F46" t="n">
-        <v>330087.48</v>
+        <v>312210.86</v>
       </c>
       <c r="G46" t="n">
         <v>0</v>
       </c>
       <c r="H46" t="n">
-        <v>210055.67</v>
+        <v>247166.93</v>
       </c>
       <c r="I46" t="n">
-        <v>330087.48</v>
+        <v>312210.86</v>
       </c>
       <c r="J46" t="n">
-        <v>330087.48</v>
+        <v>312210.86</v>
       </c>
       <c r="K46" t="n">
         <v>0</v>
@@ -2247,37 +2247,37 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Bursa İmalat Tedarik Ltd.</t>
+          <t>Müşteri Grubu B - Atlas</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Ürün Alpha Standart</t>
+          <t>Dış Cephe Yalıtım ve Kompozit Giydirme</t>
         </is>
       </c>
       <c r="C47" s="2" t="n">
         <v>45749</v>
       </c>
       <c r="D47" t="n">
-        <v>23</v>
+        <v>4</v>
       </c>
       <c r="E47" t="n">
-        <v>1850</v>
+        <v>165000</v>
       </c>
       <c r="F47" t="n">
-        <v>182405.49</v>
+        <v>95397.75999999999</v>
       </c>
       <c r="G47" t="n">
-        <v>9801.559999999999</v>
+        <v>0</v>
       </c>
       <c r="H47" t="n">
-        <v>123246.95</v>
+        <v>75161.87</v>
       </c>
       <c r="I47" t="n">
-        <v>172603.93</v>
+        <v>95397.75999999999</v>
       </c>
       <c r="J47" t="n">
-        <v>172603.93</v>
+        <v>95397.75999999999</v>
       </c>
       <c r="K47" t="n">
         <v>0</v>
@@ -2286,37 +2286,37 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Akdeniz Endüstriyel Ürünler</t>
+          <t>Müşteri Grubu B - Atlas</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Ürün Alpha Standart</t>
+          <t>Kaba İnşaat Taşeron Hakediş Paketi</t>
         </is>
       </c>
       <c r="C48" s="2" t="n">
         <v>45751</v>
       </c>
       <c r="D48" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E48" t="n">
-        <v>1850</v>
+        <v>450000</v>
       </c>
       <c r="F48" t="n">
-        <v>47584.04</v>
+        <v>130087.86</v>
       </c>
       <c r="G48" t="n">
-        <v>2556.93</v>
+        <v>0</v>
       </c>
       <c r="H48" t="n">
-        <v>32151.38</v>
+        <v>104070.29</v>
       </c>
       <c r="I48" t="n">
-        <v>45027.11</v>
+        <v>130087.86</v>
       </c>
       <c r="J48" t="n">
-        <v>45027.11</v>
+        <v>130087.86</v>
       </c>
       <c r="K48" t="n">
         <v>0</v>
@@ -2325,37 +2325,37 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>İç Anadolu Tüketim Malları</t>
+          <t>Bölge Bayi C - Atlas</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Ürün Delta Kompakt</t>
+          <t>Çelik Konstrüksiyon Montaj Paketi</t>
         </is>
       </c>
       <c r="C49" s="2" t="n">
         <v>45753</v>
       </c>
       <c r="D49" t="n">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="E49" t="n">
-        <v>1200</v>
+        <v>280000</v>
       </c>
       <c r="F49" t="n">
-        <v>108028.63</v>
+        <v>526133.12</v>
       </c>
       <c r="G49" t="n">
-        <v>5804.92</v>
+        <v>12005.35</v>
       </c>
       <c r="H49" t="n">
-        <v>73819.56</v>
+        <v>422785.54</v>
       </c>
       <c r="I49" t="n">
-        <v>102223.71</v>
+        <v>514127.77</v>
       </c>
       <c r="J49" t="n">
-        <v>102223.71</v>
+        <v>514127.77</v>
       </c>
       <c r="K49" t="n">
         <v>0</v>
@@ -2364,37 +2364,37 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Ege Dağıtım ve Ticaret Ltd.</t>
+          <t>Müşteri Grubu B - Atlas</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Özel Sipariş Modeli X</t>
+          <t>İnce İşler Zemin Seramik &amp; Şap İşi</t>
         </is>
       </c>
       <c r="C50" s="2" t="n">
         <v>45755</v>
       </c>
       <c r="D50" t="n">
-        <v>5</v>
+        <v>19</v>
       </c>
       <c r="E50" t="n">
-        <v>21500</v>
+        <v>120000</v>
       </c>
       <c r="F50" t="n">
-        <v>460836.42</v>
+        <v>329555.91</v>
       </c>
       <c r="G50" t="n">
-        <v>9905.219999999999</v>
+        <v>7519.84</v>
       </c>
       <c r="H50" t="n">
-        <v>304366.38</v>
+        <v>260898.43</v>
       </c>
       <c r="I50" t="n">
-        <v>450931.2</v>
+        <v>322036.07</v>
       </c>
       <c r="J50" t="n">
-        <v>450931.2</v>
+        <v>322036.07</v>
       </c>
       <c r="K50" t="n">
         <v>0</v>
@@ -2403,37 +2403,37 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Bursa İmalat Tedarik Ltd.</t>
+          <t>Müşteri Grubu B - Atlas</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Ürün Beta Premium</t>
+          <t>Kaba İnşaat Taşeron Hakediş Paketi</t>
         </is>
       </c>
       <c r="C51" s="2" t="n">
         <v>45757</v>
       </c>
       <c r="D51" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="E51" t="n">
-        <v>4200</v>
+        <v>450000</v>
       </c>
       <c r="F51" t="n">
-        <v>144038.17</v>
+        <v>195131.79</v>
       </c>
       <c r="G51" t="n">
-        <v>3095.96</v>
+        <v>0</v>
       </c>
       <c r="H51" t="n">
-        <v>96025.45</v>
+        <v>156105.43</v>
       </c>
       <c r="I51" t="n">
-        <v>140942.21</v>
+        <v>195131.79</v>
       </c>
       <c r="J51" t="n">
-        <v>140942.21</v>
+        <v>195131.79</v>
       </c>
       <c r="K51" t="n">
         <v>0</v>
@@ -2442,37 +2442,37 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>İç Anadolu Tüketim Malları</t>
+          <t>Ulusal Hesap H - Atlas</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Ürün Gamma Endüstriyel</t>
+          <t>Çelik Konstrüksiyon Montaj Paketi</t>
         </is>
       </c>
       <c r="C52" s="2" t="n">
         <v>45759</v>
       </c>
       <c r="D52" t="n">
-        <v>21</v>
+        <v>3</v>
       </c>
       <c r="E52" t="n">
-        <v>8900</v>
+        <v>280000</v>
       </c>
       <c r="F52" t="n">
-        <v>801212.34</v>
+        <v>121415.33</v>
       </c>
       <c r="G52" t="n">
-        <v>0</v>
+        <v>2770.47</v>
       </c>
       <c r="H52" t="n">
-        <v>531140.77</v>
+        <v>97565.89</v>
       </c>
       <c r="I52" t="n">
-        <v>801212.34</v>
+        <v>118644.86</v>
       </c>
       <c r="J52" t="n">
-        <v>801212.34</v>
+        <v>118644.86</v>
       </c>
       <c r="K52" t="n">
         <v>0</v>
@@ -2481,12 +2481,12 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Adana Bölge Bayi A.Ş.</t>
+          <t>Müşteri Grubu B - Atlas</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Ürün Zeta Hızlı Tüketim</t>
+          <t>Kaba İnşaat Taşeron Hakediş Paketi</t>
         </is>
       </c>
       <c r="C53" s="2" t="n">
@@ -2496,22 +2496,22 @@
         <v>15</v>
       </c>
       <c r="E53" t="n">
-        <v>650</v>
+        <v>450000</v>
       </c>
       <c r="F53" t="n">
-        <v>41796.79</v>
+        <v>975658.9399999999</v>
       </c>
       <c r="G53" t="n">
         <v>0</v>
       </c>
       <c r="H53" t="n">
-        <v>28293.21</v>
+        <v>780527.15</v>
       </c>
       <c r="I53" t="n">
-        <v>41796.79</v>
+        <v>975658.9399999999</v>
       </c>
       <c r="J53" t="n">
-        <v>41796.79</v>
+        <v>975658.9399999999</v>
       </c>
       <c r="K53" t="n">
         <v>0</v>
@@ -2520,37 +2520,37 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Karadeniz Toptan Dağıtım A.Ş.</t>
+          <t>Bölge Bayi C - Atlas</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Ürün Delta Kompakt</t>
+          <t>İnce İşler Zemin Seramik &amp; Şap İşi</t>
         </is>
       </c>
       <c r="C54" s="2" t="n">
         <v>45763</v>
       </c>
       <c r="D54" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="E54" t="n">
-        <v>1200</v>
+        <v>120000</v>
       </c>
       <c r="F54" t="n">
-        <v>41153.76</v>
+        <v>242830.67</v>
       </c>
       <c r="G54" t="n">
-        <v>0</v>
+        <v>8311.4</v>
       </c>
       <c r="H54" t="n">
-        <v>28121.74</v>
+        <v>192240.95</v>
       </c>
       <c r="I54" t="n">
-        <v>41153.76</v>
+        <v>234519.27</v>
       </c>
       <c r="J54" t="n">
-        <v>41153.76</v>
+        <v>234519.27</v>
       </c>
       <c r="K54" t="n">
         <v>0</v>
@@ -2559,37 +2559,37 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>İç Anadolu Tüketim Malları</t>
+          <t>Ulusal Hesap H - Atlas</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Ürün Epsilon Profesyonel</t>
+          <t>Kaba İnşaat Taşeron Hakediş Paketi</t>
         </is>
       </c>
       <c r="C55" s="2" t="n">
         <v>45765</v>
       </c>
       <c r="D55" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="E55" t="n">
-        <v>15400</v>
+        <v>450000</v>
       </c>
       <c r="F55" t="n">
-        <v>264069.99</v>
+        <v>845571.08</v>
       </c>
       <c r="G55" t="n">
-        <v>0</v>
+        <v>28941.48</v>
       </c>
       <c r="H55" t="n">
-        <v>168044.54</v>
+        <v>676456.87</v>
       </c>
       <c r="I55" t="n">
-        <v>264069.99</v>
+        <v>816629.6</v>
       </c>
       <c r="J55" t="n">
-        <v>264069.99</v>
+        <v>816629.6</v>
       </c>
       <c r="K55" t="n">
         <v>0</v>
@@ -2598,37 +2598,37 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Anadolu Sanayi Grubu A.Ş.</t>
+          <t>Bölge Bayi C - Atlas</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Yedek Parça Servis Paketi</t>
+          <t>Mekanik ve Havalandırma Tesisatı</t>
         </is>
       </c>
       <c r="C56" s="2" t="n">
         <v>45767</v>
       </c>
       <c r="D56" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="E56" t="n">
-        <v>2400</v>
+        <v>195000</v>
       </c>
       <c r="F56" t="n">
-        <v>154326.62</v>
+        <v>197299.92</v>
       </c>
       <c r="G56" t="n">
-        <v>4975.64</v>
+        <v>0</v>
       </c>
       <c r="H56" t="n">
-        <v>96454.13</v>
+        <v>156828.14</v>
       </c>
       <c r="I56" t="n">
-        <v>149350.98</v>
+        <v>197299.92</v>
       </c>
       <c r="J56" t="n">
-        <v>149350.98</v>
+        <v>197299.92</v>
       </c>
       <c r="K56" t="n">
         <v>0</v>
@@ -2637,37 +2637,37 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Marmara Perakende Çözümleri</t>
+          <t>Stratejik Ortak E - Atlas</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Yedek Parça Servis Paketi</t>
+          <t>Mekanik ve Havalandırma Tesisatı</t>
         </is>
       </c>
       <c r="C57" s="2" t="n">
         <v>45769</v>
       </c>
       <c r="D57" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E57" t="n">
-        <v>2400</v>
+        <v>195000</v>
       </c>
       <c r="F57" t="n">
-        <v>164615.06</v>
+        <v>422785.54</v>
       </c>
       <c r="G57" t="n">
-        <v>5307.35</v>
+        <v>0</v>
       </c>
       <c r="H57" t="n">
-        <v>102884.41</v>
+        <v>336060.3</v>
       </c>
       <c r="I57" t="n">
-        <v>159307.71</v>
+        <v>422785.54</v>
       </c>
       <c r="J57" t="n">
-        <v>159307.71</v>
+        <v>422785.54</v>
       </c>
       <c r="K57" t="n">
         <v>0</v>
@@ -2676,37 +2676,37 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>İç Anadolu Tüketim Malları</t>
+          <t>Müşteri Grubu A - Atlas</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Yedek Parça Servis Paketi</t>
+          <t>İnce İşler Zemin Seramik &amp; Şap İşi</t>
         </is>
       </c>
       <c r="C58" s="2" t="n">
         <v>45771</v>
       </c>
       <c r="D58" t="n">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="E58" t="n">
-        <v>2400</v>
+        <v>120000</v>
       </c>
       <c r="F58" t="n">
-        <v>41153.76</v>
+        <v>346900.96</v>
       </c>
       <c r="G58" t="n">
-        <v>1326.84</v>
+        <v>19789.04</v>
       </c>
       <c r="H58" t="n">
-        <v>25721.1</v>
+        <v>274629.92</v>
       </c>
       <c r="I58" t="n">
-        <v>39826.92</v>
+        <v>327111.92</v>
       </c>
       <c r="J58" t="n">
-        <v>39826.92</v>
+        <v>327111.92</v>
       </c>
       <c r="K58" t="n">
         <v>0</v>
@@ -2715,37 +2715,37 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Kocaeli Ağır Sanayi Pazarlama</t>
+          <t>Kurumsal Müşteri D - Atlas</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Ürün Delta Kompakt</t>
+          <t>Şantiye Altyapı ve Drenaj İşi</t>
         </is>
       </c>
       <c r="C59" s="2" t="n">
         <v>45773</v>
       </c>
       <c r="D59" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E59" t="n">
-        <v>1200</v>
+        <v>85000</v>
       </c>
       <c r="F59" t="n">
-        <v>30865.32</v>
+        <v>122860.76</v>
       </c>
       <c r="G59" t="n">
-        <v>995.13</v>
+        <v>4205.17</v>
       </c>
       <c r="H59" t="n">
-        <v>21091.3</v>
+        <v>98288.60000000001</v>
       </c>
       <c r="I59" t="n">
-        <v>29870.19</v>
+        <v>118655.59</v>
       </c>
       <c r="J59" t="n">
-        <v>29870.19</v>
+        <v>118655.59</v>
       </c>
       <c r="K59" t="n">
         <v>0</v>
@@ -2754,37 +2754,37 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Ege Dağıtım ve Ticaret Ltd.</t>
+          <t>Ticari Kanal G - Atlas</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Ürün Alpha Standart</t>
+          <t>İnce İşler Zemin Seramik &amp; Şap İşi</t>
         </is>
       </c>
       <c r="C60" s="2" t="n">
         <v>45775</v>
       </c>
       <c r="D60" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="E60" t="n">
-        <v>1850</v>
+        <v>120000</v>
       </c>
       <c r="F60" t="n">
-        <v>79306.73</v>
+        <v>277520.77</v>
       </c>
       <c r="G60" t="n">
         <v>0</v>
       </c>
       <c r="H60" t="n">
-        <v>53585.63</v>
+        <v>219703.94</v>
       </c>
       <c r="I60" t="n">
-        <v>79306.73</v>
+        <v>277520.77</v>
       </c>
       <c r="J60" t="n">
-        <v>79306.73</v>
+        <v>277520.77</v>
       </c>
       <c r="K60" t="n">
         <v>0</v>
@@ -2793,37 +2793,37 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>İç Anadolu Tüketim Malları</t>
+          <t>Müşteri Grubu B - Atlas</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Ürün Epsilon Profesyonel</t>
+          <t>Mekanik ve Havalandırma Tesisatı</t>
         </is>
       </c>
       <c r="C61" s="2" t="n">
         <v>45777</v>
       </c>
       <c r="D61" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="E61" t="n">
-        <v>15400</v>
+        <v>195000</v>
       </c>
       <c r="F61" t="n">
-        <v>264069.99</v>
+        <v>366414.14</v>
       </c>
       <c r="G61" t="n">
         <v>0</v>
       </c>
       <c r="H61" t="n">
-        <v>168044.54</v>
+        <v>291252.26</v>
       </c>
       <c r="I61" t="n">
-        <v>264069.99</v>
+        <v>366414.14</v>
       </c>
       <c r="J61" t="n">
-        <v>264069.99</v>
+        <v>366414.14</v>
       </c>
       <c r="K61" t="n">
         <v>0</v>
@@ -2832,37 +2832,37 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>İç Anadolu Tüketim Malları</t>
+          <t>Ticari Kanal G - Atlas</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Ürün Gamma Endüstriyel</t>
+          <t>Çelik Konstrüksiyon Montaj Paketi</t>
         </is>
       </c>
       <c r="C62" s="2" t="n">
         <v>45779</v>
       </c>
       <c r="D62" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="E62" t="n">
-        <v>8900</v>
+        <v>280000</v>
       </c>
       <c r="F62" t="n">
-        <v>495988.59</v>
+        <v>688020.23</v>
       </c>
       <c r="G62" t="n">
         <v>0</v>
       </c>
       <c r="H62" t="n">
-        <v>328801.43</v>
+        <v>552873.4</v>
       </c>
       <c r="I62" t="n">
-        <v>495988.59</v>
+        <v>688020.23</v>
       </c>
       <c r="J62" t="n">
-        <v>495988.59</v>
+        <v>688020.23</v>
       </c>
       <c r="K62" t="n">
         <v>0</v>
@@ -2871,37 +2871,37 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Bursa İmalat Tedarik Ltd.</t>
+          <t>Müşteri Grubu A - Atlas</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Ürün Beta Premium</t>
+          <t>Dış Cephe Yalıtım ve Kompozit Giydirme</t>
         </is>
       </c>
       <c r="C63" s="2" t="n">
         <v>45781</v>
       </c>
       <c r="D63" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="E63" t="n">
-        <v>4200</v>
+        <v>165000</v>
       </c>
       <c r="F63" t="n">
-        <v>324085.89</v>
+        <v>286193.29</v>
       </c>
       <c r="G63" t="n">
-        <v>0</v>
+        <v>9795.58</v>
       </c>
       <c r="H63" t="n">
-        <v>216057.26</v>
+        <v>225485.62</v>
       </c>
       <c r="I63" t="n">
-        <v>324085.89</v>
+        <v>276397.71</v>
       </c>
       <c r="J63" t="n">
-        <v>324085.89</v>
+        <v>276397.71</v>
       </c>
       <c r="K63" t="n">
         <v>0</v>
@@ -2910,37 +2910,37 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>İç Anadolu Tüketim Malları</t>
+          <t>Ulusal Hesap H - Atlas</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Özel Sipariş Modeli X</t>
+          <t>Mekanik ve Havalandırma Tesisatı</t>
         </is>
       </c>
       <c r="C64" s="2" t="n">
         <v>45783</v>
       </c>
       <c r="D64" t="n">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="E64" t="n">
-        <v>21500</v>
+        <v>195000</v>
       </c>
       <c r="F64" t="n">
-        <v>2119847.54</v>
+        <v>535528.35</v>
       </c>
       <c r="G64" t="n">
-        <v>0</v>
+        <v>30549.34</v>
       </c>
       <c r="H64" t="n">
-        <v>1400085.35</v>
+        <v>425676.38</v>
       </c>
       <c r="I64" t="n">
-        <v>2119847.54</v>
+        <v>504979.01</v>
       </c>
       <c r="J64" t="n">
-        <v>2119847.54</v>
+        <v>504979.01</v>
       </c>
       <c r="K64" t="n">
         <v>0</v>
@@ -2949,37 +2949,37 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Akdeniz Endüstriyel Ürünler</t>
+          <t>Toptan Müşteri F - Atlas</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Ürün Gamma Endüstriyel</t>
+          <t>Dış Cephe Yalıtım ve Kompozit Giydirme</t>
         </is>
       </c>
       <c r="C65" s="2" t="n">
         <v>45785</v>
       </c>
       <c r="D65" t="n">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="E65" t="n">
-        <v>8900</v>
+        <v>165000</v>
       </c>
       <c r="F65" t="n">
-        <v>763059.38</v>
+        <v>214644.97</v>
       </c>
       <c r="G65" t="n">
-        <v>24601.8</v>
+        <v>0</v>
       </c>
       <c r="H65" t="n">
-        <v>505848.35</v>
+        <v>169114.22</v>
       </c>
       <c r="I65" t="n">
-        <v>738457.58</v>
+        <v>214644.97</v>
       </c>
       <c r="J65" t="n">
-        <v>738457.58</v>
+        <v>214644.97</v>
       </c>
       <c r="K65" t="n">
         <v>0</v>
@@ -2988,37 +2988,37 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Marmara Perakende Çözümleri</t>
+          <t>Müşteri Grubu A - Atlas</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Ürün Alpha Standart</t>
+          <t>Mekanik ve Havalandırma Tesisatı</t>
         </is>
       </c>
       <c r="C66" s="2" t="n">
         <v>45787</v>
       </c>
       <c r="D66" t="n">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="E66" t="n">
-        <v>1850</v>
+        <v>195000</v>
       </c>
       <c r="F66" t="n">
-        <v>31722.69</v>
+        <v>563714.0600000001</v>
       </c>
       <c r="G66" t="n">
-        <v>681.85</v>
+        <v>0</v>
       </c>
       <c r="H66" t="n">
-        <v>21434.25</v>
+        <v>448080.4</v>
       </c>
       <c r="I66" t="n">
-        <v>31040.84</v>
+        <v>563714.0600000001</v>
       </c>
       <c r="J66" t="n">
-        <v>31040.84</v>
+        <v>563714.0600000001</v>
       </c>
       <c r="K66" t="n">
         <v>0</v>
@@ -3027,37 +3027,37 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Toroslar Lojistik ve Ticaret</t>
+          <t>Müşteri Grubu A - Atlas</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Ürün Delta Kompakt</t>
+          <t>Mekanik ve Havalandırma Tesisatı</t>
         </is>
       </c>
       <c r="C67" s="2" t="n">
         <v>45789</v>
       </c>
       <c r="D67" t="n">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="E67" t="n">
-        <v>1200</v>
+        <v>195000</v>
       </c>
       <c r="F67" t="n">
-        <v>72019.09</v>
+        <v>56371.41</v>
       </c>
       <c r="G67" t="n">
-        <v>3869.95</v>
+        <v>1929.43</v>
       </c>
       <c r="H67" t="n">
-        <v>49213.04</v>
+        <v>44808.04</v>
       </c>
       <c r="I67" t="n">
-        <v>68149.14</v>
+        <v>54441.98</v>
       </c>
       <c r="J67" t="n">
-        <v>68149.14</v>
+        <v>54441.98</v>
       </c>
       <c r="K67" t="n">
         <v>0</v>
@@ -3066,37 +3066,37 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Bursa İmalat Tedarik Ltd.</t>
+          <t>Toptan Müşteri F - Atlas</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Ürün Epsilon Profesyonel</t>
+          <t>İnce İşler Zemin Seramik &amp; Şap İşi</t>
         </is>
       </c>
       <c r="C68" s="2" t="n">
         <v>45791</v>
       </c>
       <c r="D68" t="n">
-        <v>22</v>
+        <v>8</v>
       </c>
       <c r="E68" t="n">
-        <v>15400</v>
+        <v>120000</v>
       </c>
       <c r="F68" t="n">
-        <v>1452384.92</v>
+        <v>138760.38</v>
       </c>
       <c r="G68" t="n">
-        <v>31217.56</v>
+        <v>0</v>
       </c>
       <c r="H68" t="n">
-        <v>924244.95</v>
+        <v>109851.97</v>
       </c>
       <c r="I68" t="n">
-        <v>1421167.36</v>
+        <v>138760.38</v>
       </c>
       <c r="J68" t="n">
-        <v>1421167.36</v>
+        <v>138760.38</v>
       </c>
       <c r="K68" t="n">
         <v>0</v>
@@ -3105,37 +3105,37 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Karadeniz Toptan Dağıtım A.Ş.</t>
+          <t>Müşteri Grubu B - Atlas</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Ürün Delta Kompakt</t>
+          <t>Çelik Konstrüksiyon Montaj Paketi</t>
         </is>
       </c>
       <c r="C69" s="2" t="n">
         <v>45793</v>
       </c>
       <c r="D69" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E69" t="n">
-        <v>1200</v>
+        <v>280000</v>
       </c>
       <c r="F69" t="n">
-        <v>20576.88</v>
+        <v>323774.23</v>
       </c>
       <c r="G69" t="n">
-        <v>0</v>
+        <v>7387.91</v>
       </c>
       <c r="H69" t="n">
-        <v>14060.87</v>
+        <v>260175.72</v>
       </c>
       <c r="I69" t="n">
-        <v>20576.88</v>
+        <v>316386.32</v>
       </c>
       <c r="J69" t="n">
-        <v>20576.88</v>
+        <v>316386.32</v>
       </c>
       <c r="K69" t="n">
         <v>0</v>
@@ -3144,37 +3144,37 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Akdeniz Endüstriyel Ürünler</t>
+          <t>Müşteri Grubu A - Atlas</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Özel Sipariş Modeli X</t>
+          <t>Çelik Konstrüksiyon Montaj Paketi</t>
         </is>
       </c>
       <c r="C70" s="2" t="n">
         <v>45795</v>
       </c>
       <c r="D70" t="n">
-        <v>5</v>
+        <v>19</v>
       </c>
       <c r="E70" t="n">
-        <v>21500</v>
+        <v>280000</v>
       </c>
       <c r="F70" t="n">
-        <v>460836.42</v>
+        <v>768963.79</v>
       </c>
       <c r="G70" t="n">
-        <v>0</v>
+        <v>26319.43</v>
       </c>
       <c r="H70" t="n">
-        <v>304366.38</v>
+        <v>617917.33</v>
       </c>
       <c r="I70" t="n">
-        <v>460836.42</v>
+        <v>742644.36</v>
       </c>
       <c r="J70" t="n">
-        <v>460836.42</v>
+        <v>742644.36</v>
       </c>
       <c r="K70" t="n">
         <v>0</v>
@@ -3183,37 +3183,37 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>İç Anadolu Tüketim Malları</t>
+          <t>Toptan Müşteri F - Atlas</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Ürün Alpha Standart</t>
+          <t>Çelik Konstrüksiyon Montaj Paketi</t>
         </is>
       </c>
       <c r="C71" s="2" t="n">
         <v>45797</v>
       </c>
       <c r="D71" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="E71" t="n">
-        <v>1850</v>
+        <v>280000</v>
       </c>
       <c r="F71" t="n">
-        <v>111029.43</v>
+        <v>242830.67</v>
       </c>
       <c r="G71" t="n">
         <v>0</v>
       </c>
       <c r="H71" t="n">
-        <v>75019.88</v>
+        <v>195131.79</v>
       </c>
       <c r="I71" t="n">
-        <v>111029.43</v>
+        <v>242830.67</v>
       </c>
       <c r="J71" t="n">
-        <v>111029.43</v>
+        <v>242830.67</v>
       </c>
       <c r="K71" t="n">
         <v>0</v>
@@ -3222,37 +3222,37 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Karadeniz Toptan Dağıtım A.Ş.</t>
+          <t>Toptan Müşteri F - Atlas</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Özel Sipariş Modeli X</t>
+          <t>Şantiye Altyapı ve Drenaj İşi</t>
         </is>
       </c>
       <c r="C72" s="2" t="n">
         <v>45799</v>
       </c>
       <c r="D72" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="E72" t="n">
-        <v>21500</v>
+        <v>85000</v>
       </c>
       <c r="F72" t="n">
-        <v>645170.99</v>
+        <v>147432.91</v>
       </c>
       <c r="G72" t="n">
-        <v>0</v>
+        <v>8410.34</v>
       </c>
       <c r="H72" t="n">
-        <v>426112.93</v>
+        <v>117946.33</v>
       </c>
       <c r="I72" t="n">
-        <v>645170.99</v>
+        <v>139022.57</v>
       </c>
       <c r="J72" t="n">
-        <v>645170.99</v>
+        <v>139022.57</v>
       </c>
       <c r="K72" t="n">
         <v>0</v>
@@ -3261,37 +3261,37 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Anadolu Sanayi Grubu A.Ş.</t>
+          <t>Müşteri Grubu A - Atlas</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Ürün Delta Kompakt</t>
+          <t>Şantiye Altyapı ve Drenaj İşi</t>
         </is>
       </c>
       <c r="C73" s="2" t="n">
         <v>45801</v>
       </c>
       <c r="D73" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="E73" t="n">
-        <v>1200</v>
+        <v>85000</v>
       </c>
       <c r="F73" t="n">
-        <v>30865.32</v>
+        <v>147432.91</v>
       </c>
       <c r="G73" t="n">
-        <v>663.42</v>
+        <v>8410.34</v>
       </c>
       <c r="H73" t="n">
-        <v>21091.3</v>
+        <v>117946.33</v>
       </c>
       <c r="I73" t="n">
-        <v>30201.9</v>
+        <v>139022.57</v>
       </c>
       <c r="J73" t="n">
-        <v>30201.9</v>
+        <v>139022.57</v>
       </c>
       <c r="K73" t="n">
         <v>0</v>
@@ -3300,37 +3300,37 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Ege Dağıtım ve Ticaret Ltd.</t>
+          <t>Bölge Bayi C - Atlas</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Özel Sipariş Modeli X</t>
+          <t>İnce İşler Zemin Seramik &amp; Şap İşi</t>
         </is>
       </c>
       <c r="C74" s="2" t="n">
         <v>45803</v>
       </c>
       <c r="D74" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E74" t="n">
-        <v>21500</v>
+        <v>120000</v>
       </c>
       <c r="F74" t="n">
-        <v>368669.14</v>
+        <v>121415.33</v>
       </c>
       <c r="G74" t="n">
-        <v>7924.17</v>
+        <v>4155.7</v>
       </c>
       <c r="H74" t="n">
-        <v>243493.1</v>
+        <v>96120.47</v>
       </c>
       <c r="I74" t="n">
-        <v>360744.97</v>
+        <v>117259.63</v>
       </c>
       <c r="J74" t="n">
-        <v>360744.97</v>
+        <v>117259.63</v>
       </c>
       <c r="K74" t="n">
         <v>0</v>
@@ -3339,12 +3339,12 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Kocaeli Ağır Sanayi Pazarlama</t>
+          <t>Stratejik Ortak E - Atlas</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Yedek Parça Servis Paketi</t>
+          <t>Çelik Konstrüksiyon Montaj Paketi</t>
         </is>
       </c>
       <c r="C75" s="2" t="n">
@@ -3354,22 +3354,22 @@
         <v>16</v>
       </c>
       <c r="E75" t="n">
-        <v>2400</v>
+        <v>280000</v>
       </c>
       <c r="F75" t="n">
-        <v>164615.06</v>
+        <v>647548.45</v>
       </c>
       <c r="G75" t="n">
-        <v>5307.35</v>
+        <v>0</v>
       </c>
       <c r="H75" t="n">
-        <v>102884.41</v>
+        <v>520351.44</v>
       </c>
       <c r="I75" t="n">
-        <v>159307.71</v>
+        <v>647548.45</v>
       </c>
       <c r="J75" t="n">
-        <v>159307.71</v>
+        <v>647548.45</v>
       </c>
       <c r="K75" t="n">
         <v>0</v>
@@ -3378,37 +3378,37 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Gaziantep İhracat ve Toptan</t>
+          <t>Müşteri Grubu B - Atlas</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Ürün Epsilon Profesyonel</t>
+          <t>Kaba İnşaat Taşeron Hakediş Paketi</t>
         </is>
       </c>
       <c r="C76" s="2" t="n">
         <v>45807</v>
       </c>
       <c r="D76" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E76" t="n">
-        <v>15400</v>
+        <v>450000</v>
       </c>
       <c r="F76" t="n">
-        <v>198052.49</v>
+        <v>520351.44</v>
       </c>
       <c r="G76" t="n">
-        <v>10642.35</v>
+        <v>29683.57</v>
       </c>
       <c r="H76" t="n">
-        <v>126033.4</v>
+        <v>416281.15</v>
       </c>
       <c r="I76" t="n">
-        <v>187410.14</v>
+        <v>490667.87</v>
       </c>
       <c r="J76" t="n">
-        <v>187410.14</v>
+        <v>490667.87</v>
       </c>
       <c r="K76" t="n">
         <v>0</v>
@@ -3417,37 +3417,37 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Akdeniz Endüstriyel Ürünler</t>
+          <t>Kurumsal Müşteri D - Atlas</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Ürün Gamma Endüstriyel</t>
+          <t>Kaba İnşaat Taşeron Hakediş Paketi</t>
         </is>
       </c>
       <c r="C77" s="2" t="n">
         <v>45809</v>
       </c>
       <c r="D77" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="E77" t="n">
-        <v>8900</v>
+        <v>450000</v>
       </c>
       <c r="F77" t="n">
-        <v>457835.63</v>
+        <v>1105746.8</v>
       </c>
       <c r="G77" t="n">
-        <v>14761.08</v>
+        <v>37846.55</v>
       </c>
       <c r="H77" t="n">
-        <v>303509.01</v>
+        <v>884597.4399999999</v>
       </c>
       <c r="I77" t="n">
-        <v>443074.55</v>
+        <v>1067900.25</v>
       </c>
       <c r="J77" t="n">
-        <v>443074.55</v>
+        <v>1067900.25</v>
       </c>
       <c r="K77" t="n">
         <v>0</v>
@@ -3456,37 +3456,37 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>İç Anadolu Tüketim Malları</t>
+          <t>Müşteri Grubu A - Atlas</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Ürün Gamma Endüstriyel</t>
+          <t>Mekanik ve Havalandırma Tesisatı</t>
         </is>
       </c>
       <c r="C78" s="2" t="n">
         <v>45811</v>
       </c>
       <c r="D78" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E78" t="n">
-        <v>8900</v>
+        <v>195000</v>
       </c>
       <c r="F78" t="n">
-        <v>572294.53</v>
+        <v>563714.0600000001</v>
       </c>
       <c r="G78" t="n">
         <v>0</v>
       </c>
       <c r="H78" t="n">
-        <v>379386.26</v>
+        <v>448080.4</v>
       </c>
       <c r="I78" t="n">
-        <v>572294.53</v>
+        <v>563714.0600000001</v>
       </c>
       <c r="J78" t="n">
-        <v>572294.53</v>
+        <v>563714.0600000001</v>
       </c>
       <c r="K78" t="n">
         <v>0</v>
@@ -3495,37 +3495,37 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Karadeniz Toptan Dağıtım A.Ş.</t>
+          <t>Bölge Bayi C - Atlas</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Özel Sipariş Modeli X</t>
+          <t>Mekanik ve Havalandırma Tesisatı</t>
         </is>
       </c>
       <c r="C79" s="2" t="n">
         <v>45813</v>
       </c>
       <c r="D79" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="E79" t="n">
-        <v>21500</v>
+        <v>195000</v>
       </c>
       <c r="F79" t="n">
-        <v>1382509.26</v>
+        <v>169114.22</v>
       </c>
       <c r="G79" t="n">
-        <v>29715.65</v>
+        <v>3858.86</v>
       </c>
       <c r="H79" t="n">
-        <v>913099.14</v>
+        <v>134424.12</v>
       </c>
       <c r="I79" t="n">
-        <v>1352793.61</v>
+        <v>165255.36</v>
       </c>
       <c r="J79" t="n">
-        <v>1352793.61</v>
+        <v>165255.36</v>
       </c>
       <c r="K79" t="n">
         <v>0</v>
@@ -3534,37 +3534,37 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Toroslar Lojistik ve Ticaret</t>
+          <t>Müşteri Grubu A - Atlas</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Ürün Epsilon Profesyonel</t>
+          <t>Kaba İnşaat Taşeron Hakediş Paketi</t>
         </is>
       </c>
       <c r="C80" s="2" t="n">
         <v>45815</v>
       </c>
       <c r="D80" t="n">
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="E80" t="n">
-        <v>15400</v>
+        <v>450000</v>
       </c>
       <c r="F80" t="n">
-        <v>1254332.43</v>
+        <v>325219.65</v>
       </c>
       <c r="G80" t="n">
-        <v>0</v>
+        <v>18552.23</v>
       </c>
       <c r="H80" t="n">
-        <v>798211.55</v>
+        <v>260175.72</v>
       </c>
       <c r="I80" t="n">
-        <v>1254332.43</v>
+        <v>306667.42</v>
       </c>
       <c r="J80" t="n">
-        <v>1254332.43</v>
+        <v>306667.42</v>
       </c>
       <c r="K80" t="n">
         <v>0</v>
@@ -3573,37 +3573,37 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Marmara Perakende Çözümleri</t>
+          <t>Bölge Bayi C - Atlas</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Ürün Beta Premium</t>
+          <t>Kaba İnşaat Taşeron Hakediş Paketi</t>
         </is>
       </c>
       <c r="C81" s="2" t="n">
         <v>45817</v>
       </c>
       <c r="D81" t="n">
-        <v>3</v>
+        <v>17</v>
       </c>
       <c r="E81" t="n">
-        <v>4200</v>
+        <v>450000</v>
       </c>
       <c r="F81" t="n">
-        <v>54014.32</v>
+        <v>1105746.8</v>
       </c>
       <c r="G81" t="n">
-        <v>1160.98</v>
+        <v>25231.03</v>
       </c>
       <c r="H81" t="n">
-        <v>36009.54</v>
+        <v>884597.4399999999</v>
       </c>
       <c r="I81" t="n">
-        <v>52853.34</v>
+        <v>1080515.77</v>
       </c>
       <c r="J81" t="n">
-        <v>52853.34</v>
+        <v>1080515.77</v>
       </c>
       <c r="K81" t="n">
         <v>0</v>
@@ -3612,37 +3612,37 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Kocaeli Ağır Sanayi Pazarlama</t>
+          <t>Müşteri Grubu B - Atlas</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Yedek Parça Servis Paketi</t>
+          <t>Mekanik ve Havalandırma Tesisatı</t>
         </is>
       </c>
       <c r="C82" s="2" t="n">
         <v>45819</v>
       </c>
       <c r="D82" t="n">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="E82" t="n">
-        <v>2400</v>
+        <v>195000</v>
       </c>
       <c r="F82" t="n">
-        <v>257211.03</v>
+        <v>366414.14</v>
       </c>
       <c r="G82" t="n">
-        <v>13821.23</v>
+        <v>20902.18</v>
       </c>
       <c r="H82" t="n">
-        <v>160756.89</v>
+        <v>291252.26</v>
       </c>
       <c r="I82" t="n">
-        <v>243389.8</v>
+        <v>345511.96</v>
       </c>
       <c r="J82" t="n">
-        <v>243389.8</v>
+        <v>345511.96</v>
       </c>
       <c r="K82" t="n">
         <v>0</v>
@@ -3651,37 +3651,37 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Toroslar Lojistik ve Ticaret</t>
+          <t>Müşteri Grubu B - Atlas</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Ürün Alpha Standart</t>
+          <t>Mekanik ve Havalandırma Tesisatı</t>
         </is>
       </c>
       <c r="C83" s="2" t="n">
         <v>45821</v>
       </c>
       <c r="D83" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="E83" t="n">
-        <v>1850</v>
+        <v>195000</v>
       </c>
       <c r="F83" t="n">
-        <v>103098.75</v>
+        <v>281857.03</v>
       </c>
       <c r="G83" t="n">
-        <v>5540.01</v>
+        <v>6431.44</v>
       </c>
       <c r="H83" t="n">
-        <v>69661.32000000001</v>
+        <v>224040.2</v>
       </c>
       <c r="I83" t="n">
-        <v>97558.74000000001</v>
+        <v>275425.59</v>
       </c>
       <c r="J83" t="n">
-        <v>97558.74000000001</v>
+        <v>275425.59</v>
       </c>
       <c r="K83" t="n">
         <v>0</v>
@@ -3690,37 +3690,37 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Akdeniz Endüstriyel Ürünler</t>
+          <t>Bölge Bayi C - Atlas</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Özel Sipariş Modeli X</t>
+          <t>Çelik Konstrüksiyon Montaj Paketi</t>
         </is>
       </c>
       <c r="C84" s="2" t="n">
         <v>45823</v>
       </c>
       <c r="D84" t="n">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="E84" t="n">
-        <v>21500</v>
+        <v>280000</v>
       </c>
       <c r="F84" t="n">
-        <v>1751178.4</v>
+        <v>566604.9</v>
       </c>
       <c r="G84" t="n">
-        <v>0</v>
+        <v>19393.26</v>
       </c>
       <c r="H84" t="n">
-        <v>1156592.24</v>
+        <v>455307.51</v>
       </c>
       <c r="I84" t="n">
-        <v>1751178.4</v>
+        <v>547211.64</v>
       </c>
       <c r="J84" t="n">
-        <v>1751178.4</v>
+        <v>547211.64</v>
       </c>
       <c r="K84" t="n">
         <v>0</v>
@@ -3729,37 +3729,37 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Güneydoğu Pazarlama Ltd.</t>
+          <t>Toptan Müşteri F - Atlas</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Ürün Epsilon Profesyonel</t>
+          <t>Çelik Konstrüksiyon Montaj Paketi</t>
         </is>
       </c>
       <c r="C85" s="2" t="n">
         <v>45825</v>
       </c>
       <c r="D85" t="n">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="E85" t="n">
-        <v>15400</v>
+        <v>280000</v>
       </c>
       <c r="F85" t="n">
-        <v>198052.49</v>
+        <v>728492.01</v>
       </c>
       <c r="G85" t="n">
-        <v>6385.41</v>
+        <v>41556.99</v>
       </c>
       <c r="H85" t="n">
-        <v>126033.4</v>
+        <v>585395.37</v>
       </c>
       <c r="I85" t="n">
-        <v>191667.08</v>
+        <v>686935.02</v>
       </c>
       <c r="J85" t="n">
-        <v>191667.08</v>
+        <v>686935.02</v>
       </c>
       <c r="K85" t="n">
         <v>0</v>
@@ -3768,37 +3768,37 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Gaziantep İhracat ve Toptan</t>
+          <t>Toptan Müşteri F - Atlas</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Ürün Alpha Standart</t>
+          <t>Çelik Konstrüksiyon Montaj Paketi</t>
         </is>
       </c>
       <c r="C86" s="2" t="n">
         <v>45827</v>
       </c>
       <c r="D86" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E86" t="n">
-        <v>1850</v>
+        <v>280000</v>
       </c>
       <c r="F86" t="n">
-        <v>134821.45</v>
+        <v>768963.79</v>
       </c>
       <c r="G86" t="n">
-        <v>7244.63</v>
+        <v>0</v>
       </c>
       <c r="H86" t="n">
-        <v>91095.57000000001</v>
+        <v>617917.33</v>
       </c>
       <c r="I86" t="n">
-        <v>127576.82</v>
+        <v>768963.79</v>
       </c>
       <c r="J86" t="n">
-        <v>127576.82</v>
+        <v>768963.79</v>
       </c>
       <c r="K86" t="n">
         <v>0</v>
@@ -3807,37 +3807,37 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Gaziantep İhracat ve Toptan</t>
+          <t>Ticari Kanal G - Atlas</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Ürün Gamma Endüstriyel</t>
+          <t>Mekanik ve Havalandırma Tesisatı</t>
         </is>
       </c>
       <c r="C87" s="2" t="n">
         <v>45829</v>
       </c>
       <c r="D87" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="E87" t="n">
-        <v>8900</v>
+        <v>195000</v>
       </c>
       <c r="F87" t="n">
-        <v>152611.88</v>
+        <v>281857.03</v>
       </c>
       <c r="G87" t="n">
-        <v>4920.36</v>
+        <v>0</v>
       </c>
       <c r="H87" t="n">
-        <v>101169.67</v>
+        <v>224040.2</v>
       </c>
       <c r="I87" t="n">
-        <v>147691.52</v>
+        <v>281857.03</v>
       </c>
       <c r="J87" t="n">
-        <v>147691.52</v>
+        <v>281857.03</v>
       </c>
       <c r="K87" t="n">
         <v>0</v>
@@ -3846,37 +3846,37 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Marmara Perakende Çözümleri</t>
+          <t>Bölge Bayi C - Atlas</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Ürün Gamma Endüstriyel</t>
+          <t>Şantiye Altyapı ve Drenaj İşi</t>
         </is>
       </c>
       <c r="C88" s="2" t="n">
         <v>45831</v>
       </c>
       <c r="D88" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="E88" t="n">
-        <v>8900</v>
+        <v>85000</v>
       </c>
       <c r="F88" t="n">
-        <v>267070.78</v>
+        <v>12286.08</v>
       </c>
       <c r="G88" t="n">
-        <v>0</v>
+        <v>700.86</v>
       </c>
       <c r="H88" t="n">
-        <v>177046.92</v>
+        <v>9828.860000000001</v>
       </c>
       <c r="I88" t="n">
-        <v>267070.78</v>
+        <v>11585.22</v>
       </c>
       <c r="J88" t="n">
-        <v>267070.78</v>
+        <v>11585.22</v>
       </c>
       <c r="K88" t="n">
         <v>0</v>
@@ -3885,37 +3885,37 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Marmara Perakende Çözümleri</t>
+          <t>Ticari Kanal G - Atlas</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Ürün Alpha Standart</t>
+          <t>İnce İşler Zemin Seramik &amp; Şap İşi</t>
         </is>
       </c>
       <c r="C89" s="2" t="n">
         <v>45833</v>
       </c>
       <c r="D89" t="n">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="E89" t="n">
-        <v>1850</v>
+        <v>120000</v>
       </c>
       <c r="F89" t="n">
-        <v>111029.43</v>
+        <v>34690.1</v>
       </c>
       <c r="G89" t="n">
         <v>0</v>
       </c>
       <c r="H89" t="n">
-        <v>75019.88</v>
+        <v>27462.99</v>
       </c>
       <c r="I89" t="n">
-        <v>111029.43</v>
+        <v>34690.1</v>
       </c>
       <c r="J89" t="n">
-        <v>111029.43</v>
+        <v>34690.1</v>
       </c>
       <c r="K89" t="n">
         <v>0</v>
@@ -3924,37 +3924,37 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>İzmir Ticari Faaliyetler A.Ş.</t>
+          <t>Toptan Müşteri F - Atlas</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Yedek Parça Servis Paketi</t>
+          <t>İnce İşler Zemin Seramik &amp; Şap İşi</t>
         </is>
       </c>
       <c r="C90" s="2" t="n">
         <v>45835</v>
       </c>
       <c r="D90" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E90" t="n">
-        <v>2400</v>
+        <v>120000</v>
       </c>
       <c r="F90" t="n">
-        <v>72019.09</v>
+        <v>138760.38</v>
       </c>
       <c r="G90" t="n">
-        <v>0</v>
+        <v>7915.62</v>
       </c>
       <c r="H90" t="n">
-        <v>45011.93</v>
+        <v>109851.97</v>
       </c>
       <c r="I90" t="n">
-        <v>72019.09</v>
+        <v>130844.76</v>
       </c>
       <c r="J90" t="n">
-        <v>72019.09</v>
+        <v>130844.76</v>
       </c>
       <c r="K90" t="n">
         <v>0</v>
@@ -3963,37 +3963,37 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Adana Bölge Bayi A.Ş.</t>
+          <t>Müşteri Grubu B - Atlas</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Ürün Epsilon Profesyonel</t>
+          <t>Dış Cephe Yalıtım ve Kompozit Giydirme</t>
         </is>
       </c>
       <c r="C91" s="2" t="n">
         <v>45837</v>
       </c>
       <c r="D91" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="E91" t="n">
-        <v>15400</v>
+        <v>165000</v>
       </c>
       <c r="F91" t="n">
-        <v>726192.46</v>
+        <v>119247.2</v>
       </c>
       <c r="G91" t="n">
-        <v>0</v>
+        <v>2720.99</v>
       </c>
       <c r="H91" t="n">
-        <v>462122.48</v>
+        <v>93952.34</v>
       </c>
       <c r="I91" t="n">
-        <v>726192.46</v>
+        <v>116526.21</v>
       </c>
       <c r="J91" t="n">
-        <v>726192.46</v>
+        <v>116526.21</v>
       </c>
       <c r="K91" t="n">
         <v>0</v>
@@ -4002,37 +4002,37 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Ege Dağıtım ve Ticaret Ltd.</t>
+          <t>Müşteri Grubu B - Atlas</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Yedek Parça Servis Paketi</t>
+          <t>Çelik Konstrüksiyon Montaj Paketi</t>
         </is>
       </c>
       <c r="C92" s="2" t="n">
         <v>45840</v>
       </c>
       <c r="D92" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="E92" t="n">
-        <v>2400</v>
+        <v>280000</v>
       </c>
       <c r="F92" t="n">
-        <v>185191.94</v>
+        <v>485661.34</v>
       </c>
       <c r="G92" t="n">
-        <v>5970.77</v>
+        <v>11081.86</v>
       </c>
       <c r="H92" t="n">
-        <v>115744.96</v>
+        <v>390263.58</v>
       </c>
       <c r="I92" t="n">
-        <v>179221.17</v>
+        <v>474579.48</v>
       </c>
       <c r="J92" t="n">
-        <v>179221.17</v>
+        <v>474579.48</v>
       </c>
       <c r="K92" t="n">
         <v>0</v>
@@ -4041,37 +4041,37 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>İstanbul Kurumsal Tedarik A.Ş.</t>
+          <t>Bölge Bayi C - Atlas</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Ürün Zeta Hızlı Tüketim</t>
+          <t>Şantiye Altyapı ve Drenaj İşi</t>
         </is>
       </c>
       <c r="C93" s="2" t="n">
         <v>45842</v>
       </c>
       <c r="D93" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="E93" t="n">
-        <v>650</v>
+        <v>85000</v>
       </c>
       <c r="F93" t="n">
-        <v>25078.07</v>
+        <v>36858.23</v>
       </c>
       <c r="G93" t="n">
-        <v>1347.57</v>
+        <v>841.03</v>
       </c>
       <c r="H93" t="n">
-        <v>16975.93</v>
+        <v>29486.58</v>
       </c>
       <c r="I93" t="n">
-        <v>23730.5</v>
+        <v>36017.2</v>
       </c>
       <c r="J93" t="n">
-        <v>23730.5</v>
+        <v>36017.2</v>
       </c>
       <c r="K93" t="n">
         <v>0</v>
@@ -4080,37 +4080,37 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Güneydoğu Pazarlama Ltd.</t>
+          <t>Ulusal Hesap H - Atlas</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Ürün Alpha Standart</t>
+          <t>Kaba İnşaat Taşeron Hakediş Paketi</t>
         </is>
       </c>
       <c r="C94" s="2" t="n">
         <v>45844</v>
       </c>
       <c r="D94" t="n">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="E94" t="n">
-        <v>1850</v>
+        <v>450000</v>
       </c>
       <c r="F94" t="n">
-        <v>182405.49</v>
+        <v>585395.37</v>
       </c>
       <c r="G94" t="n">
-        <v>9801.559999999999</v>
+        <v>0</v>
       </c>
       <c r="H94" t="n">
-        <v>123246.95</v>
+        <v>468316.29</v>
       </c>
       <c r="I94" t="n">
-        <v>172603.93</v>
+        <v>585395.37</v>
       </c>
       <c r="J94" t="n">
-        <v>172603.93</v>
+        <v>585395.37</v>
       </c>
       <c r="K94" t="n">
         <v>0</v>
@@ -4119,37 +4119,37 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Ankara Proje Yönetim ve Satış</t>
+          <t>Kurumsal Müşteri D - Atlas</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Yedek Parça Servis Paketi</t>
+          <t>Şantiye Altyapı ve Drenaj İşi</t>
         </is>
       </c>
       <c r="C95" s="2" t="n">
         <v>45846</v>
       </c>
       <c r="D95" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E95" t="n">
-        <v>2400</v>
+        <v>85000</v>
       </c>
       <c r="F95" t="n">
-        <v>41153.76</v>
+        <v>36858.23</v>
       </c>
       <c r="G95" t="n">
-        <v>1326.84</v>
+        <v>841.03</v>
       </c>
       <c r="H95" t="n">
-        <v>25721.1</v>
+        <v>29486.58</v>
       </c>
       <c r="I95" t="n">
-        <v>39826.92</v>
+        <v>36017.2</v>
       </c>
       <c r="J95" t="n">
-        <v>39826.92</v>
+        <v>36017.2</v>
       </c>
       <c r="K95" t="n">
         <v>0</v>
@@ -4158,37 +4158,37 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Marmara Perakende Çözümleri</t>
+          <t>Stratejik Ortak E - Atlas</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Ürün Gamma Endüstriyel</t>
+          <t>Kaba İnşaat Taşeron Hakediş Paketi</t>
         </is>
       </c>
       <c r="C96" s="2" t="n">
         <v>45848</v>
       </c>
       <c r="D96" t="n">
-        <v>19</v>
+        <v>1</v>
       </c>
       <c r="E96" t="n">
-        <v>8900</v>
+        <v>450000</v>
       </c>
       <c r="F96" t="n">
-        <v>724906.41</v>
+        <v>65043.93</v>
       </c>
       <c r="G96" t="n">
-        <v>38952.85</v>
+        <v>0</v>
       </c>
       <c r="H96" t="n">
-        <v>480555.93</v>
+        <v>52035.14</v>
       </c>
       <c r="I96" t="n">
-        <v>685953.5600000001</v>
+        <v>65043.93</v>
       </c>
       <c r="J96" t="n">
-        <v>685953.5600000001</v>
+        <v>65043.93</v>
       </c>
       <c r="K96" t="n">
         <v>0</v>
@@ -4197,37 +4197,37 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Ankara Proje Yönetim ve Satış</t>
+          <t>Ticari Kanal G - Atlas</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Ürün Beta Premium</t>
+          <t>Dış Cephe Yalıtım ve Kompozit Giydirme</t>
         </is>
       </c>
       <c r="C97" s="2" t="n">
         <v>45850</v>
       </c>
       <c r="D97" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="E97" t="n">
-        <v>4200</v>
+        <v>165000</v>
       </c>
       <c r="F97" t="n">
-        <v>72019.09</v>
+        <v>333892.17</v>
       </c>
       <c r="G97" t="n">
-        <v>3869.95</v>
+        <v>0</v>
       </c>
       <c r="H97" t="n">
-        <v>48012.72</v>
+        <v>263066.56</v>
       </c>
       <c r="I97" t="n">
-        <v>68149.14</v>
+        <v>333892.17</v>
       </c>
       <c r="J97" t="n">
-        <v>68149.14</v>
+        <v>333892.17</v>
       </c>
       <c r="K97" t="n">
         <v>0</v>
@@ -4236,37 +4236,37 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Kocaeli Ağır Sanayi Pazarlama</t>
+          <t>Ticari Kanal G - Atlas</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Ürün Beta Premium</t>
+          <t>Dış Cephe Yalıtım ve Kompozit Giydirme</t>
         </is>
       </c>
       <c r="C98" s="2" t="n">
         <v>45852</v>
       </c>
       <c r="D98" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="E98" t="n">
-        <v>4200</v>
+        <v>165000</v>
       </c>
       <c r="F98" t="n">
-        <v>180047.72</v>
+        <v>310042.73</v>
       </c>
       <c r="G98" t="n">
-        <v>9674.860000000001</v>
+        <v>7074.58</v>
       </c>
       <c r="H98" t="n">
-        <v>120031.81</v>
+        <v>244276.09</v>
       </c>
       <c r="I98" t="n">
-        <v>170372.86</v>
+        <v>302968.15</v>
       </c>
       <c r="J98" t="n">
-        <v>170372.86</v>
+        <v>302968.15</v>
       </c>
       <c r="K98" t="n">
         <v>0</v>
@@ -4275,37 +4275,37 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Gaziantep İhracat ve Toptan</t>
+          <t>Ticari Kanal G - Atlas</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Ürün Zeta Hızlı Tüketim</t>
+          <t>Kaba İnşaat Taşeron Hakediş Paketi</t>
         </is>
       </c>
       <c r="C99" s="2" t="n">
         <v>45854</v>
       </c>
       <c r="D99" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E99" t="n">
-        <v>650</v>
+        <v>450000</v>
       </c>
       <c r="F99" t="n">
-        <v>39010.34</v>
+        <v>1040702.87</v>
       </c>
       <c r="G99" t="n">
-        <v>838.49</v>
+        <v>59367.13</v>
       </c>
       <c r="H99" t="n">
-        <v>26407</v>
+        <v>832562.3</v>
       </c>
       <c r="I99" t="n">
-        <v>38171.85</v>
+        <v>981335.74</v>
       </c>
       <c r="J99" t="n">
-        <v>38171.85</v>
+        <v>981335.74</v>
       </c>
       <c r="K99" t="n">
         <v>0</v>
@@ -4314,37 +4314,37 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Akdeniz Endüstriyel Ürünler</t>
+          <t>Kurumsal Müşteri D - Atlas</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Özel Sipariş Modeli X</t>
+          <t>Çelik Konstrüksiyon Montaj Paketi</t>
         </is>
       </c>
       <c r="C100" s="2" t="n">
         <v>45856</v>
       </c>
       <c r="D100" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="E100" t="n">
-        <v>21500</v>
+        <v>280000</v>
       </c>
       <c r="F100" t="n">
-        <v>1751178.4</v>
+        <v>607076.67</v>
       </c>
       <c r="G100" t="n">
-        <v>94099.57000000001</v>
+        <v>0</v>
       </c>
       <c r="H100" t="n">
-        <v>1156592.24</v>
+        <v>487829.47</v>
       </c>
       <c r="I100" t="n">
-        <v>1657078.83</v>
+        <v>607076.67</v>
       </c>
       <c r="J100" t="n">
-        <v>1657078.83</v>
+        <v>607076.67</v>
       </c>
       <c r="K100" t="n">
         <v>0</v>
@@ -4353,37 +4353,37 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Güneydoğu Pazarlama Ltd.</t>
+          <t>Müşteri Grubu A - Atlas</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Ürün Alpha Standart</t>
+          <t>Mekanik ve Havalandırma Tesisatı</t>
         </is>
       </c>
       <c r="C101" s="2" t="n">
         <v>45858</v>
       </c>
       <c r="D101" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E101" t="n">
-        <v>1850</v>
+        <v>195000</v>
       </c>
       <c r="F101" t="n">
-        <v>47584.04</v>
+        <v>28185.7</v>
       </c>
       <c r="G101" t="n">
-        <v>1022.77</v>
+        <v>643.14</v>
       </c>
       <c r="H101" t="n">
-        <v>32151.38</v>
+        <v>22404.02</v>
       </c>
       <c r="I101" t="n">
-        <v>46561.27</v>
+        <v>27542.56</v>
       </c>
       <c r="J101" t="n">
-        <v>46561.27</v>
+        <v>27542.56</v>
       </c>
       <c r="K101" t="n">
         <v>0</v>
@@ -4392,37 +4392,37 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Akdeniz Endüstriyel Ürünler</t>
+          <t>Stratejik Ortak E - Atlas</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Ürün Gamma Endüstriyel</t>
+          <t>Kaba İnşaat Taşeron Hakediş Paketi</t>
         </is>
       </c>
       <c r="C102" s="2" t="n">
         <v>45860</v>
       </c>
       <c r="D102" t="n">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="E102" t="n">
-        <v>8900</v>
+        <v>450000</v>
       </c>
       <c r="F102" t="n">
-        <v>763059.38</v>
+        <v>195131.79</v>
       </c>
       <c r="G102" t="n">
-        <v>41003</v>
+        <v>4452.53</v>
       </c>
       <c r="H102" t="n">
-        <v>505848.35</v>
+        <v>156105.43</v>
       </c>
       <c r="I102" t="n">
-        <v>722056.38</v>
+        <v>190679.26</v>
       </c>
       <c r="J102" t="n">
-        <v>722056.38</v>
+        <v>190679.26</v>
       </c>
       <c r="K102" t="n">
         <v>0</v>
@@ -4431,37 +4431,37 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>İzmir Ticari Faaliyetler A.Ş.</t>
+          <t>Bölge Bayi C - Atlas</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Yedek Parça Servis Paketi</t>
+          <t>Dış Cephe Yalıtım ve Kompozit Giydirme</t>
         </is>
       </c>
       <c r="C103" s="2" t="n">
         <v>45862</v>
       </c>
       <c r="D103" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E103" t="n">
-        <v>2400</v>
+        <v>165000</v>
       </c>
       <c r="F103" t="n">
-        <v>20576.88</v>
+        <v>143096.64</v>
       </c>
       <c r="G103" t="n">
-        <v>663.42</v>
+        <v>0</v>
       </c>
       <c r="H103" t="n">
-        <v>12860.55</v>
+        <v>112742.81</v>
       </c>
       <c r="I103" t="n">
-        <v>19913.46</v>
+        <v>143096.64</v>
       </c>
       <c r="J103" t="n">
-        <v>19913.46</v>
+        <v>143096.64</v>
       </c>
       <c r="K103" t="n">
         <v>0</v>
@@ -4470,37 +4470,37 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Gaziantep İhracat ve Toptan</t>
+          <t>Müşteri Grubu B - Atlas</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Ürün Zeta Hızlı Tüketim</t>
+          <t>Mekanik ve Havalandırma Tesisatı</t>
         </is>
       </c>
       <c r="C104" s="2" t="n">
         <v>45864</v>
       </c>
       <c r="D104" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="E104" t="n">
-        <v>650</v>
+        <v>195000</v>
       </c>
       <c r="F104" t="n">
-        <v>64088.41</v>
+        <v>563714.0600000001</v>
       </c>
       <c r="G104" t="n">
-        <v>0</v>
+        <v>32157.2</v>
       </c>
       <c r="H104" t="n">
-        <v>43382.93</v>
+        <v>448080.4</v>
       </c>
       <c r="I104" t="n">
-        <v>64088.41</v>
+        <v>531556.86</v>
       </c>
       <c r="J104" t="n">
-        <v>64088.41</v>
+        <v>531556.86</v>
       </c>
       <c r="K104" t="n">
         <v>0</v>
@@ -4509,37 +4509,37 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Anadolu Sanayi Grubu A.Ş.</t>
+          <t>Ulusal Hesap H - Atlas</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Özel Sipariş Modeli X</t>
+          <t>Şantiye Altyapı ve Drenaj İşi</t>
         </is>
       </c>
       <c r="C105" s="2" t="n">
         <v>45866</v>
       </c>
       <c r="D105" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="E105" t="n">
-        <v>21500</v>
+        <v>85000</v>
       </c>
       <c r="F105" t="n">
-        <v>829505.5600000001</v>
+        <v>12286.08</v>
       </c>
       <c r="G105" t="n">
-        <v>17829.39</v>
+        <v>420.52</v>
       </c>
       <c r="H105" t="n">
-        <v>547859.48</v>
+        <v>9828.860000000001</v>
       </c>
       <c r="I105" t="n">
-        <v>811676.17</v>
+        <v>11865.56</v>
       </c>
       <c r="J105" t="n">
-        <v>811676.17</v>
+        <v>11865.56</v>
       </c>
       <c r="K105" t="n">
         <v>0</v>
@@ -4548,37 +4548,37 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Anadolu Sanayi Grubu A.Ş.</t>
+          <t>Bölge Bayi C - Atlas</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Ürün Zeta Hızlı Tüketim</t>
+          <t>İnce İşler Zemin Seramik &amp; Şap İşi</t>
         </is>
       </c>
       <c r="C106" s="2" t="n">
         <v>45868</v>
       </c>
       <c r="D106" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="E106" t="n">
-        <v>650</v>
+        <v>120000</v>
       </c>
       <c r="F106" t="n">
-        <v>27864.53</v>
+        <v>242830.67</v>
       </c>
       <c r="G106" t="n">
-        <v>598.92</v>
+        <v>0</v>
       </c>
       <c r="H106" t="n">
-        <v>18862.14</v>
+        <v>192240.95</v>
       </c>
       <c r="I106" t="n">
-        <v>27265.61</v>
+        <v>242830.67</v>
       </c>
       <c r="J106" t="n">
-        <v>27265.61</v>
+        <v>242830.67</v>
       </c>
       <c r="K106" t="n">
         <v>0</v>
@@ -4587,37 +4587,37 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Karadeniz Toptan Dağıtım A.Ş.</t>
+          <t>Müşteri Grubu A - Atlas</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Özel Sipariş Modeli X</t>
+          <t>Kaba İnşaat Taşeron Hakediş Paketi</t>
         </is>
       </c>
       <c r="C107" s="2" t="n">
         <v>45870</v>
       </c>
       <c r="D107" t="n">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="E107" t="n">
-        <v>21500</v>
+        <v>450000</v>
       </c>
       <c r="F107" t="n">
-        <v>2119847.54</v>
+        <v>715483.22</v>
       </c>
       <c r="G107" t="n">
         <v>0</v>
       </c>
       <c r="H107" t="n">
-        <v>1400085.35</v>
+        <v>572386.58</v>
       </c>
       <c r="I107" t="n">
-        <v>2119847.54</v>
+        <v>715483.22</v>
       </c>
       <c r="J107" t="n">
-        <v>2119847.54</v>
+        <v>715483.22</v>
       </c>
       <c r="K107" t="n">
         <v>0</v>
@@ -4626,37 +4626,37 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Adana Bölge Bayi A.Ş.</t>
+          <t>Kurumsal Müşteri D - Atlas</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Ürün Delta Kompakt</t>
+          <t>Dış Cephe Yalıtım ve Kompozit Giydirme</t>
         </is>
       </c>
       <c r="C108" s="2" t="n">
         <v>45872</v>
       </c>
       <c r="D108" t="n">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="E108" t="n">
-        <v>1200</v>
+        <v>165000</v>
       </c>
       <c r="F108" t="n">
-        <v>25721.1</v>
+        <v>429289.93</v>
       </c>
       <c r="G108" t="n">
-        <v>552.85</v>
+        <v>24488.94</v>
       </c>
       <c r="H108" t="n">
-        <v>17576.09</v>
+        <v>338228.43</v>
       </c>
       <c r="I108" t="n">
-        <v>25168.25</v>
+        <v>404800.99</v>
       </c>
       <c r="J108" t="n">
-        <v>25168.25</v>
+        <v>404800.99</v>
       </c>
       <c r="K108" t="n">
         <v>0</v>
@@ -4665,37 +4665,37 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Bursa İmalat Tedarik Ltd.</t>
+          <t>Stratejik Ortak E - Atlas</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Özel Sipariş Modeli X</t>
+          <t>Şantiye Altyapı ve Drenaj İşi</t>
         </is>
       </c>
       <c r="C109" s="2" t="n">
         <v>45874</v>
       </c>
       <c r="D109" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="E109" t="n">
-        <v>21500</v>
+        <v>85000</v>
       </c>
       <c r="F109" t="n">
-        <v>2304182.1</v>
+        <v>122860.76</v>
       </c>
       <c r="G109" t="n">
-        <v>49526.09</v>
+        <v>2803.45</v>
       </c>
       <c r="H109" t="n">
-        <v>1521831.9</v>
+        <v>98288.60000000001</v>
       </c>
       <c r="I109" t="n">
-        <v>2254656.01</v>
+        <v>120057.31</v>
       </c>
       <c r="J109" t="n">
-        <v>2254656.01</v>
+        <v>120057.31</v>
       </c>
       <c r="K109" t="n">
         <v>0</v>
@@ -4704,37 +4704,37 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Karadeniz Toptan Dağıtım A.Ş.</t>
+          <t>Kurumsal Müşteri D - Atlas</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Yedek Parça Servis Paketi</t>
+          <t>Kaba İnşaat Taşeron Hakediş Paketi</t>
         </is>
       </c>
       <c r="C110" s="2" t="n">
         <v>45876</v>
       </c>
       <c r="D110" t="n">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="E110" t="n">
-        <v>2400</v>
+        <v>450000</v>
       </c>
       <c r="F110" t="n">
-        <v>205768.82</v>
+        <v>130087.86</v>
       </c>
       <c r="G110" t="n">
-        <v>0</v>
+        <v>4452.53</v>
       </c>
       <c r="H110" t="n">
-        <v>128605.51</v>
+        <v>104070.29</v>
       </c>
       <c r="I110" t="n">
-        <v>205768.82</v>
+        <v>125635.33</v>
       </c>
       <c r="J110" t="n">
-        <v>205768.82</v>
+        <v>125635.33</v>
       </c>
       <c r="K110" t="n">
         <v>0</v>
@@ -4743,37 +4743,37 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Toroslar Lojistik ve Ticaret</t>
+          <t>Ulusal Hesap H - Atlas</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Özel Sipariş Modeli X</t>
+          <t>Çelik Konstrüksiyon Montaj Paketi</t>
         </is>
       </c>
       <c r="C111" s="2" t="n">
         <v>45878</v>
       </c>
       <c r="D111" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="E111" t="n">
-        <v>21500</v>
+        <v>280000</v>
       </c>
       <c r="F111" t="n">
-        <v>645170.99</v>
+        <v>80943.56</v>
       </c>
       <c r="G111" t="n">
-        <v>20800.96</v>
+        <v>1846.98</v>
       </c>
       <c r="H111" t="n">
-        <v>426112.93</v>
+        <v>65043.93</v>
       </c>
       <c r="I111" t="n">
-        <v>624370.03</v>
+        <v>79096.58</v>
       </c>
       <c r="J111" t="n">
-        <v>624370.03</v>
+        <v>79096.58</v>
       </c>
       <c r="K111" t="n">
         <v>0</v>
@@ -4782,37 +4782,37 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Bursa İmalat Tedarik Ltd.</t>
+          <t>Müşteri Grubu A - Atlas</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Özel Sipariş Modeli X</t>
+          <t>Dış Cephe Yalıtım ve Kompozit Giydirme</t>
         </is>
       </c>
       <c r="C112" s="2" t="n">
         <v>45880</v>
       </c>
       <c r="D112" t="n">
-        <v>25</v>
+        <v>3</v>
       </c>
       <c r="E112" t="n">
-        <v>21500</v>
+        <v>165000</v>
       </c>
       <c r="F112" t="n">
-        <v>2304182.1</v>
+        <v>71548.32000000001</v>
       </c>
       <c r="G112" t="n">
-        <v>123815.23</v>
+        <v>1632.6</v>
       </c>
       <c r="H112" t="n">
-        <v>1521831.9</v>
+        <v>56371.41</v>
       </c>
       <c r="I112" t="n">
-        <v>2180366.87</v>
+        <v>69915.72</v>
       </c>
       <c r="J112" t="n">
-        <v>2180366.87</v>
+        <v>69915.72</v>
       </c>
       <c r="K112" t="n">
         <v>0</v>
@@ -4821,37 +4821,37 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Adana Bölge Bayi A.Ş.</t>
+          <t>Ulusal Hesap H - Atlas</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Ürün Zeta Hızlı Tüketim</t>
+          <t>Çelik Konstrüksiyon Montaj Paketi</t>
         </is>
       </c>
       <c r="C113" s="2" t="n">
         <v>45882</v>
       </c>
       <c r="D113" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E113" t="n">
-        <v>650</v>
+        <v>280000</v>
       </c>
       <c r="F113" t="n">
-        <v>5572.91</v>
+        <v>161887.11</v>
       </c>
       <c r="G113" t="n">
-        <v>299.46</v>
+        <v>0</v>
       </c>
       <c r="H113" t="n">
-        <v>3772.43</v>
+        <v>130087.86</v>
       </c>
       <c r="I113" t="n">
-        <v>5273.45</v>
+        <v>161887.11</v>
       </c>
       <c r="J113" t="n">
-        <v>5273.45</v>
+        <v>161887.11</v>
       </c>
       <c r="K113" t="n">
         <v>0</v>
@@ -4860,37 +4860,37 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Kocaeli Ağır Sanayi Pazarlama</t>
+          <t>Kurumsal Müşteri D - Atlas</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Ürün Gamma Endüstriyel</t>
+          <t>Çelik Konstrüksiyon Montaj Paketi</t>
         </is>
       </c>
       <c r="C114" s="2" t="n">
         <v>45884</v>
       </c>
       <c r="D114" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="E114" t="n">
-        <v>8900</v>
+        <v>280000</v>
       </c>
       <c r="F114" t="n">
-        <v>114458.91</v>
+        <v>404717.78</v>
       </c>
       <c r="G114" t="n">
-        <v>2460.18</v>
+        <v>0</v>
       </c>
       <c r="H114" t="n">
-        <v>75877.25</v>
+        <v>325219.65</v>
       </c>
       <c r="I114" t="n">
-        <v>111998.73</v>
+        <v>404717.78</v>
       </c>
       <c r="J114" t="n">
-        <v>111998.73</v>
+        <v>404717.78</v>
       </c>
       <c r="K114" t="n">
         <v>0</v>
@@ -4899,37 +4899,37 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Bursa İmalat Tedarik Ltd.</t>
+          <t>Ulusal Hesap H - Atlas</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Yedek Parça Servis Paketi</t>
+          <t>Kaba İnşaat Taşeron Hakediş Paketi</t>
         </is>
       </c>
       <c r="C115" s="2" t="n">
         <v>45886</v>
       </c>
       <c r="D115" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E115" t="n">
-        <v>2400</v>
+        <v>450000</v>
       </c>
       <c r="F115" t="n">
-        <v>51442.21</v>
+        <v>650439.29</v>
       </c>
       <c r="G115" t="n">
-        <v>2764.25</v>
+        <v>22262.67</v>
       </c>
       <c r="H115" t="n">
-        <v>32151.38</v>
+        <v>520351.44</v>
       </c>
       <c r="I115" t="n">
-        <v>48677.96</v>
+        <v>628176.62</v>
       </c>
       <c r="J115" t="n">
-        <v>48677.96</v>
+        <v>628176.62</v>
       </c>
       <c r="K115" t="n">
         <v>0</v>
@@ -4938,37 +4938,37 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Gaziantep İhracat ve Toptan</t>
+          <t>Ulusal Hesap H - Atlas</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Ürün Alpha Standart</t>
+          <t>Dış Cephe Yalıtım ve Kompozit Giydirme</t>
         </is>
       </c>
       <c r="C116" s="2" t="n">
         <v>45888</v>
       </c>
       <c r="D116" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E116" t="n">
-        <v>1850</v>
+        <v>165000</v>
       </c>
       <c r="F116" t="n">
-        <v>47584.04</v>
+        <v>214644.97</v>
       </c>
       <c r="G116" t="n">
         <v>0</v>
       </c>
       <c r="H116" t="n">
-        <v>32151.38</v>
+        <v>169114.22</v>
       </c>
       <c r="I116" t="n">
-        <v>47584.04</v>
+        <v>214644.97</v>
       </c>
       <c r="J116" t="n">
-        <v>47584.04</v>
+        <v>214644.97</v>
       </c>
       <c r="K116" t="n">
         <v>0</v>
@@ -4977,37 +4977,37 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Gaziantep İhracat ve Toptan</t>
+          <t>Ticari Kanal G - Atlas</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Ürün Delta Kompakt</t>
+          <t>Çelik Konstrüksiyon Montaj Paketi</t>
         </is>
       </c>
       <c r="C117" s="2" t="n">
         <v>45890</v>
       </c>
       <c r="D117" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="E117" t="n">
-        <v>1200</v>
+        <v>280000</v>
       </c>
       <c r="F117" t="n">
-        <v>10288.44</v>
+        <v>485661.34</v>
       </c>
       <c r="G117" t="n">
-        <v>0</v>
+        <v>16622.8</v>
       </c>
       <c r="H117" t="n">
-        <v>7030.43</v>
+        <v>390263.58</v>
       </c>
       <c r="I117" t="n">
-        <v>10288.44</v>
+        <v>469038.54</v>
       </c>
       <c r="J117" t="n">
-        <v>10288.44</v>
+        <v>469038.54</v>
       </c>
       <c r="K117" t="n">
         <v>0</v>
@@ -5016,37 +5016,37 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Anadolu Sanayi Grubu A.Ş.</t>
+          <t>Toptan Müşteri F - Atlas</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Özel Sipariş Modeli X</t>
+          <t>Çelik Konstrüksiyon Montaj Paketi</t>
         </is>
       </c>
       <c r="C118" s="2" t="n">
         <v>45892</v>
       </c>
       <c r="D118" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="E118" t="n">
-        <v>21500</v>
+        <v>280000</v>
       </c>
       <c r="F118" t="n">
-        <v>184334.57</v>
+        <v>607076.67</v>
       </c>
       <c r="G118" t="n">
-        <v>3962.09</v>
+        <v>0</v>
       </c>
       <c r="H118" t="n">
-        <v>121746.55</v>
+        <v>487829.47</v>
       </c>
       <c r="I118" t="n">
-        <v>180372.48</v>
+        <v>607076.67</v>
       </c>
       <c r="J118" t="n">
-        <v>180372.48</v>
+        <v>607076.67</v>
       </c>
       <c r="K118" t="n">
         <v>0</v>
@@ -5055,37 +5055,37 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Bursa İmalat Tedarik Ltd.</t>
+          <t>Stratejik Ortak E - Atlas</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Ürün Delta Kompakt</t>
+          <t>Dış Cephe Yalıtım ve Kompozit Giydirme</t>
         </is>
       </c>
       <c r="C119" s="2" t="n">
         <v>45894</v>
       </c>
       <c r="D119" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="E119" t="n">
-        <v>1200</v>
+        <v>165000</v>
       </c>
       <c r="F119" t="n">
-        <v>46297.98</v>
+        <v>357741.61</v>
       </c>
       <c r="G119" t="n">
-        <v>995.13</v>
+        <v>8162.98</v>
       </c>
       <c r="H119" t="n">
-        <v>31636.96</v>
+        <v>281857.03</v>
       </c>
       <c r="I119" t="n">
-        <v>45302.85</v>
+        <v>349578.63</v>
       </c>
       <c r="J119" t="n">
-        <v>45302.85</v>
+        <v>349578.63</v>
       </c>
       <c r="K119" t="n">
         <v>0</v>
@@ -5094,37 +5094,37 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Adana Bölge Bayi A.Ş.</t>
+          <t>Kurumsal Müşteri D - Atlas</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Özel Sipariş Modeli X</t>
+          <t>Mekanik ve Havalandırma Tesisatı</t>
         </is>
       </c>
       <c r="C120" s="2" t="n">
         <v>45896</v>
       </c>
       <c r="D120" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E120" t="n">
-        <v>21500</v>
+        <v>195000</v>
       </c>
       <c r="F120" t="n">
-        <v>1566843.83</v>
+        <v>535528.35</v>
       </c>
       <c r="G120" t="n">
-        <v>50516.61</v>
+        <v>0</v>
       </c>
       <c r="H120" t="n">
-        <v>1034845.69</v>
+        <v>425676.38</v>
       </c>
       <c r="I120" t="n">
-        <v>1516327.22</v>
+        <v>535528.35</v>
       </c>
       <c r="J120" t="n">
-        <v>1516327.22</v>
+        <v>535528.35</v>
       </c>
       <c r="K120" t="n">
         <v>0</v>
@@ -5133,37 +5133,37 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>İzmir Ticari Faaliyetler A.Ş.</t>
+          <t>Bölge Bayi C - Atlas</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Ürün Beta Premium</t>
+          <t>Şantiye Altyapı ve Drenaj İşi</t>
         </is>
       </c>
       <c r="C121" s="2" t="n">
         <v>45898</v>
       </c>
       <c r="D121" t="n">
-        <v>22</v>
+        <v>4</v>
       </c>
       <c r="E121" t="n">
-        <v>4200</v>
+        <v>85000</v>
       </c>
       <c r="F121" t="n">
-        <v>396104.98</v>
+        <v>49144.3</v>
       </c>
       <c r="G121" t="n">
         <v>0</v>
       </c>
       <c r="H121" t="n">
-        <v>264069.99</v>
+        <v>39315.44</v>
       </c>
       <c r="I121" t="n">
-        <v>396104.98</v>
+        <v>49144.3</v>
       </c>
       <c r="J121" t="n">
-        <v>396104.98</v>
+        <v>49144.3</v>
       </c>
       <c r="K121" t="n">
         <v>0</v>
@@ -5172,37 +5172,37 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Toroslar Lojistik ve Ticaret</t>
+          <t>Toptan Müşteri F - Atlas</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Ürün Zeta Hızlı Tüketim</t>
+          <t>İnce İşler Zemin Seramik &amp; Şap İşi</t>
         </is>
       </c>
       <c r="C122" s="2" t="n">
         <v>45900</v>
       </c>
       <c r="D122" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="E122" t="n">
-        <v>650</v>
+        <v>120000</v>
       </c>
       <c r="F122" t="n">
-        <v>44583.24</v>
+        <v>242830.67</v>
       </c>
       <c r="G122" t="n">
-        <v>2395.68</v>
+        <v>13852.33</v>
       </c>
       <c r="H122" t="n">
-        <v>30179.43</v>
+        <v>192240.95</v>
       </c>
       <c r="I122" t="n">
-        <v>42187.56</v>
+        <v>228978.34</v>
       </c>
       <c r="J122" t="n">
-        <v>42187.56</v>
+        <v>228978.34</v>
       </c>
       <c r="K122" t="n">
         <v>0</v>
@@ -5211,37 +5211,37 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Güneydoğu Pazarlama Ltd.</t>
+          <t>Kurumsal Müşteri D - Atlas</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Ürün Gamma Endüstriyel</t>
+          <t>İnce İşler Zemin Seramik &amp; Şap İşi</t>
         </is>
       </c>
       <c r="C123" s="2" t="n">
         <v>45902</v>
       </c>
       <c r="D123" t="n">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="E123" t="n">
-        <v>8900</v>
+        <v>120000</v>
       </c>
       <c r="F123" t="n">
-        <v>610447.5</v>
+        <v>34690.1</v>
       </c>
       <c r="G123" t="n">
-        <v>32802.4</v>
+        <v>1187.34</v>
       </c>
       <c r="H123" t="n">
-        <v>404678.68</v>
+        <v>27462.99</v>
       </c>
       <c r="I123" t="n">
-        <v>577645.1</v>
+        <v>33502.76</v>
       </c>
       <c r="J123" t="n">
-        <v>577645.1</v>
+        <v>33502.76</v>
       </c>
       <c r="K123" t="n">
         <v>0</v>
@@ -5250,37 +5250,37 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>İstanbul Kurumsal Tedarik A.Ş.</t>
+          <t>Ticari Kanal G - Atlas</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Ürün Zeta Hızlı Tüketim</t>
+          <t>İnce İşler Zemin Seramik &amp; Şap İşi</t>
         </is>
       </c>
       <c r="C124" s="2" t="n">
         <v>45904</v>
       </c>
       <c r="D124" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E124" t="n">
-        <v>650</v>
+        <v>120000</v>
       </c>
       <c r="F124" t="n">
-        <v>33437.43</v>
+        <v>277520.77</v>
       </c>
       <c r="G124" t="n">
-        <v>0</v>
+        <v>15831.23</v>
       </c>
       <c r="H124" t="n">
-        <v>22634.57</v>
+        <v>219703.94</v>
       </c>
       <c r="I124" t="n">
-        <v>33437.43</v>
+        <v>261689.54</v>
       </c>
       <c r="J124" t="n">
-        <v>33437.43</v>
+        <v>261689.54</v>
       </c>
       <c r="K124" t="n">
         <v>0</v>
@@ -5289,37 +5289,37 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Adana Bölge Bayi A.Ş.</t>
+          <t>Kurumsal Müşteri D - Atlas</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Ürün Epsilon Profesyonel</t>
+          <t>Dış Cephe Yalıtım ve Kompozit Giydirme</t>
         </is>
       </c>
       <c r="C125" s="2" t="n">
         <v>45906</v>
       </c>
       <c r="D125" t="n">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="E125" t="n">
-        <v>15400</v>
+        <v>165000</v>
       </c>
       <c r="F125" t="n">
-        <v>1584419.92</v>
+        <v>238494.41</v>
       </c>
       <c r="G125" t="n">
         <v>0</v>
       </c>
       <c r="H125" t="n">
-        <v>1008267.22</v>
+        <v>187904.69</v>
       </c>
       <c r="I125" t="n">
-        <v>1584419.92</v>
+        <v>238494.41</v>
       </c>
       <c r="J125" t="n">
-        <v>1584419.92</v>
+        <v>238494.41</v>
       </c>
       <c r="K125" t="n">
         <v>0</v>
@@ -5328,37 +5328,37 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Karadeniz Toptan Dağıtım A.Ş.</t>
+          <t>Ticari Kanal G - Atlas</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Ürün Alpha Standart</t>
+          <t>Şantiye Altyapı ve Drenaj İşi</t>
         </is>
       </c>
       <c r="C126" s="2" t="n">
         <v>45908</v>
       </c>
       <c r="D126" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="E126" t="n">
-        <v>1850</v>
+        <v>85000</v>
       </c>
       <c r="F126" t="n">
-        <v>103098.75</v>
+        <v>24572.15</v>
       </c>
       <c r="G126" t="n">
-        <v>0</v>
+        <v>1401.72</v>
       </c>
       <c r="H126" t="n">
-        <v>69661.32000000001</v>
+        <v>19657.72</v>
       </c>
       <c r="I126" t="n">
-        <v>103098.75</v>
+        <v>23170.43</v>
       </c>
       <c r="J126" t="n">
-        <v>103098.75</v>
+        <v>23170.43</v>
       </c>
       <c r="K126" t="n">
         <v>0</v>
@@ -5367,37 +5367,37 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Marmara Perakende Çözümleri</t>
+          <t>Bölge Bayi C - Atlas</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Ürün Delta Kompakt</t>
+          <t>Kaba İnşaat Taşeron Hakediş Paketi</t>
         </is>
       </c>
       <c r="C127" s="2" t="n">
         <v>45910</v>
       </c>
       <c r="D127" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="E127" t="n">
-        <v>1200</v>
+        <v>450000</v>
       </c>
       <c r="F127" t="n">
-        <v>41153.76</v>
+        <v>975658.9399999999</v>
       </c>
       <c r="G127" t="n">
         <v>0</v>
       </c>
       <c r="H127" t="n">
-        <v>28121.74</v>
+        <v>780527.15</v>
       </c>
       <c r="I127" t="n">
-        <v>41153.76</v>
+        <v>975658.9399999999</v>
       </c>
       <c r="J127" t="n">
-        <v>41153.76</v>
+        <v>975658.9399999999</v>
       </c>
       <c r="K127" t="n">
         <v>0</v>
@@ -5406,37 +5406,37 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>İzmir Ticari Faaliyetler A.Ş.</t>
+          <t>Bölge Bayi C - Atlas</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Ürün Delta Kompakt</t>
+          <t>Çelik Konstrüksiyon Montaj Paketi</t>
         </is>
       </c>
       <c r="C128" s="2" t="n">
         <v>45912</v>
       </c>
       <c r="D128" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E128" t="n">
-        <v>1200</v>
+        <v>280000</v>
       </c>
       <c r="F128" t="n">
-        <v>46297.98</v>
+        <v>283302.45</v>
       </c>
       <c r="G128" t="n">
-        <v>1492.69</v>
+        <v>0</v>
       </c>
       <c r="H128" t="n">
-        <v>31636.96</v>
+        <v>227653.75</v>
       </c>
       <c r="I128" t="n">
-        <v>44805.29</v>
+        <v>283302.45</v>
       </c>
       <c r="J128" t="n">
-        <v>44805.29</v>
+        <v>283302.45</v>
       </c>
       <c r="K128" t="n">
         <v>0</v>
@@ -5445,37 +5445,37 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>İstanbul Kurumsal Tedarik A.Ş.</t>
+          <t>Müşteri Grubu A - Atlas</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Ürün Alpha Standart</t>
+          <t>Dış Cephe Yalıtım ve Kompozit Giydirme</t>
         </is>
       </c>
       <c r="C129" s="2" t="n">
         <v>45914</v>
       </c>
       <c r="D129" t="n">
-        <v>25</v>
+        <v>3</v>
       </c>
       <c r="E129" t="n">
-        <v>1850</v>
+        <v>165000</v>
       </c>
       <c r="F129" t="n">
-        <v>198266.83</v>
+        <v>71548.32000000001</v>
       </c>
       <c r="G129" t="n">
-        <v>0</v>
+        <v>2448.89</v>
       </c>
       <c r="H129" t="n">
-        <v>133964.08</v>
+        <v>56371.41</v>
       </c>
       <c r="I129" t="n">
-        <v>198266.83</v>
+        <v>69099.42999999999</v>
       </c>
       <c r="J129" t="n">
-        <v>198266.83</v>
+        <v>69099.42999999999</v>
       </c>
       <c r="K129" t="n">
         <v>0</v>
@@ -5484,37 +5484,37 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Güneydoğu Pazarlama Ltd.</t>
+          <t>Kurumsal Müşteri D - Atlas</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Ürün Gamma Endüstriyel</t>
+          <t>Şantiye Altyapı ve Drenaj İşi</t>
         </is>
       </c>
       <c r="C130" s="2" t="n">
         <v>45916</v>
       </c>
       <c r="D130" t="n">
-        <v>21</v>
+        <v>5</v>
       </c>
       <c r="E130" t="n">
-        <v>8900</v>
+        <v>85000</v>
       </c>
       <c r="F130" t="n">
-        <v>801212.34</v>
+        <v>61430.38</v>
       </c>
       <c r="G130" t="n">
-        <v>0</v>
+        <v>3504.31</v>
       </c>
       <c r="H130" t="n">
-        <v>531140.77</v>
+        <v>49144.3</v>
       </c>
       <c r="I130" t="n">
-        <v>801212.34</v>
+        <v>57926.07</v>
       </c>
       <c r="J130" t="n">
-        <v>801212.34</v>
+        <v>57926.07</v>
       </c>
       <c r="K130" t="n">
         <v>0</v>
@@ -5523,37 +5523,37 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Ankara Proje Yönetim ve Satış</t>
+          <t>Stratejik Ortak E - Atlas</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Ürün Alpha Standart</t>
+          <t>Mekanik ve Havalandırma Tesisatı</t>
         </is>
       </c>
       <c r="C131" s="2" t="n">
         <v>45918</v>
       </c>
       <c r="D131" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="E131" t="n">
-        <v>1850</v>
+        <v>195000</v>
       </c>
       <c r="F131" t="n">
-        <v>63445.39</v>
+        <v>84557.11</v>
       </c>
       <c r="G131" t="n">
-        <v>1363.7</v>
+        <v>0</v>
       </c>
       <c r="H131" t="n">
-        <v>42868.5</v>
+        <v>67212.06</v>
       </c>
       <c r="I131" t="n">
-        <v>62081.69</v>
+        <v>84557.11</v>
       </c>
       <c r="J131" t="n">
-        <v>62081.69</v>
+        <v>84557.11</v>
       </c>
       <c r="K131" t="n">
         <v>0</v>
@@ -5562,37 +5562,37 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Ankara Proje Yönetim ve Satış</t>
+          <t>Ticari Kanal G - Atlas</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Ürün Epsilon Profesyonel</t>
+          <t>İnce İşler Zemin Seramik &amp; Şap İşi</t>
         </is>
       </c>
       <c r="C132" s="2" t="n">
         <v>45920</v>
       </c>
       <c r="D132" t="n">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="E132" t="n">
-        <v>15400</v>
+        <v>120000</v>
       </c>
       <c r="F132" t="n">
-        <v>1518402.42</v>
+        <v>225485.62</v>
       </c>
       <c r="G132" t="n">
-        <v>32636.54</v>
+        <v>12862.88</v>
       </c>
       <c r="H132" t="n">
-        <v>966256.09</v>
+        <v>178509.45</v>
       </c>
       <c r="I132" t="n">
-        <v>1485765.88</v>
+        <v>212622.74</v>
       </c>
       <c r="J132" t="n">
-        <v>1485765.88</v>
+        <v>212622.74</v>
       </c>
       <c r="K132" t="n">
         <v>0</v>
@@ -5601,37 +5601,37 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Akdeniz Endüstriyel Ürünler</t>
+          <t>Toptan Müşteri F - Atlas</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Yedek Parça Servis Paketi</t>
+          <t>Mekanik ve Havalandırma Tesisatı</t>
         </is>
       </c>
       <c r="C133" s="2" t="n">
         <v>45922</v>
       </c>
       <c r="D133" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="E133" t="n">
-        <v>2400</v>
+        <v>195000</v>
       </c>
       <c r="F133" t="n">
-        <v>123461.29</v>
+        <v>479156.95</v>
       </c>
       <c r="G133" t="n">
-        <v>3980.52</v>
+        <v>16400.17</v>
       </c>
       <c r="H133" t="n">
-        <v>77163.31</v>
+        <v>380868.34</v>
       </c>
       <c r="I133" t="n">
-        <v>119480.77</v>
+        <v>462756.78</v>
       </c>
       <c r="J133" t="n">
-        <v>119480.77</v>
+        <v>462756.78</v>
       </c>
       <c r="K133" t="n">
         <v>0</v>
@@ -5640,37 +5640,37 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>Karadeniz Toptan Dağıtım A.Ş.</t>
+          <t>Müşteri Grubu A - Atlas</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Ürün Delta Kompakt</t>
+          <t>Şantiye Altyapı ve Drenaj İşi</t>
         </is>
       </c>
       <c r="C134" s="2" t="n">
         <v>45924</v>
       </c>
       <c r="D134" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E134" t="n">
-        <v>1200</v>
+        <v>85000</v>
       </c>
       <c r="F134" t="n">
-        <v>77163.31</v>
+        <v>245721.51</v>
       </c>
       <c r="G134" t="n">
-        <v>1658.55</v>
+        <v>14017.24</v>
       </c>
       <c r="H134" t="n">
-        <v>52728.26</v>
+        <v>196577.21</v>
       </c>
       <c r="I134" t="n">
-        <v>75504.75999999999</v>
+        <v>231704.27</v>
       </c>
       <c r="J134" t="n">
-        <v>75504.75999999999</v>
+        <v>231704.27</v>
       </c>
       <c r="K134" t="n">
         <v>0</v>
@@ -5679,37 +5679,37 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>İzmir Ticari Faaliyetler A.Ş.</t>
+          <t>Ticari Kanal G - Atlas</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Yedek Parça Servis Paketi</t>
+          <t>Kaba İnşaat Taşeron Hakediş Paketi</t>
         </is>
       </c>
       <c r="C135" s="2" t="n">
         <v>45926</v>
       </c>
       <c r="D135" t="n">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="E135" t="n">
-        <v>2400</v>
+        <v>450000</v>
       </c>
       <c r="F135" t="n">
-        <v>195480.38</v>
+        <v>910615.01</v>
       </c>
       <c r="G135" t="n">
         <v>0</v>
       </c>
       <c r="H135" t="n">
-        <v>122175.24</v>
+        <v>728492.01</v>
       </c>
       <c r="I135" t="n">
-        <v>195480.38</v>
+        <v>910615.01</v>
       </c>
       <c r="J135" t="n">
-        <v>195480.38</v>
+        <v>910615.01</v>
       </c>
       <c r="K135" t="n">
         <v>0</v>
@@ -5718,1455 +5718,1455 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Anadolu Sanayi Grubu A.Ş.</t>
+          <t>Bölge Bayi C - Atlas</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Ürün Zeta Hızlı Tüketim</t>
+          <t>İnce İşler Zemin Seramik &amp; Şap İşi</t>
         </is>
       </c>
       <c r="C136" s="2" t="n">
         <v>45928</v>
       </c>
       <c r="D136" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E136" t="n">
-        <v>650</v>
+        <v>120000</v>
       </c>
       <c r="F136" t="n">
-        <v>50156.15</v>
+        <v>329555.91</v>
       </c>
       <c r="G136" t="n">
-        <v>2695.14</v>
+        <v>18799.59</v>
       </c>
       <c r="H136" t="n">
-        <v>33951.86</v>
+        <v>260898.43</v>
       </c>
       <c r="I136" t="n">
-        <v>47461.01</v>
+        <v>310756.32</v>
       </c>
       <c r="J136" t="n">
-        <v>23730.51</v>
+        <v>155378.16</v>
       </c>
       <c r="K136" t="n">
-        <v>23730.5</v>
+        <v>155378.16</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>Ankara Proje Yönetim ve Satış</t>
+          <t>Müşteri Grubu B - Atlas</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Ürün Epsilon Profesyonel</t>
+          <t>Kaba İnşaat Taşeron Hakediş Paketi</t>
         </is>
       </c>
       <c r="C137" s="2" t="n">
         <v>45931</v>
       </c>
       <c r="D137" t="n">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="E137" t="n">
-        <v>15400</v>
+        <v>450000</v>
       </c>
       <c r="F137" t="n">
-        <v>660174.97</v>
+        <v>1235834.66</v>
       </c>
       <c r="G137" t="n">
         <v>0</v>
       </c>
       <c r="H137" t="n">
-        <v>420111.34</v>
+        <v>988667.73</v>
       </c>
       <c r="I137" t="n">
-        <v>660174.97</v>
+        <v>1235834.66</v>
       </c>
       <c r="J137" t="n">
-        <v>330087.48</v>
+        <v>370750.4</v>
       </c>
       <c r="K137" t="n">
-        <v>330087.49</v>
+        <v>865084.26</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>Güneydoğu Pazarlama Ltd.</t>
+          <t>Stratejik Ortak E - Atlas</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Ürün Beta Premium</t>
+          <t>İnce İşler Zemin Seramik &amp; Şap İşi</t>
         </is>
       </c>
       <c r="C138" s="2" t="n">
         <v>45933</v>
       </c>
       <c r="D138" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E138" t="n">
-        <v>4200</v>
+        <v>120000</v>
       </c>
       <c r="F138" t="n">
-        <v>198052.49</v>
+        <v>208140.57</v>
       </c>
       <c r="G138" t="n">
-        <v>4256.94</v>
+        <v>7124.06</v>
       </c>
       <c r="H138" t="n">
-        <v>132034.99</v>
+        <v>164777.95</v>
       </c>
       <c r="I138" t="n">
-        <v>193795.55</v>
+        <v>201016.51</v>
       </c>
       <c r="J138" t="n">
-        <v>0</v>
+        <v>100508.26</v>
       </c>
       <c r="K138" t="n">
-        <v>193795.55</v>
+        <v>100508.25</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>İzmir Ticari Faaliyetler A.Ş.</t>
+          <t>Stratejik Ortak E - Atlas</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Ürün Zeta Hızlı Tüketim</t>
+          <t>Dış Cephe Yalıtım ve Kompozit Giydirme</t>
         </is>
       </c>
       <c r="C139" s="2" t="n">
         <v>45935</v>
       </c>
       <c r="D139" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="E139" t="n">
-        <v>650</v>
+        <v>165000</v>
       </c>
       <c r="F139" t="n">
-        <v>25078.07</v>
+        <v>381591.05</v>
       </c>
       <c r="G139" t="n">
-        <v>539.03</v>
+        <v>21767.95</v>
       </c>
       <c r="H139" t="n">
-        <v>16975.93</v>
+        <v>300647.5</v>
       </c>
       <c r="I139" t="n">
-        <v>24539.04</v>
+        <v>359823.1</v>
       </c>
       <c r="J139" t="n">
-        <v>12269.52</v>
+        <v>107946.93</v>
       </c>
       <c r="K139" t="n">
-        <v>12269.52</v>
+        <v>251876.17</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>İzmir Ticari Faaliyetler A.Ş.</t>
+          <t>Ulusal Hesap H - Atlas</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Ürün Epsilon Profesyonel</t>
+          <t>Kaba İnşaat Taşeron Hakediş Paketi</t>
         </is>
       </c>
       <c r="C140" s="2" t="n">
         <v>45937</v>
       </c>
       <c r="D140" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E140" t="n">
-        <v>15400</v>
+        <v>450000</v>
       </c>
       <c r="F140" t="n">
-        <v>462122.48</v>
+        <v>390263.58</v>
       </c>
       <c r="G140" t="n">
-        <v>0</v>
+        <v>8905.07</v>
       </c>
       <c r="H140" t="n">
-        <v>294077.94</v>
+        <v>312210.86</v>
       </c>
       <c r="I140" t="n">
-        <v>462122.48</v>
+        <v>381358.51</v>
       </c>
       <c r="J140" t="n">
-        <v>0</v>
+        <v>190679.26</v>
       </c>
       <c r="K140" t="n">
-        <v>462122.48</v>
+        <v>190679.25</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>İstanbul Kurumsal Tedarik A.Ş.</t>
+          <t>Ticari Kanal G - Atlas</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Ürün Delta Kompakt</t>
+          <t>Çelik Konstrüksiyon Montaj Paketi</t>
         </is>
       </c>
       <c r="C141" s="2" t="n">
         <v>45939</v>
       </c>
       <c r="D141" t="n">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="E141" t="n">
-        <v>1200</v>
+        <v>280000</v>
       </c>
       <c r="F141" t="n">
-        <v>10288.44</v>
+        <v>809435.5699999999</v>
       </c>
       <c r="G141" t="n">
-        <v>552.85</v>
+        <v>46174.44</v>
       </c>
       <c r="H141" t="n">
-        <v>7030.43</v>
+        <v>650439.29</v>
       </c>
       <c r="I141" t="n">
-        <v>9735.59</v>
+        <v>763261.13</v>
       </c>
       <c r="J141" t="n">
-        <v>4867.8</v>
+        <v>228978.34</v>
       </c>
       <c r="K141" t="n">
-        <v>4867.79</v>
+        <v>534282.79</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>Akdeniz Endüstriyel Ürünler</t>
+          <t>Ticari Kanal G - Atlas</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Ürün Zeta Hızlı Tüketim</t>
+          <t>Kaba İnşaat Taşeron Hakediş Paketi</t>
         </is>
       </c>
       <c r="C142" s="2" t="n">
         <v>45941</v>
       </c>
       <c r="D142" t="n">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="E142" t="n">
-        <v>650</v>
+        <v>450000</v>
       </c>
       <c r="F142" t="n">
-        <v>61301.96</v>
+        <v>845571.08</v>
       </c>
       <c r="G142" t="n">
-        <v>0</v>
+        <v>19294.32</v>
       </c>
       <c r="H142" t="n">
-        <v>41496.71</v>
+        <v>676456.87</v>
       </c>
       <c r="I142" t="n">
-        <v>61301.96</v>
+        <v>826276.76</v>
       </c>
       <c r="J142" t="n">
         <v>0</v>
       </c>
       <c r="K142" t="n">
-        <v>61301.96</v>
+        <v>826276.76</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>Bursa İmalat Tedarik Ltd.</t>
+          <t>Kurumsal Müşteri D - Atlas</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Ürün Alpha Standart</t>
+          <t>Kaba İnşaat Taşeron Hakediş Paketi</t>
         </is>
       </c>
       <c r="C143" s="2" t="n">
         <v>45943</v>
       </c>
       <c r="D143" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="E143" t="n">
-        <v>1850</v>
+        <v>450000</v>
       </c>
       <c r="F143" t="n">
-        <v>166544.14</v>
+        <v>1040702.87</v>
       </c>
       <c r="G143" t="n">
-        <v>5369.55</v>
+        <v>23746.85</v>
       </c>
       <c r="H143" t="n">
-        <v>112529.82</v>
+        <v>832562.3</v>
       </c>
       <c r="I143" t="n">
-        <v>161174.59</v>
+        <v>1016956.02</v>
       </c>
       <c r="J143" t="n">
-        <v>80587.28999999999</v>
+        <v>508478.01</v>
       </c>
       <c r="K143" t="n">
-        <v>80587.3</v>
+        <v>508478.01</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>Karadeniz Toptan Dağıtım A.Ş.</t>
+          <t>Toptan Müşteri F - Atlas</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Ürün Epsilon Profesyonel</t>
+          <t>Kaba İnşaat Taşeron Hakediş Paketi</t>
         </is>
       </c>
       <c r="C144" s="2" t="n">
         <v>45945</v>
       </c>
       <c r="D144" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="E144" t="n">
-        <v>15400</v>
+        <v>450000</v>
       </c>
       <c r="F144" t="n">
-        <v>924244.95</v>
+        <v>715483.22</v>
       </c>
       <c r="G144" t="n">
-        <v>29798.58</v>
+        <v>16325.96</v>
       </c>
       <c r="H144" t="n">
-        <v>588155.88</v>
+        <v>572386.58</v>
       </c>
       <c r="I144" t="n">
-        <v>894446.37</v>
+        <v>699157.26</v>
       </c>
       <c r="J144" t="n">
-        <v>0</v>
+        <v>349578.63</v>
       </c>
       <c r="K144" t="n">
-        <v>894446.37</v>
+        <v>349578.63</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>Akdeniz Endüstriyel Ürünler</t>
+          <t>Stratejik Ortak E - Atlas</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Ürün Alpha Standart</t>
+          <t>Mekanik ve Havalandırma Tesisatı</t>
         </is>
       </c>
       <c r="C145" s="2" t="n">
         <v>45947</v>
       </c>
       <c r="D145" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="E145" t="n">
-        <v>1850</v>
+        <v>195000</v>
       </c>
       <c r="F145" t="n">
-        <v>150682.79</v>
+        <v>450971.24</v>
       </c>
       <c r="G145" t="n">
-        <v>8096.94</v>
+        <v>0</v>
       </c>
       <c r="H145" t="n">
-        <v>101812.7</v>
+        <v>358464.32</v>
       </c>
       <c r="I145" t="n">
-        <v>142585.85</v>
+        <v>450971.24</v>
       </c>
       <c r="J145" t="n">
         <v>0</v>
       </c>
       <c r="K145" t="n">
-        <v>142585.85</v>
+        <v>450971.24</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>Adana Bölge Bayi A.Ş.</t>
+          <t>Kurumsal Müşteri D - Atlas</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Ürün Delta Kompakt</t>
+          <t>Çelik Konstrüksiyon Montaj Paketi</t>
         </is>
       </c>
       <c r="C146" s="2" t="n">
         <v>45949</v>
       </c>
       <c r="D146" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E146" t="n">
-        <v>1200</v>
+        <v>280000</v>
       </c>
       <c r="F146" t="n">
-        <v>56586.43</v>
+        <v>404717.78</v>
       </c>
       <c r="G146" t="n">
-        <v>0</v>
+        <v>13852.33</v>
       </c>
       <c r="H146" t="n">
-        <v>38667.39</v>
+        <v>325219.65</v>
       </c>
       <c r="I146" t="n">
-        <v>56586.43</v>
+        <v>390865.45</v>
       </c>
       <c r="J146" t="n">
-        <v>28293.22</v>
+        <v>117259.63</v>
       </c>
       <c r="K146" t="n">
-        <v>28293.21</v>
+        <v>273605.82</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>İzmir Ticari Faaliyetler A.Ş.</t>
+          <t>Toptan Müşteri F - Atlas</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Özel Sipariş Modeli X</t>
+          <t>Mekanik ve Havalandırma Tesisatı</t>
         </is>
       </c>
       <c r="C147" s="2" t="n">
         <v>45951</v>
       </c>
       <c r="D147" t="n">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="E147" t="n">
-        <v>21500</v>
+        <v>195000</v>
       </c>
       <c r="F147" t="n">
-        <v>2027680.25</v>
+        <v>394599.84</v>
       </c>
       <c r="G147" t="n">
-        <v>43582.96</v>
+        <v>22510.04</v>
       </c>
       <c r="H147" t="n">
-        <v>1339212.07</v>
+        <v>313656.28</v>
       </c>
       <c r="I147" t="n">
-        <v>1984097.29</v>
+        <v>372089.8</v>
       </c>
       <c r="J147" t="n">
         <v>0</v>
       </c>
       <c r="K147" t="n">
-        <v>1984097.29</v>
+        <v>372089.8</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>İstanbul Kurumsal Tedarik A.Ş.</t>
+          <t>Müşteri Grubu B - Atlas</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Ürün Epsilon Profesyonel</t>
+          <t>Çelik Konstrüksiyon Montaj Paketi</t>
         </is>
       </c>
       <c r="C148" s="2" t="n">
         <v>45953</v>
       </c>
       <c r="D148" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="E148" t="n">
-        <v>15400</v>
+        <v>280000</v>
       </c>
       <c r="F148" t="n">
-        <v>396104.98</v>
+        <v>607076.67</v>
       </c>
       <c r="G148" t="n">
-        <v>21284.7</v>
+        <v>0</v>
       </c>
       <c r="H148" t="n">
-        <v>252066.81</v>
+        <v>487829.47</v>
       </c>
       <c r="I148" t="n">
-        <v>374820.28</v>
+        <v>607076.67</v>
       </c>
       <c r="J148" t="n">
-        <v>112446.08</v>
+        <v>182123</v>
       </c>
       <c r="K148" t="n">
-        <v>262374.2</v>
+        <v>424953.67</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>Marmara Perakende Çözümleri</t>
+          <t>Ticari Kanal G - Atlas</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Ürün Epsilon Profesyonel</t>
+          <t>Şantiye Altyapı ve Drenaj İşi</t>
         </is>
       </c>
       <c r="C149" s="2" t="n">
         <v>45955</v>
       </c>
       <c r="D149" t="n">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="E149" t="n">
-        <v>15400</v>
+        <v>85000</v>
       </c>
       <c r="F149" t="n">
-        <v>264069.99</v>
+        <v>196577.21</v>
       </c>
       <c r="G149" t="n">
-        <v>8513.879999999999</v>
+        <v>11213.79</v>
       </c>
       <c r="H149" t="n">
-        <v>168044.54</v>
+        <v>157261.77</v>
       </c>
       <c r="I149" t="n">
-        <v>255556.11</v>
+        <v>185363.42</v>
       </c>
       <c r="J149" t="n">
-        <v>76666.83</v>
+        <v>0</v>
       </c>
       <c r="K149" t="n">
-        <v>178889.28</v>
+        <v>185363.42</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>Marmara Perakende Çözümleri</t>
+          <t>Toptan Müşteri F - Atlas</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Ürün Epsilon Profesyonel</t>
+          <t>Kaba İnşaat Taşeron Hakediş Paketi</t>
         </is>
       </c>
       <c r="C150" s="2" t="n">
         <v>45957</v>
       </c>
       <c r="D150" t="n">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="E150" t="n">
-        <v>15400</v>
+        <v>450000</v>
       </c>
       <c r="F150" t="n">
-        <v>1584419.92</v>
+        <v>1105746.8</v>
       </c>
       <c r="G150" t="n">
-        <v>85138.81</v>
+        <v>0</v>
       </c>
       <c r="H150" t="n">
-        <v>1008267.22</v>
+        <v>884597.4399999999</v>
       </c>
       <c r="I150" t="n">
-        <v>1499281.11</v>
+        <v>1105746.8</v>
       </c>
       <c r="J150" t="n">
-        <v>449784.33</v>
+        <v>552873.4</v>
       </c>
       <c r="K150" t="n">
-        <v>1049496.78</v>
+        <v>552873.4</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>Kocaeli Ağır Sanayi Pazarlama</t>
+          <t>Müşteri Grubu B - Atlas</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Ürün Gamma Endüstriyel</t>
+          <t>Mekanik ve Havalandırma Tesisatı</t>
         </is>
       </c>
       <c r="C151" s="2" t="n">
         <v>45959</v>
       </c>
       <c r="D151" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="E151" t="n">
-        <v>8900</v>
+        <v>195000</v>
       </c>
       <c r="F151" t="n">
-        <v>839365.3100000001</v>
+        <v>479156.95</v>
       </c>
       <c r="G151" t="n">
-        <v>18041.32</v>
+        <v>16400.17</v>
       </c>
       <c r="H151" t="n">
-        <v>556433.1899999999</v>
+        <v>380868.34</v>
       </c>
       <c r="I151" t="n">
-        <v>821323.99</v>
+        <v>462756.78</v>
       </c>
       <c r="J151" t="n">
-        <v>0</v>
+        <v>138827.03</v>
       </c>
       <c r="K151" t="n">
-        <v>821323.99</v>
+        <v>323929.75</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>İzmir Ticari Faaliyetler A.Ş.</t>
+          <t>Bölge Bayi C - Atlas</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Ürün Beta Premium</t>
+          <t>İnce İşler Zemin Seramik &amp; Şap İşi</t>
         </is>
       </c>
       <c r="C152" s="2" t="n">
         <v>45961</v>
       </c>
       <c r="D152" t="n">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="E152" t="n">
-        <v>4200</v>
+        <v>120000</v>
       </c>
       <c r="F152" t="n">
-        <v>144038.17</v>
+        <v>329555.91</v>
       </c>
       <c r="G152" t="n">
-        <v>3095.96</v>
+        <v>0</v>
       </c>
       <c r="H152" t="n">
-        <v>96025.45</v>
+        <v>260898.43</v>
       </c>
       <c r="I152" t="n">
-        <v>140942.21</v>
+        <v>329555.91</v>
       </c>
       <c r="J152" t="n">
-        <v>70471.10000000001</v>
+        <v>164777.95</v>
       </c>
       <c r="K152" t="n">
-        <v>70471.11</v>
+        <v>164777.96</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>Toroslar Lojistik ve Ticaret</t>
+          <t>Bölge Bayi C - Atlas</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>Ürün Epsilon Profesyonel</t>
+          <t>Çelik Konstrüksiyon Montaj Paketi</t>
         </is>
       </c>
       <c r="C153" s="2" t="n">
         <v>45963</v>
       </c>
       <c r="D153" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="E153" t="n">
-        <v>15400</v>
+        <v>280000</v>
       </c>
       <c r="F153" t="n">
-        <v>924244.95</v>
+        <v>283302.45</v>
       </c>
       <c r="G153" t="n">
-        <v>19865.72</v>
+        <v>0</v>
       </c>
       <c r="H153" t="n">
-        <v>588155.88</v>
+        <v>227653.75</v>
       </c>
       <c r="I153" t="n">
-        <v>904379.23</v>
+        <v>283302.45</v>
       </c>
       <c r="J153" t="n">
-        <v>271313.77</v>
+        <v>141651.23</v>
       </c>
       <c r="K153" t="n">
-        <v>633065.46</v>
+        <v>141651.22</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>İç Anadolu Tüketim Malları</t>
+          <t>Kurumsal Müşteri D - Atlas</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>Ürün Epsilon Profesyonel</t>
+          <t>Kaba İnşaat Taşeron Hakediş Paketi</t>
         </is>
       </c>
       <c r="C154" s="2" t="n">
         <v>45965</v>
       </c>
       <c r="D154" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="E154" t="n">
-        <v>15400</v>
+        <v>450000</v>
       </c>
       <c r="F154" t="n">
-        <v>1254332.43</v>
+        <v>975658.9399999999</v>
       </c>
       <c r="G154" t="n">
-        <v>26960.62</v>
+        <v>0</v>
       </c>
       <c r="H154" t="n">
-        <v>798211.55</v>
+        <v>780527.15</v>
       </c>
       <c r="I154" t="n">
-        <v>1227371.81</v>
+        <v>975658.9399999999</v>
       </c>
       <c r="J154" t="n">
-        <v>368211.54</v>
+        <v>0</v>
       </c>
       <c r="K154" t="n">
-        <v>859160.27</v>
+        <v>975658.9399999999</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>Güneydoğu Pazarlama Ltd.</t>
+          <t>Toptan Müşteri F - Atlas</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>Ürün Beta Premium</t>
+          <t>Şantiye Altyapı ve Drenaj İşi</t>
         </is>
       </c>
       <c r="C155" s="2" t="n">
         <v>45967</v>
       </c>
       <c r="D155" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="E155" t="n">
-        <v>4200</v>
+        <v>85000</v>
       </c>
       <c r="F155" t="n">
-        <v>288076.35</v>
+        <v>86002.53</v>
       </c>
       <c r="G155" t="n">
-        <v>0</v>
+        <v>1962.41</v>
       </c>
       <c r="H155" t="n">
-        <v>192050.9</v>
+        <v>68802.02</v>
       </c>
       <c r="I155" t="n">
-        <v>288076.35</v>
+        <v>84040.12</v>
       </c>
       <c r="J155" t="n">
-        <v>144038.17</v>
+        <v>42020.06</v>
       </c>
       <c r="K155" t="n">
-        <v>144038.18</v>
+        <v>42020.06</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>Adana Bölge Bayi A.Ş.</t>
+          <t>Toptan Müşteri F - Atlas</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>Ürün Beta Premium</t>
+          <t>Dış Cephe Yalıtım ve Kompozit Giydirme</t>
         </is>
       </c>
       <c r="C156" s="2" t="n">
         <v>45969</v>
       </c>
       <c r="D156" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E156" t="n">
-        <v>4200</v>
+        <v>165000</v>
       </c>
       <c r="F156" t="n">
-        <v>288076.35</v>
+        <v>405440.49</v>
       </c>
       <c r="G156" t="n">
-        <v>0</v>
+        <v>13877.07</v>
       </c>
       <c r="H156" t="n">
-        <v>192050.9</v>
+        <v>319437.96</v>
       </c>
       <c r="I156" t="n">
-        <v>288076.35</v>
+        <v>391563.42</v>
       </c>
       <c r="J156" t="n">
-        <v>0</v>
+        <v>117469.03</v>
       </c>
       <c r="K156" t="n">
-        <v>288076.35</v>
+        <v>274094.39</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>İstanbul Kurumsal Tedarik A.Ş.</t>
+          <t>Müşteri Grubu B - Atlas</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>Ürün Beta Premium</t>
+          <t>Şantiye Altyapı ve Drenaj İşi</t>
         </is>
       </c>
       <c r="C157" s="2" t="n">
         <v>45971</v>
       </c>
       <c r="D157" t="n">
-        <v>22</v>
+        <v>1</v>
       </c>
       <c r="E157" t="n">
-        <v>4200</v>
+        <v>85000</v>
       </c>
       <c r="F157" t="n">
-        <v>396104.98</v>
+        <v>12286.08</v>
       </c>
       <c r="G157" t="n">
-        <v>12770.82</v>
+        <v>0</v>
       </c>
       <c r="H157" t="n">
-        <v>264069.99</v>
+        <v>9828.860000000001</v>
       </c>
       <c r="I157" t="n">
-        <v>383334.16</v>
+        <v>12286.08</v>
       </c>
       <c r="J157" t="n">
-        <v>0</v>
+        <v>6143.04</v>
       </c>
       <c r="K157" t="n">
-        <v>383334.16</v>
+        <v>6143.04</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>İstanbul Kurumsal Tedarik A.Ş.</t>
+          <t>Toptan Müşteri F - Atlas</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>Ürün Epsilon Profesyonel</t>
+          <t>Dış Cephe Yalıtım ve Kompozit Giydirme</t>
         </is>
       </c>
       <c r="C158" s="2" t="n">
         <v>45973</v>
       </c>
       <c r="D158" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="E158" t="n">
-        <v>15400</v>
+        <v>165000</v>
       </c>
       <c r="F158" t="n">
-        <v>924244.95</v>
+        <v>476988.82</v>
       </c>
       <c r="G158" t="n">
-        <v>0</v>
+        <v>16325.96</v>
       </c>
       <c r="H158" t="n">
-        <v>588155.88</v>
+        <v>375809.37</v>
       </c>
       <c r="I158" t="n">
-        <v>924244.95</v>
+        <v>460662.86</v>
       </c>
       <c r="J158" t="n">
-        <v>462122.47</v>
+        <v>0</v>
       </c>
       <c r="K158" t="n">
-        <v>462122.48</v>
+        <v>460662.86</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>Adana Bölge Bayi A.Ş.</t>
+          <t>Bölge Bayi C - Atlas</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>Ürün Gamma Endüstriyel</t>
+          <t>Dış Cephe Yalıtım ve Kompozit Giydirme</t>
         </is>
       </c>
       <c r="C159" s="2" t="n">
         <v>45975</v>
       </c>
       <c r="D159" t="n">
-        <v>5</v>
+        <v>19</v>
       </c>
       <c r="E159" t="n">
-        <v>8900</v>
+        <v>165000</v>
       </c>
       <c r="F159" t="n">
-        <v>190764.84</v>
+        <v>453139.38</v>
       </c>
       <c r="G159" t="n">
-        <v>0</v>
+        <v>25849.44</v>
       </c>
       <c r="H159" t="n">
-        <v>126462.09</v>
+        <v>357018.9</v>
       </c>
       <c r="I159" t="n">
-        <v>190764.84</v>
+        <v>427289.94</v>
       </c>
       <c r="J159" t="n">
-        <v>95382.42</v>
+        <v>0</v>
       </c>
       <c r="K159" t="n">
-        <v>95382.42</v>
+        <v>427289.94</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>İç Anadolu Tüketim Malları</t>
+          <t>Toptan Müşteri F - Atlas</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>Yedek Parça Servis Paketi</t>
+          <t>Mekanik ve Havalandırma Tesisatı</t>
         </is>
       </c>
       <c r="C160" s="2" t="n">
         <v>45977</v>
       </c>
       <c r="D160" t="n">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="E160" t="n">
-        <v>2400</v>
+        <v>195000</v>
       </c>
       <c r="F160" t="n">
-        <v>195480.38</v>
+        <v>169114.22</v>
       </c>
       <c r="G160" t="n">
-        <v>6302.48</v>
+        <v>3858.86</v>
       </c>
       <c r="H160" t="n">
-        <v>122175.24</v>
+        <v>134424.12</v>
       </c>
       <c r="I160" t="n">
-        <v>189177.9</v>
+        <v>165255.36</v>
       </c>
       <c r="J160" t="n">
-        <v>94588.95</v>
+        <v>49576.61</v>
       </c>
       <c r="K160" t="n">
-        <v>94588.95</v>
+        <v>115678.75</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>Marmara Perakende Çözümleri</t>
+          <t>Müşteri Grubu B - Atlas</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>Ürün Zeta Hızlı Tüketim</t>
+          <t>Mekanik ve Havalandırma Tesisatı</t>
         </is>
       </c>
       <c r="C161" s="2" t="n">
         <v>45979</v>
       </c>
       <c r="D161" t="n">
-        <v>23</v>
+        <v>1</v>
       </c>
       <c r="E161" t="n">
-        <v>650</v>
+        <v>195000</v>
       </c>
       <c r="F161" t="n">
-        <v>64088.41</v>
+        <v>28185.7</v>
       </c>
       <c r="G161" t="n">
-        <v>0</v>
+        <v>964.72</v>
       </c>
       <c r="H161" t="n">
-        <v>43382.93</v>
+        <v>22404.02</v>
       </c>
       <c r="I161" t="n">
-        <v>64088.41</v>
+        <v>27220.98</v>
       </c>
       <c r="J161" t="n">
         <v>0</v>
       </c>
       <c r="K161" t="n">
-        <v>64088.41</v>
+        <v>27220.98</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>Kocaeli Ağır Sanayi Pazarlama</t>
+          <t>Müşteri Grubu A - Atlas</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>Ürün Beta Premium</t>
+          <t>Çelik Konstrüksiyon Montaj Paketi</t>
         </is>
       </c>
       <c r="C162" s="2" t="n">
         <v>45981</v>
       </c>
       <c r="D162" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="E162" t="n">
-        <v>4200</v>
+        <v>280000</v>
       </c>
       <c r="F162" t="n">
-        <v>288076.35</v>
+        <v>768963.79</v>
       </c>
       <c r="G162" t="n">
-        <v>6191.91</v>
+        <v>0</v>
       </c>
       <c r="H162" t="n">
-        <v>192050.9</v>
+        <v>617917.33</v>
       </c>
       <c r="I162" t="n">
-        <v>281884.44</v>
+        <v>768963.79</v>
       </c>
       <c r="J162" t="n">
-        <v>84565.33</v>
+        <v>384481.9</v>
       </c>
       <c r="K162" t="n">
-        <v>197319.11</v>
+        <v>384481.89</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>İzmir Ticari Faaliyetler A.Ş.</t>
+          <t>Kurumsal Müşteri D - Atlas</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>Ürün Gamma Endüstriyel</t>
+          <t>Şantiye Altyapı ve Drenaj İşi</t>
         </is>
       </c>
       <c r="C163" s="2" t="n">
         <v>45983</v>
       </c>
       <c r="D163" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E163" t="n">
-        <v>8900</v>
+        <v>85000</v>
       </c>
       <c r="F163" t="n">
-        <v>419682.66</v>
+        <v>98288.60000000001</v>
       </c>
       <c r="G163" t="n">
         <v>0</v>
       </c>
       <c r="H163" t="n">
-        <v>278216.59</v>
+        <v>78630.88</v>
       </c>
       <c r="I163" t="n">
-        <v>419682.66</v>
+        <v>98288.60000000001</v>
       </c>
       <c r="J163" t="n">
-        <v>125904.8</v>
+        <v>29486.58</v>
       </c>
       <c r="K163" t="n">
-        <v>293777.86</v>
+        <v>68802.02</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>Anadolu Sanayi Grubu A.Ş.</t>
+          <t>Stratejik Ortak E - Atlas</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>Özel Sipariş Modeli X</t>
+          <t>Şantiye Altyapı ve Drenaj İşi</t>
         </is>
       </c>
       <c r="C164" s="2" t="n">
         <v>45985</v>
       </c>
       <c r="D164" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="E164" t="n">
-        <v>21500</v>
+        <v>85000</v>
       </c>
       <c r="F164" t="n">
-        <v>829505.5600000001</v>
+        <v>172005.06</v>
       </c>
       <c r="G164" t="n">
-        <v>0</v>
+        <v>9812.07</v>
       </c>
       <c r="H164" t="n">
-        <v>547859.48</v>
+        <v>137604.05</v>
       </c>
       <c r="I164" t="n">
-        <v>829505.5600000001</v>
+        <v>162192.99</v>
       </c>
       <c r="J164" t="n">
-        <v>414752.78</v>
+        <v>48657.9</v>
       </c>
       <c r="K164" t="n">
-        <v>414752.78</v>
+        <v>113535.09</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>Kocaeli Ağır Sanayi Pazarlama</t>
+          <t>Müşteri Grubu A - Atlas</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>Ürün Gamma Endüstriyel</t>
+          <t>Şantiye Altyapı ve Drenaj İşi</t>
         </is>
       </c>
       <c r="C165" s="2" t="n">
         <v>45987</v>
       </c>
       <c r="D165" t="n">
-        <v>19</v>
+        <v>1</v>
       </c>
       <c r="E165" t="n">
-        <v>8900</v>
+        <v>85000</v>
       </c>
       <c r="F165" t="n">
-        <v>724906.41</v>
+        <v>12286.08</v>
       </c>
       <c r="G165" t="n">
-        <v>0</v>
+        <v>420.52</v>
       </c>
       <c r="H165" t="n">
-        <v>480555.93</v>
+        <v>9828.860000000001</v>
       </c>
       <c r="I165" t="n">
-        <v>724906.41</v>
+        <v>11865.56</v>
       </c>
       <c r="J165" t="n">
-        <v>0</v>
+        <v>3559.67</v>
       </c>
       <c r="K165" t="n">
-        <v>724906.41</v>
+        <v>8305.889999999999</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>Güneydoğu Pazarlama Ltd.</t>
+          <t>Bölge Bayi C - Atlas</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>Ürün Beta Premium</t>
+          <t>Şantiye Altyapı ve Drenaj İşi</t>
         </is>
       </c>
       <c r="C166" s="2" t="n">
         <v>45989</v>
       </c>
       <c r="D166" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E166" t="n">
-        <v>4200</v>
+        <v>85000</v>
       </c>
       <c r="F166" t="n">
-        <v>90023.86</v>
+        <v>73716.45</v>
       </c>
       <c r="G166" t="n">
-        <v>4837.43</v>
+        <v>4205.17</v>
       </c>
       <c r="H166" t="n">
-        <v>60015.91</v>
+        <v>58973.16</v>
       </c>
       <c r="I166" t="n">
-        <v>85186.42999999999</v>
+        <v>69511.28</v>
       </c>
       <c r="J166" t="n">
-        <v>42593.21</v>
+        <v>20853.38</v>
       </c>
       <c r="K166" t="n">
-        <v>42593.22</v>
+        <v>48657.9</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>Akdeniz Endüstriyel Ürünler</t>
+          <t>Müşteri Grubu A - Atlas</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>Yedek Parça Servis Paketi</t>
+          <t>Çelik Konstrüksiyon Montaj Paketi</t>
         </is>
       </c>
       <c r="C167" s="2" t="n">
         <v>45991</v>
       </c>
       <c r="D167" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E167" t="n">
-        <v>2400</v>
+        <v>280000</v>
       </c>
       <c r="F167" t="n">
-        <v>133749.73</v>
+        <v>364246</v>
       </c>
       <c r="G167" t="n">
-        <v>4312.23</v>
+        <v>20778.5</v>
       </c>
       <c r="H167" t="n">
-        <v>83593.58</v>
+        <v>292697.68</v>
       </c>
       <c r="I167" t="n">
-        <v>129437.5</v>
+        <v>343467.5</v>
       </c>
       <c r="J167" t="n">
-        <v>64718.75</v>
+        <v>103040.25</v>
       </c>
       <c r="K167" t="n">
-        <v>64718.75</v>
+        <v>240427.25</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>Güneydoğu Pazarlama Ltd.</t>
+          <t>Stratejik Ortak E - Atlas</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>Yedek Parça Servis Paketi</t>
+          <t>Şantiye Altyapı ve Drenaj İşi</t>
         </is>
       </c>
       <c r="C168" s="2" t="n">
         <v>45993</v>
       </c>
       <c r="D168" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="E168" t="n">
-        <v>2400</v>
+        <v>85000</v>
       </c>
       <c r="F168" t="n">
-        <v>10288.44</v>
+        <v>110574.68</v>
       </c>
       <c r="G168" t="n">
-        <v>0</v>
+        <v>3784.65</v>
       </c>
       <c r="H168" t="n">
-        <v>6430.28</v>
+        <v>88459.74000000001</v>
       </c>
       <c r="I168" t="n">
-        <v>10288.44</v>
+        <v>106790.03</v>
       </c>
       <c r="J168" t="n">
-        <v>3086.53</v>
+        <v>53395.01</v>
       </c>
       <c r="K168" t="n">
-        <v>7201.91</v>
+        <v>53395.02</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>İstanbul Kurumsal Tedarik A.Ş.</t>
+          <t>Ticari Kanal G - Atlas</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>Ürün Delta Kompakt</t>
+          <t>Mekanik ve Havalandırma Tesisatı</t>
         </is>
       </c>
       <c r="C169" s="2" t="n">
         <v>45995</v>
       </c>
       <c r="D169" t="n">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="E169" t="n">
-        <v>1200</v>
+        <v>195000</v>
       </c>
       <c r="F169" t="n">
-        <v>123461.29</v>
+        <v>422785.54</v>
       </c>
       <c r="G169" t="n">
-        <v>2653.68</v>
+        <v>9647.16</v>
       </c>
       <c r="H169" t="n">
-        <v>84365.22</v>
+        <v>336060.3</v>
       </c>
       <c r="I169" t="n">
-        <v>120807.61</v>
+        <v>413138.38</v>
       </c>
       <c r="J169" t="n">
-        <v>60403.81</v>
+        <v>123941.51</v>
       </c>
       <c r="K169" t="n">
-        <v>60403.8</v>
+        <v>289196.87</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>Anadolu Sanayi Grubu A.Ş.</t>
+          <t>Kurumsal Müşteri D - Atlas</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>Ürün Zeta Hızlı Tüketim</t>
+          <t>Dış Cephe Yalıtım ve Kompozit Giydirme</t>
         </is>
       </c>
       <c r="C170" s="2" t="n">
         <v>45997</v>
       </c>
       <c r="D170" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="E170" t="n">
-        <v>650</v>
+        <v>165000</v>
       </c>
       <c r="F170" t="n">
-        <v>69661.32000000001</v>
+        <v>238494.41</v>
       </c>
       <c r="G170" t="n">
-        <v>3743.25</v>
+        <v>13604.97</v>
       </c>
       <c r="H170" t="n">
-        <v>47155.35</v>
+        <v>187904.69</v>
       </c>
       <c r="I170" t="n">
-        <v>65918.07000000001</v>
+        <v>224889.44</v>
       </c>
       <c r="J170" t="n">
-        <v>32959.04</v>
+        <v>67466.83</v>
       </c>
       <c r="K170" t="n">
-        <v>32959.03</v>
+        <v>157422.61</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>Toroslar Lojistik ve Ticaret</t>
+          <t>Ticari Kanal G - Atlas</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>Ürün Alpha Standart</t>
+          <t>İnce İşler Zemin Seramik &amp; Şap İşi</t>
         </is>
       </c>
       <c r="C171" s="2" t="n">
         <v>45999</v>
       </c>
       <c r="D171" t="n">
-        <v>22</v>
+        <v>4</v>
       </c>
       <c r="E171" t="n">
-        <v>1850</v>
+        <v>120000</v>
       </c>
       <c r="F171" t="n">
-        <v>174474.81</v>
+        <v>69380.19</v>
       </c>
       <c r="G171" t="n">
         <v>0</v>
       </c>
       <c r="H171" t="n">
-        <v>117888.39</v>
+        <v>54925.98</v>
       </c>
       <c r="I171" t="n">
-        <v>174474.81</v>
+        <v>69380.19</v>
       </c>
       <c r="J171" t="n">
-        <v>87237.39999999999</v>
+        <v>0</v>
       </c>
       <c r="K171" t="n">
-        <v>87237.41</v>
+        <v>69380.19</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>İzmir Ticari Faaliyetler A.Ş.</t>
+          <t>Toptan Müşteri F - Atlas</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Ürün Delta Kompakt</t>
+          <t>İnce İşler Zemin Seramik &amp; Şap İşi</t>
         </is>
       </c>
       <c r="C172" s="2" t="n">
         <v>46001</v>
       </c>
       <c r="D172" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="E172" t="n">
-        <v>1200</v>
+        <v>120000</v>
       </c>
       <c r="F172" t="n">
-        <v>41153.76</v>
+        <v>346900.96</v>
       </c>
       <c r="G172" t="n">
-        <v>884.5599999999999</v>
+        <v>19789.04</v>
       </c>
       <c r="H172" t="n">
-        <v>28121.74</v>
+        <v>274629.92</v>
       </c>
       <c r="I172" t="n">
-        <v>40269.2</v>
+        <v>327111.92</v>
       </c>
       <c r="J172" t="n">
-        <v>0</v>
+        <v>98133.58</v>
       </c>
       <c r="K172" t="n">
-        <v>40269.2</v>
+        <v>228978.34</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>Karadeniz Toptan Dağıtım A.Ş.</t>
+          <t>Stratejik Ortak E - Atlas</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>Ürün Gamma Endüstriyel</t>
+          <t>Mekanik ve Havalandırma Tesisatı</t>
         </is>
       </c>
       <c r="C173" s="2" t="n">
@@ -7176,75 +7176,75 @@
         <v>4</v>
       </c>
       <c r="E173" t="n">
-        <v>8900</v>
+        <v>195000</v>
       </c>
       <c r="F173" t="n">
-        <v>152611.88</v>
+        <v>112742.81</v>
       </c>
       <c r="G173" t="n">
-        <v>4920.36</v>
+        <v>3858.86</v>
       </c>
       <c r="H173" t="n">
-        <v>101169.67</v>
+        <v>89616.08</v>
       </c>
       <c r="I173" t="n">
-        <v>147691.52</v>
+        <v>108883.95</v>
       </c>
       <c r="J173" t="n">
-        <v>44307.46</v>
+        <v>0</v>
       </c>
       <c r="K173" t="n">
-        <v>103384.06</v>
+        <v>108883.95</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>İstanbul Kurumsal Tedarik A.Ş.</t>
+          <t>Müşteri Grubu B - Atlas</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>Ürün Epsilon Profesyonel</t>
+          <t>Mekanik ve Havalandırma Tesisatı</t>
         </is>
       </c>
       <c r="C174" s="2" t="n">
         <v>46005</v>
       </c>
       <c r="D174" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E174" t="n">
-        <v>15400</v>
+        <v>195000</v>
       </c>
       <c r="F174" t="n">
-        <v>396104.98</v>
+        <v>253671.32</v>
       </c>
       <c r="G174" t="n">
-        <v>0</v>
+        <v>5788.3</v>
       </c>
       <c r="H174" t="n">
-        <v>252066.81</v>
+        <v>201636.18</v>
       </c>
       <c r="I174" t="n">
-        <v>396104.98</v>
+        <v>247883.02</v>
       </c>
       <c r="J174" t="n">
-        <v>0</v>
+        <v>123941.51</v>
       </c>
       <c r="K174" t="n">
-        <v>396104.98</v>
+        <v>123941.51</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>Adana Bölge Bayi A.Ş.</t>
+          <t>Stratejik Ortak E - Atlas</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Ürün Alpha Standart</t>
+          <t>Mekanik ve Havalandırma Tesisatı</t>
         </is>
       </c>
       <c r="C175" s="2" t="n">
@@ -7254,259 +7254,259 @@
         <v>10</v>
       </c>
       <c r="E175" t="n">
-        <v>1850</v>
+        <v>195000</v>
       </c>
       <c r="F175" t="n">
-        <v>79306.73</v>
+        <v>281857.03</v>
       </c>
       <c r="G175" t="n">
-        <v>1704.62</v>
+        <v>0</v>
       </c>
       <c r="H175" t="n">
-        <v>53585.63</v>
+        <v>224040.2</v>
       </c>
       <c r="I175" t="n">
-        <v>77602.11</v>
+        <v>281857.03</v>
       </c>
       <c r="J175" t="n">
-        <v>38801.06</v>
+        <v>140928.52</v>
       </c>
       <c r="K175" t="n">
-        <v>38801.05</v>
+        <v>140928.51</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>Güneydoğu Pazarlama Ltd.</t>
+          <t>Bölge Bayi C - Atlas</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>Ürün Zeta Hızlı Tüketim</t>
+          <t>İnce İşler Zemin Seramik &amp; Şap İşi</t>
         </is>
       </c>
       <c r="C176" s="2" t="n">
         <v>46009</v>
       </c>
       <c r="D176" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="E176" t="n">
-        <v>650</v>
+        <v>120000</v>
       </c>
       <c r="F176" t="n">
-        <v>39010.34</v>
+        <v>138760.38</v>
       </c>
       <c r="G176" t="n">
         <v>0</v>
       </c>
       <c r="H176" t="n">
-        <v>26407</v>
+        <v>109851.97</v>
       </c>
       <c r="I176" t="n">
-        <v>39010.34</v>
+        <v>138760.38</v>
       </c>
       <c r="J176" t="n">
-        <v>19505.17</v>
+        <v>69380.19</v>
       </c>
       <c r="K176" t="n">
-        <v>19505.17</v>
+        <v>69380.19</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>İç Anadolu Tüketim Malları</t>
+          <t>Ticari Kanal G - Atlas</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>Özel Sipariş Modeli X</t>
+          <t>Şantiye Altyapı ve Drenaj İşi</t>
         </is>
       </c>
       <c r="C177" s="2" t="n">
         <v>46011</v>
       </c>
       <c r="D177" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E177" t="n">
-        <v>21500</v>
+        <v>85000</v>
       </c>
       <c r="F177" t="n">
-        <v>1106007.41</v>
+        <v>135146.83</v>
       </c>
       <c r="G177" t="n">
         <v>0</v>
       </c>
       <c r="H177" t="n">
-        <v>730479.3100000001</v>
+        <v>108117.46</v>
       </c>
       <c r="I177" t="n">
-        <v>1106007.41</v>
+        <v>135146.83</v>
       </c>
       <c r="J177" t="n">
-        <v>553003.7</v>
+        <v>67573.41</v>
       </c>
       <c r="K177" t="n">
-        <v>553003.71</v>
+        <v>67573.42</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>Marmara Perakende Çözümleri</t>
+          <t>Müşteri Grubu A - Atlas</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>Yedek Parça Servis Paketi</t>
+          <t>Şantiye Altyapı ve Drenaj İşi</t>
         </is>
       </c>
       <c r="C178" s="2" t="n">
         <v>46013</v>
       </c>
       <c r="D178" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="E178" t="n">
-        <v>2400</v>
+        <v>85000</v>
       </c>
       <c r="F178" t="n">
-        <v>10288.44</v>
+        <v>196577.21</v>
       </c>
       <c r="G178" t="n">
-        <v>0</v>
+        <v>4485.52</v>
       </c>
       <c r="H178" t="n">
-        <v>6430.28</v>
+        <v>157261.77</v>
       </c>
       <c r="I178" t="n">
-        <v>10288.44</v>
+        <v>192091.69</v>
       </c>
       <c r="J178" t="n">
         <v>0</v>
       </c>
       <c r="K178" t="n">
-        <v>10288.44</v>
+        <v>192091.69</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>Toroslar Lojistik ve Ticaret</t>
+          <t>Stratejik Ortak E - Atlas</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>Ürün Gamma Endüstriyel</t>
+          <t>Dış Cephe Yalıtım ve Kompozit Giydirme</t>
         </is>
       </c>
       <c r="C179" s="2" t="n">
         <v>46015</v>
       </c>
       <c r="D179" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="E179" t="n">
-        <v>8900</v>
+        <v>165000</v>
       </c>
       <c r="F179" t="n">
-        <v>267070.78</v>
+        <v>310042.73</v>
       </c>
       <c r="G179" t="n">
-        <v>0</v>
+        <v>10611.87</v>
       </c>
       <c r="H179" t="n">
-        <v>177046.92</v>
+        <v>244276.09</v>
       </c>
       <c r="I179" t="n">
-        <v>267070.78</v>
+        <v>299430.86</v>
       </c>
       <c r="J179" t="n">
-        <v>80121.23</v>
+        <v>89829.25999999999</v>
       </c>
       <c r="K179" t="n">
-        <v>186949.55</v>
+        <v>209601.6</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>Ankara Proje Yönetim ve Satış</t>
+          <t>Müşteri Grubu A - Atlas</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>Ürün Gamma Endüstriyel</t>
+          <t>İnce İşler Zemin Seramik &amp; Şap İşi</t>
         </is>
       </c>
       <c r="C180" s="2" t="n">
         <v>46017</v>
       </c>
       <c r="D180" t="n">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="E180" t="n">
-        <v>8900</v>
+        <v>120000</v>
       </c>
       <c r="F180" t="n">
-        <v>152611.88</v>
+        <v>329555.91</v>
       </c>
       <c r="G180" t="n">
-        <v>3280.24</v>
+        <v>0</v>
       </c>
       <c r="H180" t="n">
-        <v>101169.67</v>
+        <v>260898.43</v>
       </c>
       <c r="I180" t="n">
-        <v>149331.64</v>
+        <v>329555.91</v>
       </c>
       <c r="J180" t="n">
         <v>0</v>
       </c>
       <c r="K180" t="n">
-        <v>149331.64</v>
+        <v>329555.91</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>Bursa İmalat Tedarik Ltd.</t>
+          <t>Toptan Müşteri F - Atlas</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>Ürün Alpha Standart</t>
+          <t>Şantiye Altyapı ve Drenaj İşi</t>
         </is>
       </c>
       <c r="C181" s="2" t="n">
         <v>46019</v>
       </c>
       <c r="D181" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="E181" t="n">
-        <v>1850</v>
+        <v>85000</v>
       </c>
       <c r="F181" t="n">
-        <v>103098.75</v>
+        <v>98288.60000000001</v>
       </c>
       <c r="G181" t="n">
-        <v>2216</v>
+        <v>5606.9</v>
       </c>
       <c r="H181" t="n">
-        <v>69661.32000000001</v>
+        <v>78630.88</v>
       </c>
       <c r="I181" t="n">
-        <v>100882.75</v>
+        <v>92681.7</v>
       </c>
       <c r="J181" t="n">
-        <v>0</v>
+        <v>46340.85</v>
       </c>
       <c r="K181" t="n">
-        <v>100882.75</v>
+        <v>46340.85</v>
       </c>
     </row>
   </sheetData>
